--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\elecroomscada_mariadb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C588AD0-BE37-4D6D-BFFB-B1A571690F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49307ED1-5295-49AF-A125-47F1B95350AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40380" yWindow="3990" windowWidth="17370" windowHeight="11910" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="37470" yWindow="1290" windowWidth="19845" windowHeight="11910" activeTab="1" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="287">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -189,13 +190,731 @@
   <si>
     <t>배기팬 가동</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한전고압계전기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x30004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x30005</t>
+  </si>
+  <si>
+    <t>0x30006</t>
+  </si>
+  <si>
+    <t>0x30007</t>
+  </si>
+  <si>
+    <t>0x30008</t>
+  </si>
+  <si>
+    <t>0x30009</t>
+  </si>
+  <si>
+    <t>0x30010</t>
+  </si>
+  <si>
+    <t>0x30011</t>
+  </si>
+  <si>
+    <t>0x30012</t>
+  </si>
+  <si>
+    <t>0x30013</t>
+  </si>
+  <si>
+    <t>0x30014</t>
+  </si>
+  <si>
+    <t>0x30015</t>
+  </si>
+  <si>
+    <t>0x30016</t>
+  </si>
+  <si>
+    <t>0x30017</t>
+  </si>
+  <si>
+    <t>0x30018</t>
+  </si>
+  <si>
+    <t>0x30019</t>
+  </si>
+  <si>
+    <t>0x30020</t>
+  </si>
+  <si>
+    <t>0x30021</t>
+  </si>
+  <si>
+    <t>0x30022</t>
+  </si>
+  <si>
+    <t>0x30023</t>
+  </si>
+  <si>
+    <t>0x30024</t>
+  </si>
+  <si>
+    <t>0x30025</t>
+  </si>
+  <si>
+    <t>0x30026</t>
+  </si>
+  <si>
+    <t>0x30027</t>
+  </si>
+  <si>
+    <t>0x30028</t>
+  </si>
+  <si>
+    <t>0x30029</t>
+  </si>
+  <si>
+    <t>0x30030</t>
+  </si>
+  <si>
+    <t>0x30031</t>
+  </si>
+  <si>
+    <t>0x30032</t>
+  </si>
+  <si>
+    <t>0x30033</t>
+  </si>
+  <si>
+    <t>0x30034</t>
+  </si>
+  <si>
+    <t>0x30035</t>
+  </si>
+  <si>
+    <t>D00400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00401</t>
+  </si>
+  <si>
+    <t>D00402</t>
+  </si>
+  <si>
+    <t>D00403</t>
+  </si>
+  <si>
+    <t>D00404</t>
+  </si>
+  <si>
+    <t>D00405</t>
+  </si>
+  <si>
+    <t>D00406</t>
+  </si>
+  <si>
+    <t>D00407</t>
+  </si>
+  <si>
+    <t>D00408</t>
+  </si>
+  <si>
+    <t>D00409</t>
+  </si>
+  <si>
+    <t>D00410</t>
+  </si>
+  <si>
+    <t>D00411</t>
+  </si>
+  <si>
+    <t>D00412</t>
+  </si>
+  <si>
+    <t>D00413</t>
+  </si>
+  <si>
+    <t>D00414</t>
+  </si>
+  <si>
+    <t>D00415</t>
+  </si>
+  <si>
+    <t>D00416</t>
+  </si>
+  <si>
+    <t>D00417</t>
+  </si>
+  <si>
+    <t>D00418</t>
+  </si>
+  <si>
+    <t>D00419</t>
+  </si>
+  <si>
+    <t>D00420</t>
+  </si>
+  <si>
+    <t>D00421</t>
+  </si>
+  <si>
+    <t>D00422</t>
+  </si>
+  <si>
+    <t>D00423</t>
+  </si>
+  <si>
+    <t>D00424</t>
+  </si>
+  <si>
+    <t>D00425</t>
+  </si>
+  <si>
+    <t>D00426</t>
+  </si>
+  <si>
+    <t>D00427</t>
+  </si>
+  <si>
+    <t>D00428</t>
+  </si>
+  <si>
+    <t>D00429</t>
+  </si>
+  <si>
+    <t>D00430</t>
+  </si>
+  <si>
+    <t>D00431</t>
+  </si>
+  <si>
+    <t>KEP_V_R</t>
+  </si>
+  <si>
+    <t>KEP_V_S</t>
+  </si>
+  <si>
+    <t>KEP_V_T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEP_V_S_T</t>
+  </si>
+  <si>
+    <t>KEP_V_R_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEP_V_T_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEP_A_R</t>
+  </si>
+  <si>
+    <t>KEP_A_S</t>
+  </si>
+  <si>
+    <t>KEP_A_T</t>
+  </si>
+  <si>
+    <t>KEP_frequency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEP_P_kW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEP_P_kWh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR1계전기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x30036</t>
+  </si>
+  <si>
+    <t>0x30037</t>
+  </si>
+  <si>
+    <t>0x30038</t>
+  </si>
+  <si>
+    <t>D00500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00501</t>
+  </si>
+  <si>
+    <t>D00502</t>
+  </si>
+  <si>
+    <t>D00503</t>
+  </si>
+  <si>
+    <t>D00504</t>
+  </si>
+  <si>
+    <t>D00505</t>
+  </si>
+  <si>
+    <t>D00506</t>
+  </si>
+  <si>
+    <t>D00507</t>
+  </si>
+  <si>
+    <t>D00508</t>
+  </si>
+  <si>
+    <t>D00509</t>
+  </si>
+  <si>
+    <t>D00510</t>
+  </si>
+  <si>
+    <t>D00511</t>
+  </si>
+  <si>
+    <t>D00512</t>
+  </si>
+  <si>
+    <t>D00513</t>
+  </si>
+  <si>
+    <t>D00514</t>
+  </si>
+  <si>
+    <t>D00515</t>
+  </si>
+  <si>
+    <t>D00516</t>
+  </si>
+  <si>
+    <t>D00517</t>
+  </si>
+  <si>
+    <t>D00518</t>
+  </si>
+  <si>
+    <t>D00519</t>
+  </si>
+  <si>
+    <t>D00520</t>
+  </si>
+  <si>
+    <t>D00521</t>
+  </si>
+  <si>
+    <t>D00522</t>
+  </si>
+  <si>
+    <t>D00523</t>
+  </si>
+  <si>
+    <t>D00524</t>
+  </si>
+  <si>
+    <t>D00525</t>
+  </si>
+  <si>
+    <t>D00526</t>
+  </si>
+  <si>
+    <t>D00527</t>
+  </si>
+  <si>
+    <t>D00528</t>
+  </si>
+  <si>
+    <t>D00529</t>
+  </si>
+  <si>
+    <t>D00530</t>
+  </si>
+  <si>
+    <t>D00531</t>
+  </si>
+  <si>
+    <t>D00532</t>
+  </si>
+  <si>
+    <t>D00533</t>
+  </si>
+  <si>
+    <t>D00534</t>
+  </si>
+  <si>
+    <t>0x30039</t>
+  </si>
+  <si>
+    <t>D00535</t>
+  </si>
+  <si>
+    <t>0x30040</t>
+  </si>
+  <si>
+    <t>D00536</t>
+  </si>
+  <si>
+    <t>0x30041</t>
+  </si>
+  <si>
+    <t>D00537</t>
+  </si>
+  <si>
+    <t>Tr1_A_R</t>
+  </si>
+  <si>
+    <t>Tr1_A_S</t>
+  </si>
+  <si>
+    <t>Tr1_A_T</t>
+  </si>
+  <si>
+    <t>Tr1_V_R</t>
+  </si>
+  <si>
+    <t>Tr1_V_S</t>
+  </si>
+  <si>
+    <t>Tr1_V_T</t>
+  </si>
+  <si>
+    <t>Tr1_V_R_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tr1_V_S_T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tr1_V_T_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tr1_P_kW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tr1_Temp</t>
+  </si>
+  <si>
+    <t>TR2계전기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00601</t>
+  </si>
+  <si>
+    <t>D00602</t>
+  </si>
+  <si>
+    <t>D00603</t>
+  </si>
+  <si>
+    <t>D00604</t>
+  </si>
+  <si>
+    <t>D00605</t>
+  </si>
+  <si>
+    <t>D00606</t>
+  </si>
+  <si>
+    <t>D00607</t>
+  </si>
+  <si>
+    <t>D00608</t>
+  </si>
+  <si>
+    <t>D00609</t>
+  </si>
+  <si>
+    <t>D00610</t>
+  </si>
+  <si>
+    <t>D00611</t>
+  </si>
+  <si>
+    <t>D00612</t>
+  </si>
+  <si>
+    <t>D00613</t>
+  </si>
+  <si>
+    <t>D00614</t>
+  </si>
+  <si>
+    <t>D00615</t>
+  </si>
+  <si>
+    <t>D00616</t>
+  </si>
+  <si>
+    <t>D00617</t>
+  </si>
+  <si>
+    <t>D00618</t>
+  </si>
+  <si>
+    <t>D00619</t>
+  </si>
+  <si>
+    <t>D00620</t>
+  </si>
+  <si>
+    <t>D00621</t>
+  </si>
+  <si>
+    <t>D00622</t>
+  </si>
+  <si>
+    <t>D00623</t>
+  </si>
+  <si>
+    <t>D00624</t>
+  </si>
+  <si>
+    <t>D00625</t>
+  </si>
+  <si>
+    <t>D00626</t>
+  </si>
+  <si>
+    <t>D00627</t>
+  </si>
+  <si>
+    <t>D00628</t>
+  </si>
+  <si>
+    <t>D00629</t>
+  </si>
+  <si>
+    <t>D00630</t>
+  </si>
+  <si>
+    <t>D00631</t>
+  </si>
+  <si>
+    <t>D00632</t>
+  </si>
+  <si>
+    <t>D00633</t>
+  </si>
+  <si>
+    <t>D00634</t>
+  </si>
+  <si>
+    <t>D00635</t>
+  </si>
+  <si>
+    <t>D00636</t>
+  </si>
+  <si>
+    <t>D00637</t>
+  </si>
+  <si>
+    <t>Tr2_Temp</t>
+  </si>
+  <si>
+    <t>Tr2_A_R</t>
+  </si>
+  <si>
+    <t>Tr2_A_S</t>
+  </si>
+  <si>
+    <t>Tr2_A_T</t>
+  </si>
+  <si>
+    <t>Tr2_V_R</t>
+  </si>
+  <si>
+    <t>Tr2_V_S</t>
+  </si>
+  <si>
+    <t>Tr2_V_T</t>
+  </si>
+  <si>
+    <t>Tr2_V_R_S</t>
+  </si>
+  <si>
+    <t>Tr2_V_S_T</t>
+  </si>
+  <si>
+    <t>Tr2_V_T_R</t>
+  </si>
+  <si>
+    <t>Tr2_P_kW</t>
+  </si>
+  <si>
+    <t>TR3계전기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00701</t>
+  </si>
+  <si>
+    <t>D00702</t>
+  </si>
+  <si>
+    <t>D00703</t>
+  </si>
+  <si>
+    <t>D00704</t>
+  </si>
+  <si>
+    <t>D00705</t>
+  </si>
+  <si>
+    <t>D00706</t>
+  </si>
+  <si>
+    <t>D00707</t>
+  </si>
+  <si>
+    <t>D00708</t>
+  </si>
+  <si>
+    <t>D00709</t>
+  </si>
+  <si>
+    <t>D00710</t>
+  </si>
+  <si>
+    <t>D00711</t>
+  </si>
+  <si>
+    <t>D00712</t>
+  </si>
+  <si>
+    <t>D00713</t>
+  </si>
+  <si>
+    <t>D00714</t>
+  </si>
+  <si>
+    <t>D00715</t>
+  </si>
+  <si>
+    <t>D00716</t>
+  </si>
+  <si>
+    <t>D00717</t>
+  </si>
+  <si>
+    <t>D00718</t>
+  </si>
+  <si>
+    <t>D00719</t>
+  </si>
+  <si>
+    <t>D00720</t>
+  </si>
+  <si>
+    <t>D00721</t>
+  </si>
+  <si>
+    <t>D00722</t>
+  </si>
+  <si>
+    <t>D00723</t>
+  </si>
+  <si>
+    <t>D00724</t>
+  </si>
+  <si>
+    <t>D00725</t>
+  </si>
+  <si>
+    <t>D00726</t>
+  </si>
+  <si>
+    <t>D00727</t>
+  </si>
+  <si>
+    <t>D00728</t>
+  </si>
+  <si>
+    <t>D00729</t>
+  </si>
+  <si>
+    <t>D00730</t>
+  </si>
+  <si>
+    <t>D00731</t>
+  </si>
+  <si>
+    <t>D00732</t>
+  </si>
+  <si>
+    <t>D00733</t>
+  </si>
+  <si>
+    <t>D00734</t>
+  </si>
+  <si>
+    <t>D00735</t>
+  </si>
+  <si>
+    <t>D00736</t>
+  </si>
+  <si>
+    <t>D00737</t>
+  </si>
+  <si>
+    <t>Tr3_A_R</t>
+  </si>
+  <si>
+    <t>Tr3_A_S</t>
+  </si>
+  <si>
+    <t>Tr3_A_T</t>
+  </si>
+  <si>
+    <t>Tr3_V_R</t>
+  </si>
+  <si>
+    <t>Tr3_V_S</t>
+  </si>
+  <si>
+    <t>Tr3_V_T</t>
+  </si>
+  <si>
+    <t>Tr3_V_R_S</t>
+  </si>
+  <si>
+    <t>Tr3_V_S_T</t>
+  </si>
+  <si>
+    <t>Tr3_V_T_R</t>
+  </si>
+  <si>
+    <t>Tr3_P_kW</t>
+  </si>
+  <si>
+    <t>Tr3_Temp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +929,24 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,8 +971,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -922,4 +1671,1375 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F70ADEE-C5E8-4BF1-B083-ED91F0E7FD88}">
+  <dimension ref="A1:E149"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.796875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B44" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B45" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B47" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B49" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B53" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B54" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B55" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B58" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B59" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B61" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B65" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B66" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B67" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B68" t="s">
+        <v>170</v>
+      </c>
+      <c r="C68" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B69" t="s">
+        <v>172</v>
+      </c>
+      <c r="C69" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B70" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D71" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" t="s">
+        <v>55</v>
+      </c>
+      <c r="C72" t="s">
+        <v>188</v>
+      </c>
+      <c r="D72" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B73" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B74" t="s">
+        <v>57</v>
+      </c>
+      <c r="C74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B76" t="s">
+        <v>59</v>
+      </c>
+      <c r="C76" t="s">
+        <v>192</v>
+      </c>
+      <c r="D76" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C77" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B78" t="s">
+        <v>61</v>
+      </c>
+      <c r="C78" t="s">
+        <v>194</v>
+      </c>
+      <c r="D78" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B79" t="s">
+        <v>62</v>
+      </c>
+      <c r="C79" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B80" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B81" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B82" t="s">
+        <v>65</v>
+      </c>
+      <c r="C82" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B83" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B84" t="s">
+        <v>67</v>
+      </c>
+      <c r="C84" t="s">
+        <v>200</v>
+      </c>
+      <c r="D84" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B85" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B86" t="s">
+        <v>69</v>
+      </c>
+      <c r="C86" t="s">
+        <v>202</v>
+      </c>
+      <c r="D86" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B87" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B88" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" t="s">
+        <v>204</v>
+      </c>
+      <c r="D88" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B89" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B90" t="s">
+        <v>73</v>
+      </c>
+      <c r="C90" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B91" t="s">
+        <v>74</v>
+      </c>
+      <c r="C91" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B92" t="s">
+        <v>75</v>
+      </c>
+      <c r="C92" t="s">
+        <v>208</v>
+      </c>
+      <c r="D92" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B93" t="s">
+        <v>76</v>
+      </c>
+      <c r="C93" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B94" t="s">
+        <v>77</v>
+      </c>
+      <c r="C94" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B95" t="s">
+        <v>78</v>
+      </c>
+      <c r="C95" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B96" t="s">
+        <v>79</v>
+      </c>
+      <c r="C96" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B97" t="s">
+        <v>80</v>
+      </c>
+      <c r="C97" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B98" t="s">
+        <v>81</v>
+      </c>
+      <c r="C98" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B99" t="s">
+        <v>82</v>
+      </c>
+      <c r="C99" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B100" t="s">
+        <v>83</v>
+      </c>
+      <c r="C100" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B101" t="s">
+        <v>84</v>
+      </c>
+      <c r="C101" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B102" t="s">
+        <v>85</v>
+      </c>
+      <c r="C102" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B103" t="s">
+        <v>86</v>
+      </c>
+      <c r="C103" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B104" t="s">
+        <v>132</v>
+      </c>
+      <c r="C104" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B105" t="s">
+        <v>133</v>
+      </c>
+      <c r="C105" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B106" t="s">
+        <v>134</v>
+      </c>
+      <c r="C106" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B108" t="s">
+        <v>172</v>
+      </c>
+      <c r="C108" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B109" t="s">
+        <v>174</v>
+      </c>
+      <c r="C109" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D110" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>237</v>
+      </c>
+      <c r="B111" t="s">
+        <v>55</v>
+      </c>
+      <c r="C111" t="s">
+        <v>238</v>
+      </c>
+      <c r="D111" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B112" t="s">
+        <v>56</v>
+      </c>
+      <c r="C112" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B113" t="s">
+        <v>57</v>
+      </c>
+      <c r="C113" t="s">
+        <v>240</v>
+      </c>
+      <c r="D113" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B114" t="s">
+        <v>58</v>
+      </c>
+      <c r="C114" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B115" t="s">
+        <v>59</v>
+      </c>
+      <c r="C115" t="s">
+        <v>242</v>
+      </c>
+      <c r="D115" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B116" t="s">
+        <v>60</v>
+      </c>
+      <c r="C116" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B117" t="s">
+        <v>61</v>
+      </c>
+      <c r="C117" t="s">
+        <v>244</v>
+      </c>
+      <c r="D117" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B118" t="s">
+        <v>62</v>
+      </c>
+      <c r="C118" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B119" t="s">
+        <v>63</v>
+      </c>
+      <c r="C119" t="s">
+        <v>246</v>
+      </c>
+      <c r="D119" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B120" t="s">
+        <v>64</v>
+      </c>
+      <c r="C120" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B121" t="s">
+        <v>65</v>
+      </c>
+      <c r="C121" t="s">
+        <v>248</v>
+      </c>
+      <c r="D121" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B122" t="s">
+        <v>66</v>
+      </c>
+      <c r="C122" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B123" t="s">
+        <v>67</v>
+      </c>
+      <c r="C123" t="s">
+        <v>250</v>
+      </c>
+      <c r="D123" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B124" t="s">
+        <v>68</v>
+      </c>
+      <c r="C124" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B125" t="s">
+        <v>69</v>
+      </c>
+      <c r="C125" t="s">
+        <v>252</v>
+      </c>
+      <c r="D125" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B126" t="s">
+        <v>70</v>
+      </c>
+      <c r="C126" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B127" t="s">
+        <v>71</v>
+      </c>
+      <c r="C127" t="s">
+        <v>254</v>
+      </c>
+      <c r="D127" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B128" t="s">
+        <v>72</v>
+      </c>
+      <c r="C128" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B129" t="s">
+        <v>73</v>
+      </c>
+      <c r="C129" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B130" t="s">
+        <v>74</v>
+      </c>
+      <c r="C130" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B131" t="s">
+        <v>75</v>
+      </c>
+      <c r="C131" t="s">
+        <v>258</v>
+      </c>
+      <c r="D131" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B132" t="s">
+        <v>76</v>
+      </c>
+      <c r="C132" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B133" t="s">
+        <v>77</v>
+      </c>
+      <c r="C133" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B134" t="s">
+        <v>78</v>
+      </c>
+      <c r="C134" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B135" t="s">
+        <v>79</v>
+      </c>
+      <c r="C135" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B136" t="s">
+        <v>80</v>
+      </c>
+      <c r="C136" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B137" t="s">
+        <v>81</v>
+      </c>
+      <c r="C137" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B138" t="s">
+        <v>82</v>
+      </c>
+      <c r="C138" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B139" t="s">
+        <v>83</v>
+      </c>
+      <c r="C139" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B140" t="s">
+        <v>84</v>
+      </c>
+      <c r="C140" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B141" t="s">
+        <v>85</v>
+      </c>
+      <c r="C141" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B142" t="s">
+        <v>86</v>
+      </c>
+      <c r="C142" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B143" t="s">
+        <v>132</v>
+      </c>
+      <c r="C143" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B144" t="s">
+        <v>133</v>
+      </c>
+      <c r="C144" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B145" t="s">
+        <v>134</v>
+      </c>
+      <c r="C145" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B146" t="s">
+        <v>170</v>
+      </c>
+      <c r="C146" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B147" t="s">
+        <v>172</v>
+      </c>
+      <c r="C147" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B148" t="s">
+        <v>174</v>
+      </c>
+      <c r="C148" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D149" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49307ED1-5295-49AF-A125-47F1B95350AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEE8606-1686-4310-A66C-F1DA0A609EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37470" yWindow="1290" windowWidth="19845" windowHeight="11910" activeTab="1" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="37860" yWindow="1155" windowWidth="19845" windowHeight="11910" activeTab="1" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="292">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -908,6 +908,26 @@
   </si>
   <si>
     <t>Tr3_Temp</t>
+  </si>
+  <si>
+    <t>계전기 명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기기 주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLC 메모리 주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변수명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나눔수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -971,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -982,9 +1002,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1675,1367 +1692,1404 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F70ADEE-C5E8-4BF1-B083-ED91F0E7FD88}">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.796875" style="4"/>
+    <col min="5" max="5" width="7.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>54</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>55</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E2" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1000</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1000</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1000</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1000</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
         <v>75</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
         <v>78</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B25" t="s">
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
         <v>79</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E26">
         <v>1000</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="2"/>
     </row>
     <row r="27" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
         <v>84</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" s="4">
-        <v>1000</v>
-      </c>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
         <v>86</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
         <v>131</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>55</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>135</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>176</v>
       </c>
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" t="s">
-        <v>136</v>
-      </c>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>137</v>
+      </c>
+      <c r="D36" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D37" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>139</v>
+      </c>
+      <c r="D38" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
-      </c>
-      <c r="D39" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="D40" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>143</v>
+      </c>
+      <c r="D42" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
-      </c>
-      <c r="D43" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>145</v>
+      </c>
+      <c r="D44" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>147</v>
+      </c>
+      <c r="D46" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
-      </c>
-      <c r="D47" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" t="s">
+        <v>149</v>
+      </c>
+      <c r="D48" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B49" t="s">
         <v>70</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B49" t="s">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B50" t="s">
         <v>71</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>151</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B50" t="s">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B51" t="s">
         <v>72</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B51" t="s">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B52" t="s">
         <v>73</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B52" t="s">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B53" t="s">
         <v>74</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B53" t="s">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B54" t="s">
         <v>75</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>155</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B54" t="s">
+      <c r="E54">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B55" t="s">
         <v>76</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B55" t="s">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B56" t="s">
         <v>77</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B56" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B57" t="s">
         <v>78</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B57" t="s">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B58" t="s">
         <v>79</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C58" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B58" t="s">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B59" t="s">
         <v>80</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B59" t="s">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B60" t="s">
         <v>81</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C60" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B60" t="s">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B61" t="s">
         <v>82</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B61" t="s">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B62" t="s">
         <v>83</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B62" t="s">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B63" t="s">
         <v>84</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B63" t="s">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B64" t="s">
         <v>85</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B64" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B65" t="s">
         <v>86</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B65" t="s">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B66" t="s">
         <v>132</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B66" t="s">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B67" t="s">
         <v>133</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B67" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B68" t="s">
         <v>134</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B68" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B69" t="s">
         <v>170</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B69" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B70" t="s">
         <v>172</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B70" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B71" t="s">
         <v>174</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D71" s="4" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D72" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A72" t="s">
+      <c r="E72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
         <v>187</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B73" t="s">
         <v>55</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C73" t="s">
         <v>188</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D73" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B73" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B74" t="s">
         <v>56</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B74" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B75" t="s">
         <v>57</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" t="s">
         <v>190</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D75" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B75" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B76" t="s">
         <v>58</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C76" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B76" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B77" t="s">
         <v>59</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C77" t="s">
         <v>192</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D77" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B77" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B78" t="s">
         <v>60</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C78" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B78" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B79" t="s">
         <v>61</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C79" t="s">
         <v>194</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D79" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B79" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B80" t="s">
         <v>62</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B80" t="s">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B81" t="s">
         <v>63</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C81" t="s">
         <v>196</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D81" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B81" t="s">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B82" t="s">
         <v>64</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C82" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B82" t="s">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B83" t="s">
         <v>65</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C83" t="s">
         <v>198</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D83" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B83" t="s">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B84" t="s">
         <v>66</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C84" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B84" t="s">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B85" t="s">
         <v>67</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C85" t="s">
         <v>200</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D85" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B85" t="s">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B86" t="s">
         <v>68</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C86" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B86" t="s">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B87" t="s">
         <v>69</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C87" t="s">
         <v>202</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D87" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B87" t="s">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B88" t="s">
         <v>70</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C88" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B88" t="s">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B89" t="s">
         <v>71</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C89" t="s">
         <v>204</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D89" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B89" t="s">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B90" t="s">
         <v>72</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C90" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B90" t="s">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B91" t="s">
         <v>73</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B91" t="s">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B92" t="s">
         <v>74</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C92" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B92" t="s">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B93" t="s">
         <v>75</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C93" t="s">
         <v>208</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D93" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B93" t="s">
+      <c r="E93">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B94" t="s">
         <v>76</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C94" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B94" t="s">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B95" t="s">
         <v>77</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C95" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="95" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B95" t="s">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B96" t="s">
         <v>78</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C96" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B96" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B97" t="s">
         <v>79</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C97" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B97" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B98" t="s">
         <v>80</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C98" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B98" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B99" t="s">
         <v>81</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C99" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B99" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B100" t="s">
         <v>82</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C100" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B100" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B101" t="s">
         <v>83</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C101" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B101" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B102" t="s">
         <v>84</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B102" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B103" t="s">
         <v>85</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C103" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B103" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B104" t="s">
         <v>86</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C104" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B104" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B105" t="s">
         <v>132</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C105" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B105" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B106" t="s">
         <v>133</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C106" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B106" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B107" t="s">
         <v>134</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C107" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B107" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B108" t="s">
         <v>170</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C108" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B108" t="s">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B109" t="s">
         <v>172</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C109" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B109" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B110" t="s">
         <v>174</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C110" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D110" s="4" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D111" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
+      <c r="E111">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
         <v>237</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B112" t="s">
         <v>55</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C112" t="s">
         <v>238</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D112" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B112" t="s">
-        <v>56</v>
-      </c>
-      <c r="C112" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B113" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>240</v>
-      </c>
-      <c r="D113" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B114" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C114" t="s">
-        <v>241</v>
+        <v>240</v>
+      </c>
+      <c r="D114" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B115" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C115" t="s">
-        <v>242</v>
-      </c>
-      <c r="D115" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B116" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C116" t="s">
-        <v>243</v>
+        <v>242</v>
+      </c>
+      <c r="D116" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B117" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C117" t="s">
-        <v>244</v>
-      </c>
-      <c r="D117" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B118" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C118" t="s">
-        <v>245</v>
+        <v>244</v>
+      </c>
+      <c r="D118" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B119" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>246</v>
-      </c>
-      <c r="D119" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B120" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C120" t="s">
-        <v>247</v>
+        <v>246</v>
+      </c>
+      <c r="D120" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B121" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C121" t="s">
-        <v>248</v>
-      </c>
-      <c r="D121" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B122" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C122" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="D122" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B123" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C123" t="s">
-        <v>250</v>
-      </c>
-      <c r="D123" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B124" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C124" t="s">
-        <v>251</v>
+        <v>250</v>
+      </c>
+      <c r="D124" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B125" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C125" t="s">
-        <v>252</v>
-      </c>
-      <c r="D125" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B126" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C126" t="s">
-        <v>253</v>
+        <v>252</v>
+      </c>
+      <c r="D126" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C127" t="s">
-        <v>254</v>
-      </c>
-      <c r="D127" t="s">
-        <v>284</v>
+        <v>253</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B128" t="s">
+        <v>71</v>
+      </c>
+      <c r="C128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D128" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B129" t="s">
         <v>72</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C129" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B129" t="s">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B130" t="s">
         <v>73</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C130" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B130" t="s">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B131" t="s">
         <v>74</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C131" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B131" t="s">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B132" t="s">
         <v>75</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C132" t="s">
         <v>258</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D132" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B132" t="s">
+      <c r="E132">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B133" t="s">
         <v>76</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C133" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B133" t="s">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B134" t="s">
         <v>77</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C134" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B134" t="s">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B135" t="s">
         <v>78</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C135" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B135" t="s">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B136" t="s">
         <v>79</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C136" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B136" t="s">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B137" t="s">
         <v>80</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C137" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B137" t="s">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B138" t="s">
         <v>81</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C138" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B138" t="s">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B139" t="s">
         <v>82</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C139" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B139" t="s">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B140" t="s">
         <v>83</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C140" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B140" t="s">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B141" t="s">
         <v>84</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C141" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B141" t="s">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B142" t="s">
         <v>85</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C142" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B142" t="s">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B143" t="s">
         <v>86</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C143" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B143" t="s">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B144" t="s">
         <v>132</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C144" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B144" t="s">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B145" t="s">
         <v>133</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C145" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B145" t="s">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B146" t="s">
         <v>134</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C146" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B146" t="s">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B147" t="s">
         <v>170</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B147" t="s">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B148" t="s">
         <v>172</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C148" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B148" t="s">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B149" t="s">
         <v>174</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C149" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="D149" s="4" t="s">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D150" t="s">
         <v>286</v>
+      </c>
+      <c r="E150">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEE8606-1686-4310-A66C-F1DA0A609EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F004A3-08E2-4EF9-B2C5-F407472EC52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37860" yWindow="1155" windowWidth="19845" windowHeight="11910" activeTab="1" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="34320" yWindow="2115" windowWidth="19845" windowHeight="11910" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="766">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -927,6 +929,1438 @@
   </si>
   <si>
     <t>나눔수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변압기 냉각 설비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tr_cooling_start</t>
+  </si>
+  <si>
+    <t>VAR</t>
+  </si>
+  <si>
+    <t>temp_tr01_temp</t>
+  </si>
+  <si>
+    <t>WORD</t>
+  </si>
+  <si>
+    <t>D07027[AUTO]</t>
+  </si>
+  <si>
+    <t>temp_tr02_temp</t>
+  </si>
+  <si>
+    <t>D07028[AUTO]</t>
+  </si>
+  <si>
+    <t>temp_tr03_temp</t>
+  </si>
+  <si>
+    <t>D07029[AUTO]</t>
+  </si>
+  <si>
+    <t>tr01_temp_high</t>
+  </si>
+  <si>
+    <t>BIT</t>
+  </si>
+  <si>
+    <t>D06563.6[AUTO]</t>
+  </si>
+  <si>
+    <t>tr01_temp_low</t>
+  </si>
+  <si>
+    <t>D06563.7[AUTO]</t>
+  </si>
+  <si>
+    <t>tr02_temp_high</t>
+  </si>
+  <si>
+    <t>D06563.D[AUTO]</t>
+  </si>
+  <si>
+    <t>tr02_temp_low</t>
+  </si>
+  <si>
+    <t>D06563.E[AUTO]</t>
+  </si>
+  <si>
+    <t>tr03_temp_high</t>
+  </si>
+  <si>
+    <t>D06563.F[AUTO]</t>
+  </si>
+  <si>
+    <t>tr03_temp_low</t>
+  </si>
+  <si>
+    <t>D06564.0[AUTO]</t>
+  </si>
+  <si>
+    <t>VAR_EXTERNAL</t>
+  </si>
+  <si>
+    <t>TR1_opertime_time</t>
+  </si>
+  <si>
+    <t>D06255[AUTO]</t>
+  </si>
+  <si>
+    <t>래치2</t>
+  </si>
+  <si>
+    <t>TR1_opertime_timer</t>
+  </si>
+  <si>
+    <t>TIMER100</t>
+  </si>
+  <si>
+    <t>T0034[AUTO]</t>
+  </si>
+  <si>
+    <t>TR2_opertime_time</t>
+  </si>
+  <si>
+    <t>D06256[AUTO]</t>
+  </si>
+  <si>
+    <t>TR2_opertime_timer</t>
+  </si>
+  <si>
+    <t>T0036[AUTO]</t>
+  </si>
+  <si>
+    <t>TR3_opertime_time</t>
+  </si>
+  <si>
+    <t>D06257[AUTO]</t>
+  </si>
+  <si>
+    <t>TR3_opertime_timer</t>
+  </si>
+  <si>
+    <t>T0035[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_1_cooling_manual_out</t>
+  </si>
+  <si>
+    <t>D06564.1[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_1_cooling_out</t>
+  </si>
+  <si>
+    <t>D06564.2[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_2_cooling_manual_out</t>
+  </si>
+  <si>
+    <t>D06564.3[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_2_cooling_out</t>
+  </si>
+  <si>
+    <t>D06564.4[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_3_cooling_manual_out</t>
+  </si>
+  <si>
+    <t>D06584.2[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_3_cooling_out</t>
+  </si>
+  <si>
+    <t>D06584.3[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_cooling_auto</t>
+  </si>
+  <si>
+    <t>D06253.7[AUTO]</t>
+  </si>
+  <si>
+    <t>D06253.6[AUTO]</t>
+  </si>
+  <si>
+    <t>TR_opertime_total_time</t>
+  </si>
+  <si>
+    <t>D06258[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_simulation_injection_temp_igh</t>
+  </si>
+  <si>
+    <t>D07030[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_simulation_injection_temp_low</t>
+  </si>
+  <si>
+    <t>D07031[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_EF_tot_op_hour</t>
+  </si>
+  <si>
+    <t>D06242[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_SF_tot_op_hour</t>
+  </si>
+  <si>
+    <t>D06241[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_1hr_count</t>
+  </si>
+  <si>
+    <t>D06955[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_TR1_temp_high_set</t>
+  </si>
+  <si>
+    <t>D06534[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_TR1_temp_low_set</t>
+  </si>
+  <si>
+    <t>D06535[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_TR2_temp_high_set</t>
+  </si>
+  <si>
+    <t>D06532[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_TR2_temp_low_set</t>
+  </si>
+  <si>
+    <t>D06533[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_TR_temp_high_set</t>
+  </si>
+  <si>
+    <t>D06960[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_TR_temp_low_set</t>
+  </si>
+  <si>
+    <t>D06961[AUTO]</t>
+  </si>
+  <si>
+    <t>_01_CH0_TEMP</t>
+  </si>
+  <si>
+    <t>U01.04</t>
+  </si>
+  <si>
+    <t>온도입력모듈 : 채널0 온도변환값(전기실온도)</t>
+  </si>
+  <si>
+    <t>_01_CH1_TEMP</t>
+  </si>
+  <si>
+    <t>U01.05</t>
+  </si>
+  <si>
+    <t>온도입력모듈 : 채널1 온도변환값(외기온도)</t>
+  </si>
+  <si>
+    <t>_01_CH2_TEMP</t>
+  </si>
+  <si>
+    <t>U01.06</t>
+  </si>
+  <si>
+    <t>온도입력모듈 : 채널2 온도변환값</t>
+  </si>
+  <si>
+    <t>_01_CH3_TEMP</t>
+  </si>
+  <si>
+    <t>U01.07</t>
+  </si>
+  <si>
+    <t>온도입력모듈 : 채널3 온도변환값</t>
+  </si>
+  <si>
+    <t>_02_CH0_DATA</t>
+  </si>
+  <si>
+    <t>U02.02</t>
+  </si>
+  <si>
+    <t>아날로그입력 모듈: 채널0 변환값</t>
+  </si>
+  <si>
+    <t>_02_CH1_DATA</t>
+  </si>
+  <si>
+    <t>U02.03</t>
+  </si>
+  <si>
+    <t>아날로그입력 모듈: 채널1 변환값</t>
+  </si>
+  <si>
+    <t>_02_CH2_DATA</t>
+  </si>
+  <si>
+    <t>U02.04</t>
+  </si>
+  <si>
+    <t>아날로그입력 모듈: 채널2 변환값</t>
+  </si>
+  <si>
+    <t>월간타이머리셋</t>
+  </si>
+  <si>
+    <t>D06659.F[AUTO]</t>
+  </si>
+  <si>
+    <t>P00048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tr1_fan_on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P00049</t>
+  </si>
+  <si>
+    <t>P0004A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tr2_fan_on</t>
+  </si>
+  <si>
+    <t>tr3_fan_on</t>
+  </si>
+  <si>
+    <t>BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D06240.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D06240.3</t>
+  </si>
+  <si>
+    <t>D06240.4</t>
+  </si>
+  <si>
+    <t>manual_start_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manual_start_2</t>
+  </si>
+  <si>
+    <t>manual_start_3</t>
+  </si>
+  <si>
+    <t>autumn_set_sw</t>
+  </si>
+  <si>
+    <t>D06506.7[AUTO]</t>
+  </si>
+  <si>
+    <t>가을철 온도</t>
+  </si>
+  <si>
+    <t>basic_win_2_main_menu</t>
+  </si>
+  <si>
+    <t>D06557.5[AUTO]</t>
+  </si>
+  <si>
+    <t>basic_win_2_main_menu_action</t>
+  </si>
+  <si>
+    <t>D06557.6[AUTO]</t>
+  </si>
+  <si>
+    <t>basic_win_3_main_menu</t>
+  </si>
+  <si>
+    <t>D06557.7[AUTO]</t>
+  </si>
+  <si>
+    <t>basic_win_3_main_menu_action</t>
+  </si>
+  <si>
+    <t>D06557.8[AUTO]</t>
+  </si>
+  <si>
+    <t>basic_win_5_main_menu</t>
+  </si>
+  <si>
+    <t>D06557.9[AUTO]</t>
+  </si>
+  <si>
+    <t>basic_win_5_main_menu_action</t>
+  </si>
+  <si>
+    <t>D06557.A[AUTO]</t>
+  </si>
+  <si>
+    <t>cold_winter_set_sw</t>
+  </si>
+  <si>
+    <t>D06619.0[AUTO]</t>
+  </si>
+  <si>
+    <t>dword_reserved_01</t>
+  </si>
+  <si>
+    <t>DWORD</t>
+  </si>
+  <si>
+    <t>D06962[AUTO]</t>
+  </si>
+  <si>
+    <t>dword_reserved_02</t>
+  </si>
+  <si>
+    <t>D06964[AUTO]</t>
+  </si>
+  <si>
+    <t>dword_reserved_03</t>
+  </si>
+  <si>
+    <t>D06966[AUTO]</t>
+  </si>
+  <si>
+    <t>dword_reserved_04</t>
+  </si>
+  <si>
+    <t>D06968[AUTO]</t>
+  </si>
+  <si>
+    <t>dword_reserved_05</t>
+  </si>
+  <si>
+    <t>D06970[AUTO]</t>
+  </si>
+  <si>
+    <t>dword_reserved_06</t>
+  </si>
+  <si>
+    <t>D06972[AUTO]</t>
+  </si>
+  <si>
+    <t>early_winter_set_sw</t>
+  </si>
+  <si>
+    <t>D06506.8[AUTO]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">초겨울 </t>
+  </si>
+  <si>
+    <t>EF_local_auto_point_hour</t>
+  </si>
+  <si>
+    <t>D06557.B[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_local_auto_start</t>
+  </si>
+  <si>
+    <t>D06557.C[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_local_auto_start_out</t>
+  </si>
+  <si>
+    <t>D06253.5[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_local_manual_point_hour</t>
+  </si>
+  <si>
+    <t>D06558.2[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_local_manual_start</t>
+  </si>
+  <si>
+    <t>D06558.3[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_local_manual_start_out</t>
+  </si>
+  <si>
+    <t>D06253.4[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_local_manual_start_sw</t>
+  </si>
+  <si>
+    <t>D06240.1</t>
+  </si>
+  <si>
+    <t>EF_op_room_point_hour</t>
+  </si>
+  <si>
+    <t>D06558.4[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_op_room_start</t>
+  </si>
+  <si>
+    <t>D06558.5[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_op_room_start_out</t>
+  </si>
+  <si>
+    <t>D06253.3[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_stop</t>
+  </si>
+  <si>
+    <t>D06558.6[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_stop_out</t>
+  </si>
+  <si>
+    <t>D06558.7[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_tot_point_hour</t>
+  </si>
+  <si>
+    <t>D06558.8[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_trip</t>
+  </si>
+  <si>
+    <t>D06558.9[AUTO]</t>
+  </si>
+  <si>
+    <t>EF_trip_reset</t>
+  </si>
+  <si>
+    <t>D06558.F[AUTO]</t>
+  </si>
+  <si>
+    <t>heart_beat_manual_sw</t>
+  </si>
+  <si>
+    <t>D06506.C[AUTO]</t>
+  </si>
+  <si>
+    <t>heart_beat_mem</t>
+  </si>
+  <si>
+    <t>D06531[AUTO]</t>
+  </si>
+  <si>
+    <t>heart_beat_timer</t>
+  </si>
+  <si>
+    <t>T0101[AUTO]</t>
+  </si>
+  <si>
+    <t>op_hour_reset</t>
+  </si>
+  <si>
+    <t>D06559.0[AUTO]</t>
+  </si>
+  <si>
+    <t>op_hour_reset_pw_fail</t>
+  </si>
+  <si>
+    <t>D06506.1[AUTO]</t>
+  </si>
+  <si>
+    <t>op_hour_reset_pw_ok</t>
+  </si>
+  <si>
+    <t>D06506.0[AUTO]</t>
+  </si>
+  <si>
+    <t>op_hour_reset_start</t>
+  </si>
+  <si>
+    <t>D06559.1[AUTO]</t>
+  </si>
+  <si>
+    <t>op_hour_reset_start_action</t>
+  </si>
+  <si>
+    <t>D06559.2[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_high_set_change</t>
+  </si>
+  <si>
+    <t>D06974[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_high_set_change_diff</t>
+  </si>
+  <si>
+    <t>D06975[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_high_set_change_ok</t>
+  </si>
+  <si>
+    <t>D06559.3[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_high_set_change_toggle</t>
+  </si>
+  <si>
+    <t>D06559.4[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_high_set_sw</t>
+  </si>
+  <si>
+    <t>D06559.5[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_low_set_change</t>
+  </si>
+  <si>
+    <t>D06976[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_low_set_change_diff</t>
+  </si>
+  <si>
+    <t>D06977[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_low_set_change_ok</t>
+  </si>
+  <si>
+    <t>D06559.6[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_low_set_change_toggle</t>
+  </si>
+  <si>
+    <t>D06559.C[AUTO]</t>
+  </si>
+  <si>
+    <t>outdoor_temp_low_set_sw</t>
+  </si>
+  <si>
+    <t>D06559.D[AUTO]</t>
+  </si>
+  <si>
+    <t>plc_error</t>
+  </si>
+  <si>
+    <t>D06660.1[AUTO]</t>
+  </si>
+  <si>
+    <t>plc_run</t>
+  </si>
+  <si>
+    <t>D06660.0[AUTO]</t>
+  </si>
+  <si>
+    <t>real_reserved_01</t>
+  </si>
+  <si>
+    <t>REAL</t>
+  </si>
+  <si>
+    <t>D06978[AUTO]</t>
+  </si>
+  <si>
+    <t>real_reserved_02</t>
+  </si>
+  <si>
+    <t>D06980[AUTO]</t>
+  </si>
+  <si>
+    <t>real_reserved_03</t>
+  </si>
+  <si>
+    <t>D06982[AUTO]</t>
+  </si>
+  <si>
+    <t>real_reserved_04</t>
+  </si>
+  <si>
+    <t>D06984[AUTO]</t>
+  </si>
+  <si>
+    <t>real_reserved_05</t>
+  </si>
+  <si>
+    <t>D06986[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_high_set_change</t>
+  </si>
+  <si>
+    <t>D06988[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_high_set_change_diff</t>
+  </si>
+  <si>
+    <t>D06989[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_high_set_change_limit_ok</t>
+  </si>
+  <si>
+    <t>D06559.E[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_high_set_change_ok</t>
+  </si>
+  <si>
+    <t>D06559.F[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_high_set_change_toggle</t>
+  </si>
+  <si>
+    <t>D06560.0[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_high_set_sw</t>
+  </si>
+  <si>
+    <t>D06560.1[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_low_set_change</t>
+  </si>
+  <si>
+    <t>D06990[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_low_set_change_diff</t>
+  </si>
+  <si>
+    <t>D06991[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_low_set_change_ok</t>
+  </si>
+  <si>
+    <t>D06560.2[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_low_set_change_toggle</t>
+  </si>
+  <si>
+    <t>D06560.3[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_low_set_sw</t>
+  </si>
+  <si>
+    <t>D06560.9[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_trend_win_open</t>
+  </si>
+  <si>
+    <t>D06560.A[AUTO]</t>
+  </si>
+  <si>
+    <t>room_temp_trend_win_trigger</t>
+  </si>
+  <si>
+    <t>D06560.B[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_local_auto_point_hour</t>
+  </si>
+  <si>
+    <t>D06560.C[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_local_auto_start</t>
+  </si>
+  <si>
+    <t>D06560.D[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_local_auto_start_out</t>
+  </si>
+  <si>
+    <t>D06253.0[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_local_manual_point_hour</t>
+  </si>
+  <si>
+    <t>D06560.E[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_local_manual_start</t>
+  </si>
+  <si>
+    <t>D06560.F[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_local_manual_start_out</t>
+  </si>
+  <si>
+    <t>D06253.1[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_local_manual_start_sw</t>
+  </si>
+  <si>
+    <t>D06240.0</t>
+  </si>
+  <si>
+    <t>SF_op_room_point_hour</t>
+  </si>
+  <si>
+    <t>D06561.0[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_op_room_start</t>
+  </si>
+  <si>
+    <t>D06561.6[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_op_room_start_out</t>
+  </si>
+  <si>
+    <t>D06253.2[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_stop</t>
+  </si>
+  <si>
+    <t>D06253.8[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_stop_out</t>
+  </si>
+  <si>
+    <t>D06561.8[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_tot_point_hour</t>
+  </si>
+  <si>
+    <t>D06561.9[AUTO]</t>
+  </si>
+  <si>
+    <t>sf_trip</t>
+  </si>
+  <si>
+    <t>D06561.A[AUTO]</t>
+  </si>
+  <si>
+    <t>SF_trip_reset</t>
+  </si>
+  <si>
+    <t>D06561.B[AUTO]</t>
+  </si>
+  <si>
+    <t>spring_set_sw</t>
+  </si>
+  <si>
+    <t>D06506.5[AUTO]</t>
+  </si>
+  <si>
+    <t>summer_set_sw</t>
+  </si>
+  <si>
+    <t>D06506.4[AUTO]</t>
+  </si>
+  <si>
+    <t>하절기운전온도 변경</t>
+  </si>
+  <si>
+    <t>tot_power</t>
+  </si>
+  <si>
+    <t>D06992[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_cost</t>
+  </si>
+  <si>
+    <t>D06994[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_l_a_op</t>
+  </si>
+  <si>
+    <t>D06996[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_l_a_op_cost</t>
+  </si>
+  <si>
+    <t>D06998[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_l_a_op_R</t>
+  </si>
+  <si>
+    <t>D07000[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_l_m_op</t>
+  </si>
+  <si>
+    <t>D07002[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_l_m_op_cost</t>
+  </si>
+  <si>
+    <t>D07004[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_l_m_op_R</t>
+  </si>
+  <si>
+    <t>D07006[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_opr_op</t>
+  </si>
+  <si>
+    <t>D07008[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_opr_op_R</t>
+  </si>
+  <si>
+    <t>D07010[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_opr_op_R_cost</t>
+  </si>
+  <si>
+    <t>D07012[AUTO]</t>
+  </si>
+  <si>
+    <t>tot_power_R</t>
+  </si>
+  <si>
+    <t>D07014[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_temp_trend_win_open</t>
+  </si>
+  <si>
+    <t>D06561.C[AUTO]</t>
+  </si>
+  <si>
+    <t>tr_temp_trend_win_trigger</t>
+  </si>
+  <si>
+    <t>D06561.D[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change</t>
+  </si>
+  <si>
+    <t>D06562.3[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_action</t>
+  </si>
+  <si>
+    <t>D06562.4[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_complete</t>
+  </si>
+  <si>
+    <t>D06562.5[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_complete_action</t>
+  </si>
+  <si>
+    <t>D06562.6[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_password</t>
+  </si>
+  <si>
+    <t>D07016[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_password_fail</t>
+  </si>
+  <si>
+    <t>D06562.7[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_password_ok</t>
+  </si>
+  <si>
+    <t>D06562.8[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_pw_fail</t>
+  </si>
+  <si>
+    <t>D06506.2[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_pw_ok</t>
+  </si>
+  <si>
+    <t>D06506.3[AUTO]</t>
+  </si>
+  <si>
+    <t>unit_price_change_temp_value</t>
+  </si>
+  <si>
+    <t>D07017[AUTO]</t>
+  </si>
+  <si>
+    <t>winter_set_sw</t>
+  </si>
+  <si>
+    <t>D06506.6[AUTO]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">겨울철 </t>
+  </si>
+  <si>
+    <t>win_2_view_graph</t>
+  </si>
+  <si>
+    <t>D06562.9[AUTO]</t>
+  </si>
+  <si>
+    <t>win_2_view_graph_open</t>
+  </si>
+  <si>
+    <t>D06562.A[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_01</t>
+  </si>
+  <si>
+    <t>D07018[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_02</t>
+  </si>
+  <si>
+    <t>D07019[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_03</t>
+  </si>
+  <si>
+    <t>D07020[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_04</t>
+  </si>
+  <si>
+    <t>D07021[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_05</t>
+  </si>
+  <si>
+    <t>D07022[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_06</t>
+  </si>
+  <si>
+    <t>D07023[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_07</t>
+  </si>
+  <si>
+    <t>D07024[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_08</t>
+  </si>
+  <si>
+    <t>D07025[AUTO]</t>
+  </si>
+  <si>
+    <t>word_reserved_09</t>
+  </si>
+  <si>
+    <t>D07026[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_EF_tot_local_auto_op_timer</t>
+  </si>
+  <si>
+    <t>T0005[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_EF_tot_local_manual_op_timer</t>
+  </si>
+  <si>
+    <t>T0007[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_EF_tot_op_room_op_timer</t>
+  </si>
+  <si>
+    <t>T0003[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_EF_tot_op_timer</t>
+  </si>
+  <si>
+    <t>T0001[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_SF_tot_local_auto_op_timer</t>
+  </si>
+  <si>
+    <t>T0004[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_SF_tot_local_manual_op_timer</t>
+  </si>
+  <si>
+    <t>T0006[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_SF_tot_op_room_op_timer</t>
+  </si>
+  <si>
+    <t>T0002[AUTO]</t>
+  </si>
+  <si>
+    <t>_000_SF_tot_op_timer</t>
+  </si>
+  <si>
+    <t>T0000[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_EF_tot_local_auto_op_hour</t>
+  </si>
+  <si>
+    <t>D06246[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_EF_tot_local_manual_op_hour</t>
+  </si>
+  <si>
+    <t>D06248[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_EF_tot_op_room_op_hour</t>
+  </si>
+  <si>
+    <t>D06244[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_SF_tot_local_auto_op_hour</t>
+  </si>
+  <si>
+    <t>D06245[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_SF_tot_local_manual_op_hour</t>
+  </si>
+  <si>
+    <t>D06247[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_SF_tot_op_room_op_hour</t>
+  </si>
+  <si>
+    <t>D06243[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_tot_local_auto_op_hour</t>
+  </si>
+  <si>
+    <t>D06251[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_tot_local_manual_op_hour</t>
+  </si>
+  <si>
+    <t>D06252[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_tot_op_hour</t>
+  </si>
+  <si>
+    <t>D06249[AUTO]</t>
+  </si>
+  <si>
+    <t>_001_tot_op_room_op_hour</t>
+  </si>
+  <si>
+    <t>D06250[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_EF_tot_local_auto_op_hour</t>
+  </si>
+  <si>
+    <t>COUNTER</t>
+  </si>
+  <si>
+    <t>C0005[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_EF_tot_local_manual_op_hour</t>
+  </si>
+  <si>
+    <t>C0007[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_EF_tot_op_hour</t>
+  </si>
+  <si>
+    <t>C0001[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_ESF_tot_op_hour</t>
+  </si>
+  <si>
+    <t>_006_EF_tot_op_room_op_hour</t>
+  </si>
+  <si>
+    <t>C0003[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_SF_tot_local_auto_op_hour</t>
+  </si>
+  <si>
+    <t>C0004[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_SF_tot_local_manual_op_hour</t>
+  </si>
+  <si>
+    <t>C0006[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_SF_tot_op_hour</t>
+  </si>
+  <si>
+    <t>C0000[AUTO]</t>
+  </si>
+  <si>
+    <t>_006_SF_tot_op_room_op_hour</t>
+  </si>
+  <si>
+    <t>C0002[AUTO]</t>
+  </si>
+  <si>
+    <t>_007_outdoor_temp</t>
+  </si>
+  <si>
+    <t>D06925[AUTO]</t>
+  </si>
+  <si>
+    <t>_007_outdoor_temp_max_reset</t>
+  </si>
+  <si>
+    <t>D06660.2[AUTO]</t>
+  </si>
+  <si>
+    <t>_007_room_temp</t>
+  </si>
+  <si>
+    <t>D06926[AUTO]</t>
+  </si>
+  <si>
+    <t>_008_room_temp_high_set</t>
+  </si>
+  <si>
+    <t>D06927[AUTO]</t>
+  </si>
+  <si>
+    <t>_008_room_temp_high_set_high_limit</t>
+  </si>
+  <si>
+    <t>D06928[AUTO]</t>
+  </si>
+  <si>
+    <t>_008_room_temp_high_set_low_limit</t>
+  </si>
+  <si>
+    <t>D06929[AUTO]</t>
+  </si>
+  <si>
+    <t>_008_room_temp_low_set</t>
+  </si>
+  <si>
+    <t>D06930[AUTO]</t>
+  </si>
+  <si>
+    <t>_008_room_temp_low_set_high_limit</t>
+  </si>
+  <si>
+    <t>D06931[AUTO]</t>
+  </si>
+  <si>
+    <t>_008_room_temp_low_set_low_limit</t>
+  </si>
+  <si>
+    <t>D06932[AUTO]</t>
+  </si>
+  <si>
+    <t>_009_outdoor_temp_high_set</t>
+  </si>
+  <si>
+    <t>D06933[AUTO]</t>
+  </si>
+  <si>
+    <t>_009_outdoor_temp_high_set_high_limit</t>
+  </si>
+  <si>
+    <t>D06934[AUTO]</t>
+  </si>
+  <si>
+    <t>_009_outdoor_temp_high_set_low_limit</t>
+  </si>
+  <si>
+    <t>D06935[AUTO]</t>
+  </si>
+  <si>
+    <t>_009_outdoor_temp_low_set</t>
+  </si>
+  <si>
+    <t>D06936[AUTO]</t>
+  </si>
+  <si>
+    <t>_009_outdoor_temp_low_set_high_limit</t>
+  </si>
+  <si>
+    <t>D06937[AUTO]</t>
+  </si>
+  <si>
+    <t>_009_outdoor_temp_low_set_low_limit</t>
+  </si>
+  <si>
+    <t>D06938[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_R_power_unit_price_percent</t>
+  </si>
+  <si>
+    <t>D06949[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_1_thousand_hour</t>
+  </si>
+  <si>
+    <t>UINT</t>
+  </si>
+  <si>
+    <t>D06956[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_fan_power_capacity</t>
+  </si>
+  <si>
+    <t>D06957[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_high_low_diff</t>
+  </si>
+  <si>
+    <t>D06958[AUTO]</t>
+  </si>
+  <si>
+    <t>_010_W_power_unit_price</t>
+  </si>
+  <si>
+    <t>D06959[AUTO]</t>
+  </si>
+  <si>
+    <t>급기_현장_수동_출력</t>
+  </si>
+  <si>
+    <t>D06563.0[AUTO]</t>
+  </si>
+  <si>
+    <t>룸_온도내리기</t>
+  </si>
+  <si>
+    <t>D06563.1[AUTO]</t>
+  </si>
+  <si>
+    <t>룸_온도올리기</t>
+  </si>
+  <si>
+    <t>D06563.2[AUTO]</t>
+  </si>
+  <si>
+    <t>배기_현장_수동_출력</t>
+  </si>
+  <si>
+    <t>D06563.3[AUTO]</t>
+  </si>
+  <si>
+    <t>외_온도내리기</t>
+  </si>
+  <si>
+    <t>D06563.4[AUTO]</t>
+  </si>
+  <si>
+    <t>외_온도올리기</t>
+  </si>
+  <si>
+    <t>D06563.5[AUTO]</t>
+  </si>
+  <si>
+    <t>전기실_급배기_동시기동방지</t>
+  </si>
+  <si>
+    <t>T0155[AUTO]</t>
+  </si>
+  <si>
+    <t>P00044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF_operation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P00045</t>
+  </si>
+  <si>
+    <t>EF_operation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -934,7 +2368,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,6 +2402,14 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -991,7 +2433,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1002,6 +2444,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3096,4 +4541,6491 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8CB00BD-499D-452F-8901-A9EC4B3FAAEA}">
+  <dimension ref="A1:J72"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D7" t="s">
+        <v>392</v>
+      </c>
+      <c r="I7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D8" t="s">
+        <v>394</v>
+      </c>
+      <c r="I8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D9" t="s">
+        <v>395</v>
+      </c>
+      <c r="I9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D11" t="s">
+        <v>360</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>315</v>
+      </c>
+      <c r="B12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C12" t="s">
+        <v>296</v>
+      </c>
+      <c r="D12" t="s">
+        <v>362</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13" t="s">
+        <v>363</v>
+      </c>
+      <c r="C13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>315</v>
+      </c>
+      <c r="B14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C14" t="s">
+        <v>296</v>
+      </c>
+      <c r="D14" t="s">
+        <v>366</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>315</v>
+      </c>
+      <c r="B15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" t="s">
+        <v>296</v>
+      </c>
+      <c r="D15" t="s">
+        <v>368</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>294</v>
+      </c>
+      <c r="B30" t="s">
+        <v>295</v>
+      </c>
+      <c r="C30" t="s">
+        <v>296</v>
+      </c>
+      <c r="D30" t="s">
+        <v>297</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" t="s">
+        <v>298</v>
+      </c>
+      <c r="C31" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C32" t="s">
+        <v>296</v>
+      </c>
+      <c r="D32" t="s">
+        <v>301</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>294</v>
+      </c>
+      <c r="B33" t="s">
+        <v>302</v>
+      </c>
+      <c r="C33" t="s">
+        <v>303</v>
+      </c>
+      <c r="D33" t="s">
+        <v>304</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>294</v>
+      </c>
+      <c r="B34" t="s">
+        <v>305</v>
+      </c>
+      <c r="C34" t="s">
+        <v>303</v>
+      </c>
+      <c r="D34" t="s">
+        <v>306</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>294</v>
+      </c>
+      <c r="B35" t="s">
+        <v>307</v>
+      </c>
+      <c r="C35" t="s">
+        <v>303</v>
+      </c>
+      <c r="D35" t="s">
+        <v>308</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>294</v>
+      </c>
+      <c r="B36" t="s">
+        <v>309</v>
+      </c>
+      <c r="C36" t="s">
+        <v>303</v>
+      </c>
+      <c r="D36" t="s">
+        <v>310</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>294</v>
+      </c>
+      <c r="B37" t="s">
+        <v>311</v>
+      </c>
+      <c r="C37" t="s">
+        <v>303</v>
+      </c>
+      <c r="D37" t="s">
+        <v>312</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>294</v>
+      </c>
+      <c r="B38" t="s">
+        <v>313</v>
+      </c>
+      <c r="C38" t="s">
+        <v>303</v>
+      </c>
+      <c r="D38" t="s">
+        <v>314</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>315</v>
+      </c>
+      <c r="B39" t="s">
+        <v>316</v>
+      </c>
+      <c r="C39" t="s">
+        <v>296</v>
+      </c>
+      <c r="D39" t="s">
+        <v>317</v>
+      </c>
+      <c r="E39" t="s">
+        <v>318</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>315</v>
+      </c>
+      <c r="B40" t="s">
+        <v>319</v>
+      </c>
+      <c r="C40" t="s">
+        <v>320</v>
+      </c>
+      <c r="D40" t="s">
+        <v>321</v>
+      </c>
+      <c r="E40" t="s">
+        <v>318</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>315</v>
+      </c>
+      <c r="B41" t="s">
+        <v>322</v>
+      </c>
+      <c r="C41" t="s">
+        <v>296</v>
+      </c>
+      <c r="D41" t="s">
+        <v>323</v>
+      </c>
+      <c r="E41" t="s">
+        <v>318</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>315</v>
+      </c>
+      <c r="B42" t="s">
+        <v>324</v>
+      </c>
+      <c r="C42" t="s">
+        <v>320</v>
+      </c>
+      <c r="D42" t="s">
+        <v>325</v>
+      </c>
+      <c r="E42" t="s">
+        <v>318</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>315</v>
+      </c>
+      <c r="B43" t="s">
+        <v>326</v>
+      </c>
+      <c r="C43" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43" t="s">
+        <v>327</v>
+      </c>
+      <c r="E43" t="s">
+        <v>318</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>315</v>
+      </c>
+      <c r="B44" t="s">
+        <v>328</v>
+      </c>
+      <c r="C44" t="s">
+        <v>320</v>
+      </c>
+      <c r="D44" t="s">
+        <v>329</v>
+      </c>
+      <c r="E44" t="s">
+        <v>318</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>294</v>
+      </c>
+      <c r="B45" t="s">
+        <v>330</v>
+      </c>
+      <c r="C45" t="s">
+        <v>303</v>
+      </c>
+      <c r="D45" t="s">
+        <v>331</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" t="s">
+        <v>332</v>
+      </c>
+      <c r="C46" t="s">
+        <v>303</v>
+      </c>
+      <c r="D46" t="s">
+        <v>333</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>294</v>
+      </c>
+      <c r="B47" t="s">
+        <v>334</v>
+      </c>
+      <c r="C47" t="s">
+        <v>303</v>
+      </c>
+      <c r="D47" t="s">
+        <v>335</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>294</v>
+      </c>
+      <c r="B48" t="s">
+        <v>336</v>
+      </c>
+      <c r="C48" t="s">
+        <v>303</v>
+      </c>
+      <c r="D48" t="s">
+        <v>337</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>336</v>
+      </c>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>294</v>
+      </c>
+      <c r="B49" t="s">
+        <v>338</v>
+      </c>
+      <c r="C49" t="s">
+        <v>303</v>
+      </c>
+      <c r="D49" t="s">
+        <v>339</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
+        <v>338</v>
+      </c>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>294</v>
+      </c>
+      <c r="B50" t="s">
+        <v>340</v>
+      </c>
+      <c r="C50" t="s">
+        <v>303</v>
+      </c>
+      <c r="D50" t="s">
+        <v>341</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F51" s="4">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F52" s="4">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>315</v>
+      </c>
+      <c r="B53" t="s">
+        <v>345</v>
+      </c>
+      <c r="C53" t="s">
+        <v>296</v>
+      </c>
+      <c r="D53" t="s">
+        <v>346</v>
+      </c>
+      <c r="E53" t="s">
+        <v>318</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" t="s">
+        <v>347</v>
+      </c>
+      <c r="C54" t="s">
+        <v>296</v>
+      </c>
+      <c r="D54" t="s">
+        <v>348</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>294</v>
+      </c>
+      <c r="B55" t="s">
+        <v>349</v>
+      </c>
+      <c r="C55" t="s">
+        <v>296</v>
+      </c>
+      <c r="D55" t="s">
+        <v>350</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>315</v>
+      </c>
+      <c r="B56" t="s">
+        <v>351</v>
+      </c>
+      <c r="C56" t="s">
+        <v>296</v>
+      </c>
+      <c r="D56" t="s">
+        <v>352</v>
+      </c>
+      <c r="E56" t="s">
+        <v>318</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>315</v>
+      </c>
+      <c r="B57" t="s">
+        <v>353</v>
+      </c>
+      <c r="C57" t="s">
+        <v>296</v>
+      </c>
+      <c r="D57" t="s">
+        <v>354</v>
+      </c>
+      <c r="E57" t="s">
+        <v>318</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>315</v>
+      </c>
+      <c r="B58" t="s">
+        <v>355</v>
+      </c>
+      <c r="C58" t="s">
+        <v>296</v>
+      </c>
+      <c r="D58" t="s">
+        <v>356</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>315</v>
+      </c>
+      <c r="B59" t="s">
+        <v>357</v>
+      </c>
+      <c r="C59" t="s">
+        <v>296</v>
+      </c>
+      <c r="D59" t="s">
+        <v>358</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>315</v>
+      </c>
+      <c r="B60" t="s">
+        <v>359</v>
+      </c>
+      <c r="C60" t="s">
+        <v>296</v>
+      </c>
+      <c r="D60" t="s">
+        <v>360</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" t="s">
+        <v>361</v>
+      </c>
+      <c r="C61" t="s">
+        <v>296</v>
+      </c>
+      <c r="D61" t="s">
+        <v>362</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>315</v>
+      </c>
+      <c r="B62" t="s">
+        <v>363</v>
+      </c>
+      <c r="C62" t="s">
+        <v>296</v>
+      </c>
+      <c r="D62" t="s">
+        <v>364</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>315</v>
+      </c>
+      <c r="B63" t="s">
+        <v>365</v>
+      </c>
+      <c r="C63" t="s">
+        <v>296</v>
+      </c>
+      <c r="D63" t="s">
+        <v>366</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>315</v>
+      </c>
+      <c r="B64" t="s">
+        <v>367</v>
+      </c>
+      <c r="C64" t="s">
+        <v>296</v>
+      </c>
+      <c r="D64" t="s">
+        <v>368</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>315</v>
+      </c>
+      <c r="B65" t="s">
+        <v>369</v>
+      </c>
+      <c r="C65" t="s">
+        <v>296</v>
+      </c>
+      <c r="D65" t="s">
+        <v>370</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>315</v>
+      </c>
+      <c r="B66" t="s">
+        <v>372</v>
+      </c>
+      <c r="C66" t="s">
+        <v>296</v>
+      </c>
+      <c r="D66" t="s">
+        <v>373</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>315</v>
+      </c>
+      <c r="B67" t="s">
+        <v>375</v>
+      </c>
+      <c r="C67" t="s">
+        <v>296</v>
+      </c>
+      <c r="D67" t="s">
+        <v>376</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>315</v>
+      </c>
+      <c r="B68" t="s">
+        <v>378</v>
+      </c>
+      <c r="C68" t="s">
+        <v>296</v>
+      </c>
+      <c r="D68" t="s">
+        <v>379</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>315</v>
+      </c>
+      <c r="B69" t="s">
+        <v>381</v>
+      </c>
+      <c r="C69" t="s">
+        <v>296</v>
+      </c>
+      <c r="D69" t="s">
+        <v>382</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>315</v>
+      </c>
+      <c r="B70" t="s">
+        <v>384</v>
+      </c>
+      <c r="C70" t="s">
+        <v>296</v>
+      </c>
+      <c r="D70" t="s">
+        <v>385</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>315</v>
+      </c>
+      <c r="B71" t="s">
+        <v>387</v>
+      </c>
+      <c r="C71" t="s">
+        <v>296</v>
+      </c>
+      <c r="D71" t="s">
+        <v>388</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>315</v>
+      </c>
+      <c r="B72" t="s">
+        <v>390</v>
+      </c>
+      <c r="C72" t="s">
+        <v>303</v>
+      </c>
+      <c r="D72" t="s">
+        <v>391</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2836F51-32CE-4EC5-A2A6-D682AE17D0BB}">
+  <dimension ref="A1:I229"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F1">
+        <v>1</v>
+      </c>
+      <c r="G1">
+        <v>0</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" t="s">
+        <v>562</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D4" t="s">
+        <v>554</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" t="s">
+        <v>571</v>
+      </c>
+      <c r="C5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D5" t="s">
+        <v>572</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D7" t="s">
+        <v>441</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" t="s">
+        <v>455</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>294</v>
+      </c>
+      <c r="B9" t="s">
+        <v>446</v>
+      </c>
+      <c r="C9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D9" t="s">
+        <v>447</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D10" t="s">
+        <v>465</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="D11" t="s">
+        <v>762</v>
+      </c>
+      <c r="I11" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="D12" t="s">
+        <v>764</v>
+      </c>
+      <c r="I12" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>315</v>
+      </c>
+      <c r="B51" t="s">
+        <v>405</v>
+      </c>
+      <c r="C51" t="s">
+        <v>303</v>
+      </c>
+      <c r="D51" t="s">
+        <v>406</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>294</v>
+      </c>
+      <c r="B52" t="s">
+        <v>408</v>
+      </c>
+      <c r="C52" t="s">
+        <v>303</v>
+      </c>
+      <c r="D52" t="s">
+        <v>409</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" t="s">
+        <v>410</v>
+      </c>
+      <c r="C53" t="s">
+        <v>303</v>
+      </c>
+      <c r="D53" t="s">
+        <v>411</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" t="s">
+        <v>412</v>
+      </c>
+      <c r="C54" t="s">
+        <v>303</v>
+      </c>
+      <c r="D54" t="s">
+        <v>413</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>294</v>
+      </c>
+      <c r="B55" t="s">
+        <v>414</v>
+      </c>
+      <c r="C55" t="s">
+        <v>303</v>
+      </c>
+      <c r="D55" t="s">
+        <v>415</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>294</v>
+      </c>
+      <c r="B56" t="s">
+        <v>416</v>
+      </c>
+      <c r="C56" t="s">
+        <v>303</v>
+      </c>
+      <c r="D56" t="s">
+        <v>417</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>294</v>
+      </c>
+      <c r="B57" t="s">
+        <v>418</v>
+      </c>
+      <c r="C57" t="s">
+        <v>303</v>
+      </c>
+      <c r="D57" t="s">
+        <v>419</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>315</v>
+      </c>
+      <c r="B58" t="s">
+        <v>420</v>
+      </c>
+      <c r="C58" t="s">
+        <v>303</v>
+      </c>
+      <c r="D58" t="s">
+        <v>421</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>422</v>
+      </c>
+      <c r="C59" t="s">
+        <v>423</v>
+      </c>
+      <c r="D59" t="s">
+        <v>424</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>294</v>
+      </c>
+      <c r="B60" t="s">
+        <v>425</v>
+      </c>
+      <c r="C60" t="s">
+        <v>423</v>
+      </c>
+      <c r="D60" t="s">
+        <v>426</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" t="s">
+        <v>427</v>
+      </c>
+      <c r="C61" t="s">
+        <v>423</v>
+      </c>
+      <c r="D61" t="s">
+        <v>428</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>294</v>
+      </c>
+      <c r="B62" t="s">
+        <v>429</v>
+      </c>
+      <c r="C62" t="s">
+        <v>423</v>
+      </c>
+      <c r="D62" t="s">
+        <v>430</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" t="s">
+        <v>431</v>
+      </c>
+      <c r="C63" t="s">
+        <v>423</v>
+      </c>
+      <c r="D63" t="s">
+        <v>432</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>294</v>
+      </c>
+      <c r="B64" t="s">
+        <v>433</v>
+      </c>
+      <c r="C64" t="s">
+        <v>423</v>
+      </c>
+      <c r="D64" t="s">
+        <v>434</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>315</v>
+      </c>
+      <c r="B65" t="s">
+        <v>435</v>
+      </c>
+      <c r="C65" t="s">
+        <v>303</v>
+      </c>
+      <c r="D65" t="s">
+        <v>436</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>294</v>
+      </c>
+      <c r="B66" t="s">
+        <v>438</v>
+      </c>
+      <c r="C66" t="s">
+        <v>303</v>
+      </c>
+      <c r="D66" t="s">
+        <v>439</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>294</v>
+      </c>
+      <c r="B67" t="s">
+        <v>440</v>
+      </c>
+      <c r="C67" t="s">
+        <v>303</v>
+      </c>
+      <c r="D67" t="s">
+        <v>441</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>294</v>
+      </c>
+      <c r="B68" t="s">
+        <v>442</v>
+      </c>
+      <c r="C68" t="s">
+        <v>303</v>
+      </c>
+      <c r="D68" t="s">
+        <v>443</v>
+      </c>
+      <c r="E68" t="s">
+        <v>318</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>294</v>
+      </c>
+      <c r="B69" t="s">
+        <v>444</v>
+      </c>
+      <c r="C69" t="s">
+        <v>303</v>
+      </c>
+      <c r="D69" t="s">
+        <v>445</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>294</v>
+      </c>
+      <c r="B70" t="s">
+        <v>446</v>
+      </c>
+      <c r="C70" t="s">
+        <v>303</v>
+      </c>
+      <c r="D70" t="s">
+        <v>447</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>294</v>
+      </c>
+      <c r="B71" t="s">
+        <v>448</v>
+      </c>
+      <c r="C71" t="s">
+        <v>303</v>
+      </c>
+      <c r="D71" t="s">
+        <v>449</v>
+      </c>
+      <c r="E71" t="s">
+        <v>318</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>294</v>
+      </c>
+      <c r="B72" t="s">
+        <v>450</v>
+      </c>
+      <c r="C72" t="s">
+        <v>303</v>
+      </c>
+      <c r="D72" t="s">
+        <v>451</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>294</v>
+      </c>
+      <c r="B73" t="s">
+        <v>452</v>
+      </c>
+      <c r="C73" t="s">
+        <v>303</v>
+      </c>
+      <c r="D73" t="s">
+        <v>453</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>294</v>
+      </c>
+      <c r="B74" t="s">
+        <v>454</v>
+      </c>
+      <c r="C74" t="s">
+        <v>303</v>
+      </c>
+      <c r="D74" t="s">
+        <v>455</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>294</v>
+      </c>
+      <c r="B75" t="s">
+        <v>456</v>
+      </c>
+      <c r="C75" t="s">
+        <v>303</v>
+      </c>
+      <c r="D75" t="s">
+        <v>457</v>
+      </c>
+      <c r="E75" t="s">
+        <v>318</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>294</v>
+      </c>
+      <c r="B76" t="s">
+        <v>458</v>
+      </c>
+      <c r="C76" t="s">
+        <v>303</v>
+      </c>
+      <c r="D76" t="s">
+        <v>459</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>294</v>
+      </c>
+      <c r="B77" t="s">
+        <v>460</v>
+      </c>
+      <c r="C77" t="s">
+        <v>303</v>
+      </c>
+      <c r="D77" t="s">
+        <v>461</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>294</v>
+      </c>
+      <c r="B78" t="s">
+        <v>462</v>
+      </c>
+      <c r="C78" t="s">
+        <v>303</v>
+      </c>
+      <c r="D78" t="s">
+        <v>463</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>294</v>
+      </c>
+      <c r="B79" t="s">
+        <v>464</v>
+      </c>
+      <c r="C79" t="s">
+        <v>303</v>
+      </c>
+      <c r="D79" t="s">
+        <v>465</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>294</v>
+      </c>
+      <c r="B80" t="s">
+        <v>466</v>
+      </c>
+      <c r="C80" t="s">
+        <v>303</v>
+      </c>
+      <c r="D80" t="s">
+        <v>467</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>315</v>
+      </c>
+      <c r="B81" t="s">
+        <v>468</v>
+      </c>
+      <c r="C81" t="s">
+        <v>303</v>
+      </c>
+      <c r="D81" t="s">
+        <v>469</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>315</v>
+      </c>
+      <c r="B82" t="s">
+        <v>470</v>
+      </c>
+      <c r="C82" t="s">
+        <v>296</v>
+      </c>
+      <c r="D82" t="s">
+        <v>471</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>315</v>
+      </c>
+      <c r="B83" t="s">
+        <v>472</v>
+      </c>
+      <c r="C83" t="s">
+        <v>320</v>
+      </c>
+      <c r="D83" t="s">
+        <v>473</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>294</v>
+      </c>
+      <c r="B84" t="s">
+        <v>474</v>
+      </c>
+      <c r="C84" t="s">
+        <v>303</v>
+      </c>
+      <c r="D84" t="s">
+        <v>475</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>294</v>
+      </c>
+      <c r="B85" t="s">
+        <v>476</v>
+      </c>
+      <c r="C85" t="s">
+        <v>303</v>
+      </c>
+      <c r="D85" t="s">
+        <v>477</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>294</v>
+      </c>
+      <c r="B86" t="s">
+        <v>478</v>
+      </c>
+      <c r="C86" t="s">
+        <v>303</v>
+      </c>
+      <c r="D86" t="s">
+        <v>479</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>294</v>
+      </c>
+      <c r="B87" t="s">
+        <v>480</v>
+      </c>
+      <c r="C87" t="s">
+        <v>303</v>
+      </c>
+      <c r="D87" t="s">
+        <v>481</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>294</v>
+      </c>
+      <c r="B88" t="s">
+        <v>482</v>
+      </c>
+      <c r="C88" t="s">
+        <v>303</v>
+      </c>
+      <c r="D88" t="s">
+        <v>483</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>294</v>
+      </c>
+      <c r="B89" t="s">
+        <v>484</v>
+      </c>
+      <c r="C89" t="s">
+        <v>296</v>
+      </c>
+      <c r="D89" t="s">
+        <v>485</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" t="s">
+        <v>486</v>
+      </c>
+      <c r="C90" t="s">
+        <v>296</v>
+      </c>
+      <c r="D90" t="s">
+        <v>487</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>294</v>
+      </c>
+      <c r="B91" t="s">
+        <v>488</v>
+      </c>
+      <c r="C91" t="s">
+        <v>303</v>
+      </c>
+      <c r="D91" t="s">
+        <v>489</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>294</v>
+      </c>
+      <c r="B92" t="s">
+        <v>490</v>
+      </c>
+      <c r="C92" t="s">
+        <v>303</v>
+      </c>
+      <c r="D92" t="s">
+        <v>491</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>294</v>
+      </c>
+      <c r="B93" t="s">
+        <v>492</v>
+      </c>
+      <c r="C93" t="s">
+        <v>303</v>
+      </c>
+      <c r="D93" t="s">
+        <v>493</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>294</v>
+      </c>
+      <c r="B94" t="s">
+        <v>494</v>
+      </c>
+      <c r="C94" t="s">
+        <v>296</v>
+      </c>
+      <c r="D94" t="s">
+        <v>495</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>294</v>
+      </c>
+      <c r="B95" t="s">
+        <v>496</v>
+      </c>
+      <c r="C95" t="s">
+        <v>296</v>
+      </c>
+      <c r="D95" t="s">
+        <v>497</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>294</v>
+      </c>
+      <c r="B96" t="s">
+        <v>498</v>
+      </c>
+      <c r="C96" t="s">
+        <v>303</v>
+      </c>
+      <c r="D96" t="s">
+        <v>499</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>294</v>
+      </c>
+      <c r="B97" t="s">
+        <v>500</v>
+      </c>
+      <c r="C97" t="s">
+        <v>303</v>
+      </c>
+      <c r="D97" t="s">
+        <v>501</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>294</v>
+      </c>
+      <c r="B98" t="s">
+        <v>502</v>
+      </c>
+      <c r="C98" t="s">
+        <v>303</v>
+      </c>
+      <c r="D98" t="s">
+        <v>503</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>294</v>
+      </c>
+      <c r="B99" t="s">
+        <v>504</v>
+      </c>
+      <c r="C99" t="s">
+        <v>303</v>
+      </c>
+      <c r="D99" t="s">
+        <v>505</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>294</v>
+      </c>
+      <c r="B100" t="s">
+        <v>506</v>
+      </c>
+      <c r="C100" t="s">
+        <v>303</v>
+      </c>
+      <c r="D100" t="s">
+        <v>507</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>294</v>
+      </c>
+      <c r="B101" t="s">
+        <v>508</v>
+      </c>
+      <c r="C101" t="s">
+        <v>509</v>
+      </c>
+      <c r="D101" t="s">
+        <v>510</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>294</v>
+      </c>
+      <c r="B102" t="s">
+        <v>511</v>
+      </c>
+      <c r="C102" t="s">
+        <v>509</v>
+      </c>
+      <c r="D102" t="s">
+        <v>512</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>294</v>
+      </c>
+      <c r="B103" t="s">
+        <v>513</v>
+      </c>
+      <c r="C103" t="s">
+        <v>509</v>
+      </c>
+      <c r="D103" t="s">
+        <v>514</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>294</v>
+      </c>
+      <c r="B104" t="s">
+        <v>515</v>
+      </c>
+      <c r="C104" t="s">
+        <v>509</v>
+      </c>
+      <c r="D104" t="s">
+        <v>516</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>294</v>
+      </c>
+      <c r="B105" t="s">
+        <v>517</v>
+      </c>
+      <c r="C105" t="s">
+        <v>509</v>
+      </c>
+      <c r="D105" t="s">
+        <v>518</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>294</v>
+      </c>
+      <c r="B106" t="s">
+        <v>519</v>
+      </c>
+      <c r="C106" t="s">
+        <v>296</v>
+      </c>
+      <c r="D106" t="s">
+        <v>520</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>294</v>
+      </c>
+      <c r="B107" t="s">
+        <v>521</v>
+      </c>
+      <c r="C107" t="s">
+        <v>296</v>
+      </c>
+      <c r="D107" t="s">
+        <v>522</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>294</v>
+      </c>
+      <c r="B108" t="s">
+        <v>523</v>
+      </c>
+      <c r="C108" t="s">
+        <v>303</v>
+      </c>
+      <c r="D108" t="s">
+        <v>524</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>294</v>
+      </c>
+      <c r="B109" t="s">
+        <v>525</v>
+      </c>
+      <c r="C109" t="s">
+        <v>303</v>
+      </c>
+      <c r="D109" t="s">
+        <v>526</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>294</v>
+      </c>
+      <c r="B110" t="s">
+        <v>527</v>
+      </c>
+      <c r="C110" t="s">
+        <v>303</v>
+      </c>
+      <c r="D110" t="s">
+        <v>528</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>294</v>
+      </c>
+      <c r="B111" t="s">
+        <v>529</v>
+      </c>
+      <c r="C111" t="s">
+        <v>303</v>
+      </c>
+      <c r="D111" t="s">
+        <v>530</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>294</v>
+      </c>
+      <c r="B112" t="s">
+        <v>531</v>
+      </c>
+      <c r="C112" t="s">
+        <v>296</v>
+      </c>
+      <c r="D112" t="s">
+        <v>532</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>294</v>
+      </c>
+      <c r="B113" t="s">
+        <v>533</v>
+      </c>
+      <c r="C113" t="s">
+        <v>296</v>
+      </c>
+      <c r="D113" t="s">
+        <v>534</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>294</v>
+      </c>
+      <c r="B114" t="s">
+        <v>535</v>
+      </c>
+      <c r="C114" t="s">
+        <v>303</v>
+      </c>
+      <c r="D114" t="s">
+        <v>536</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>294</v>
+      </c>
+      <c r="B115" t="s">
+        <v>537</v>
+      </c>
+      <c r="C115" t="s">
+        <v>303</v>
+      </c>
+      <c r="D115" t="s">
+        <v>538</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>294</v>
+      </c>
+      <c r="B116" t="s">
+        <v>539</v>
+      </c>
+      <c r="C116" t="s">
+        <v>303</v>
+      </c>
+      <c r="D116" t="s">
+        <v>540</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>294</v>
+      </c>
+      <c r="B117" t="s">
+        <v>541</v>
+      </c>
+      <c r="C117" t="s">
+        <v>303</v>
+      </c>
+      <c r="D117" t="s">
+        <v>542</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>294</v>
+      </c>
+      <c r="B118" t="s">
+        <v>543</v>
+      </c>
+      <c r="C118" t="s">
+        <v>303</v>
+      </c>
+      <c r="D118" t="s">
+        <v>544</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>294</v>
+      </c>
+      <c r="B119" t="s">
+        <v>545</v>
+      </c>
+      <c r="C119" t="s">
+        <v>303</v>
+      </c>
+      <c r="D119" t="s">
+        <v>546</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>294</v>
+      </c>
+      <c r="B120" t="s">
+        <v>547</v>
+      </c>
+      <c r="C120" t="s">
+        <v>303</v>
+      </c>
+      <c r="D120" t="s">
+        <v>548</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>294</v>
+      </c>
+      <c r="B121" t="s">
+        <v>549</v>
+      </c>
+      <c r="C121" t="s">
+        <v>303</v>
+      </c>
+      <c r="D121" t="s">
+        <v>550</v>
+      </c>
+      <c r="E121" t="s">
+        <v>318</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>294</v>
+      </c>
+      <c r="B122" t="s">
+        <v>551</v>
+      </c>
+      <c r="C122" t="s">
+        <v>303</v>
+      </c>
+      <c r="D122" t="s">
+        <v>552</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>294</v>
+      </c>
+      <c r="B123" t="s">
+        <v>553</v>
+      </c>
+      <c r="C123" t="s">
+        <v>303</v>
+      </c>
+      <c r="D123" t="s">
+        <v>554</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>294</v>
+      </c>
+      <c r="B124" t="s">
+        <v>555</v>
+      </c>
+      <c r="C124" t="s">
+        <v>303</v>
+      </c>
+      <c r="D124" t="s">
+        <v>556</v>
+      </c>
+      <c r="E124" t="s">
+        <v>318</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>294</v>
+      </c>
+      <c r="B125" t="s">
+        <v>557</v>
+      </c>
+      <c r="C125" t="s">
+        <v>303</v>
+      </c>
+      <c r="D125" t="s">
+        <v>558</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>294</v>
+      </c>
+      <c r="B126" t="s">
+        <v>559</v>
+      </c>
+      <c r="C126" t="s">
+        <v>303</v>
+      </c>
+      <c r="D126" t="s">
+        <v>560</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>294</v>
+      </c>
+      <c r="B127" t="s">
+        <v>561</v>
+      </c>
+      <c r="C127" t="s">
+        <v>303</v>
+      </c>
+      <c r="D127" t="s">
+        <v>562</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>294</v>
+      </c>
+      <c r="B128" t="s">
+        <v>563</v>
+      </c>
+      <c r="C128" t="s">
+        <v>303</v>
+      </c>
+      <c r="D128" t="s">
+        <v>564</v>
+      </c>
+      <c r="E128" t="s">
+        <v>318</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>294</v>
+      </c>
+      <c r="B129" t="s">
+        <v>565</v>
+      </c>
+      <c r="C129" t="s">
+        <v>303</v>
+      </c>
+      <c r="D129" t="s">
+        <v>566</v>
+      </c>
+      <c r="E129" t="s">
+        <v>318</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>294</v>
+      </c>
+      <c r="B130" t="s">
+        <v>567</v>
+      </c>
+      <c r="C130" t="s">
+        <v>303</v>
+      </c>
+      <c r="D130" t="s">
+        <v>568</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>294</v>
+      </c>
+      <c r="B131" t="s">
+        <v>569</v>
+      </c>
+      <c r="C131" t="s">
+        <v>303</v>
+      </c>
+      <c r="D131" t="s">
+        <v>570</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" t="s">
+        <v>571</v>
+      </c>
+      <c r="C132" t="s">
+        <v>303</v>
+      </c>
+      <c r="D132" t="s">
+        <v>572</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>294</v>
+      </c>
+      <c r="B133" t="s">
+        <v>573</v>
+      </c>
+      <c r="C133" t="s">
+        <v>303</v>
+      </c>
+      <c r="D133" t="s">
+        <v>574</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A134" t="s">
+        <v>315</v>
+      </c>
+      <c r="B134" t="s">
+        <v>575</v>
+      </c>
+      <c r="C134" t="s">
+        <v>303</v>
+      </c>
+      <c r="D134" t="s">
+        <v>576</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>315</v>
+      </c>
+      <c r="B135" t="s">
+        <v>577</v>
+      </c>
+      <c r="C135" t="s">
+        <v>303</v>
+      </c>
+      <c r="D135" t="s">
+        <v>578</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>294</v>
+      </c>
+      <c r="B136" t="s">
+        <v>580</v>
+      </c>
+      <c r="C136" t="s">
+        <v>423</v>
+      </c>
+      <c r="D136" t="s">
+        <v>581</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>294</v>
+      </c>
+      <c r="B137" t="s">
+        <v>582</v>
+      </c>
+      <c r="C137" t="s">
+        <v>509</v>
+      </c>
+      <c r="D137" t="s">
+        <v>583</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A138" t="s">
+        <v>294</v>
+      </c>
+      <c r="B138" t="s">
+        <v>584</v>
+      </c>
+      <c r="C138" t="s">
+        <v>423</v>
+      </c>
+      <c r="D138" t="s">
+        <v>585</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>294</v>
+      </c>
+      <c r="B139" t="s">
+        <v>586</v>
+      </c>
+      <c r="C139" t="s">
+        <v>509</v>
+      </c>
+      <c r="D139" t="s">
+        <v>587</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>294</v>
+      </c>
+      <c r="B140" t="s">
+        <v>588</v>
+      </c>
+      <c r="C140" t="s">
+        <v>509</v>
+      </c>
+      <c r="D140" t="s">
+        <v>589</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>294</v>
+      </c>
+      <c r="B141" t="s">
+        <v>590</v>
+      </c>
+      <c r="C141" t="s">
+        <v>423</v>
+      </c>
+      <c r="D141" t="s">
+        <v>591</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
+        <v>294</v>
+      </c>
+      <c r="B142" t="s">
+        <v>592</v>
+      </c>
+      <c r="C142" t="s">
+        <v>509</v>
+      </c>
+      <c r="D142" t="s">
+        <v>593</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>294</v>
+      </c>
+      <c r="B143" t="s">
+        <v>594</v>
+      </c>
+      <c r="C143" t="s">
+        <v>509</v>
+      </c>
+      <c r="D143" t="s">
+        <v>595</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>294</v>
+      </c>
+      <c r="B144" t="s">
+        <v>596</v>
+      </c>
+      <c r="C144" t="s">
+        <v>423</v>
+      </c>
+      <c r="D144" t="s">
+        <v>597</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>294</v>
+      </c>
+      <c r="B145" t="s">
+        <v>598</v>
+      </c>
+      <c r="C145" t="s">
+        <v>509</v>
+      </c>
+      <c r="D145" t="s">
+        <v>599</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>294</v>
+      </c>
+      <c r="B146" t="s">
+        <v>600</v>
+      </c>
+      <c r="C146" t="s">
+        <v>509</v>
+      </c>
+      <c r="D146" t="s">
+        <v>601</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A147" t="s">
+        <v>294</v>
+      </c>
+      <c r="B147" t="s">
+        <v>602</v>
+      </c>
+      <c r="C147" t="s">
+        <v>509</v>
+      </c>
+      <c r="D147" t="s">
+        <v>603</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>294</v>
+      </c>
+      <c r="B148" t="s">
+        <v>604</v>
+      </c>
+      <c r="C148" t="s">
+        <v>303</v>
+      </c>
+      <c r="D148" t="s">
+        <v>605</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>294</v>
+      </c>
+      <c r="B149" t="s">
+        <v>606</v>
+      </c>
+      <c r="C149" t="s">
+        <v>303</v>
+      </c>
+      <c r="D149" t="s">
+        <v>607</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>294</v>
+      </c>
+      <c r="B150" t="s">
+        <v>608</v>
+      </c>
+      <c r="C150" t="s">
+        <v>303</v>
+      </c>
+      <c r="D150" t="s">
+        <v>609</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>294</v>
+      </c>
+      <c r="B151" t="s">
+        <v>610</v>
+      </c>
+      <c r="C151" t="s">
+        <v>303</v>
+      </c>
+      <c r="D151" t="s">
+        <v>611</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>294</v>
+      </c>
+      <c r="B152" t="s">
+        <v>612</v>
+      </c>
+      <c r="C152" t="s">
+        <v>303</v>
+      </c>
+      <c r="D152" t="s">
+        <v>613</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>294</v>
+      </c>
+      <c r="B153" t="s">
+        <v>614</v>
+      </c>
+      <c r="C153" t="s">
+        <v>303</v>
+      </c>
+      <c r="D153" t="s">
+        <v>615</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>294</v>
+      </c>
+      <c r="B154" t="s">
+        <v>616</v>
+      </c>
+      <c r="C154" t="s">
+        <v>296</v>
+      </c>
+      <c r="D154" t="s">
+        <v>617</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>294</v>
+      </c>
+      <c r="B155" t="s">
+        <v>618</v>
+      </c>
+      <c r="C155" t="s">
+        <v>303</v>
+      </c>
+      <c r="D155" t="s">
+        <v>619</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>294</v>
+      </c>
+      <c r="B156" t="s">
+        <v>620</v>
+      </c>
+      <c r="C156" t="s">
+        <v>303</v>
+      </c>
+      <c r="D156" t="s">
+        <v>621</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>294</v>
+      </c>
+      <c r="B157" t="s">
+        <v>622</v>
+      </c>
+      <c r="C157" t="s">
+        <v>303</v>
+      </c>
+      <c r="D157" t="s">
+        <v>623</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>294</v>
+      </c>
+      <c r="B158" t="s">
+        <v>624</v>
+      </c>
+      <c r="C158" t="s">
+        <v>303</v>
+      </c>
+      <c r="D158" t="s">
+        <v>625</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>294</v>
+      </c>
+      <c r="B159" t="s">
+        <v>626</v>
+      </c>
+      <c r="C159" t="s">
+        <v>296</v>
+      </c>
+      <c r="D159" t="s">
+        <v>627</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>315</v>
+      </c>
+      <c r="B160" t="s">
+        <v>628</v>
+      </c>
+      <c r="C160" t="s">
+        <v>303</v>
+      </c>
+      <c r="D160" t="s">
+        <v>629</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>294</v>
+      </c>
+      <c r="B161" t="s">
+        <v>631</v>
+      </c>
+      <c r="C161" t="s">
+        <v>303</v>
+      </c>
+      <c r="D161" t="s">
+        <v>632</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>294</v>
+      </c>
+      <c r="B162" t="s">
+        <v>633</v>
+      </c>
+      <c r="C162" t="s">
+        <v>303</v>
+      </c>
+      <c r="D162" t="s">
+        <v>634</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>294</v>
+      </c>
+      <c r="B163" t="s">
+        <v>635</v>
+      </c>
+      <c r="C163" t="s">
+        <v>296</v>
+      </c>
+      <c r="D163" t="s">
+        <v>636</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>294</v>
+      </c>
+      <c r="B164" t="s">
+        <v>637</v>
+      </c>
+      <c r="C164" t="s">
+        <v>296</v>
+      </c>
+      <c r="D164" t="s">
+        <v>638</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>294</v>
+      </c>
+      <c r="B165" t="s">
+        <v>639</v>
+      </c>
+      <c r="C165" t="s">
+        <v>296</v>
+      </c>
+      <c r="D165" t="s">
+        <v>640</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>294</v>
+      </c>
+      <c r="B166" t="s">
+        <v>641</v>
+      </c>
+      <c r="C166" t="s">
+        <v>296</v>
+      </c>
+      <c r="D166" t="s">
+        <v>642</v>
+      </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>294</v>
+      </c>
+      <c r="B167" t="s">
+        <v>643</v>
+      </c>
+      <c r="C167" t="s">
+        <v>296</v>
+      </c>
+      <c r="D167" t="s">
+        <v>644</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A168" t="s">
+        <v>294</v>
+      </c>
+      <c r="B168" t="s">
+        <v>645</v>
+      </c>
+      <c r="C168" t="s">
+        <v>296</v>
+      </c>
+      <c r="D168" t="s">
+        <v>646</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
+        <v>294</v>
+      </c>
+      <c r="B169" t="s">
+        <v>647</v>
+      </c>
+      <c r="C169" t="s">
+        <v>296</v>
+      </c>
+      <c r="D169" t="s">
+        <v>648</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>294</v>
+      </c>
+      <c r="B170" t="s">
+        <v>649</v>
+      </c>
+      <c r="C170" t="s">
+        <v>296</v>
+      </c>
+      <c r="D170" t="s">
+        <v>650</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>294</v>
+      </c>
+      <c r="B171" t="s">
+        <v>651</v>
+      </c>
+      <c r="C171" t="s">
+        <v>296</v>
+      </c>
+      <c r="D171" t="s">
+        <v>652</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>315</v>
+      </c>
+      <c r="B172" t="s">
+        <v>653</v>
+      </c>
+      <c r="C172" t="s">
+        <v>320</v>
+      </c>
+      <c r="D172" t="s">
+        <v>654</v>
+      </c>
+      <c r="E172" t="s">
+        <v>318</v>
+      </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="I172" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A173" t="s">
+        <v>315</v>
+      </c>
+      <c r="B173" t="s">
+        <v>655</v>
+      </c>
+      <c r="C173" t="s">
+        <v>320</v>
+      </c>
+      <c r="D173" t="s">
+        <v>656</v>
+      </c>
+      <c r="E173" t="s">
+        <v>318</v>
+      </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>1</v>
+      </c>
+      <c r="I173" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A174" t="s">
+        <v>315</v>
+      </c>
+      <c r="B174" t="s">
+        <v>657</v>
+      </c>
+      <c r="C174" t="s">
+        <v>320</v>
+      </c>
+      <c r="D174" t="s">
+        <v>658</v>
+      </c>
+      <c r="E174" t="s">
+        <v>318</v>
+      </c>
+      <c r="F174">
+        <v>0</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>1</v>
+      </c>
+      <c r="I174" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
+        <v>315</v>
+      </c>
+      <c r="B175" t="s">
+        <v>659</v>
+      </c>
+      <c r="C175" t="s">
+        <v>320</v>
+      </c>
+      <c r="D175" t="s">
+        <v>660</v>
+      </c>
+      <c r="E175" t="s">
+        <v>318</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>1</v>
+      </c>
+      <c r="I175" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
+        <v>315</v>
+      </c>
+      <c r="B176" t="s">
+        <v>661</v>
+      </c>
+      <c r="C176" t="s">
+        <v>320</v>
+      </c>
+      <c r="D176" t="s">
+        <v>662</v>
+      </c>
+      <c r="E176" t="s">
+        <v>318</v>
+      </c>
+      <c r="F176">
+        <v>0</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+      <c r="I176" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
+        <v>315</v>
+      </c>
+      <c r="B177" t="s">
+        <v>663</v>
+      </c>
+      <c r="C177" t="s">
+        <v>320</v>
+      </c>
+      <c r="D177" t="s">
+        <v>664</v>
+      </c>
+      <c r="E177" t="s">
+        <v>318</v>
+      </c>
+      <c r="F177">
+        <v>0</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>1</v>
+      </c>
+      <c r="I177" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A178" t="s">
+        <v>315</v>
+      </c>
+      <c r="B178" t="s">
+        <v>665</v>
+      </c>
+      <c r="C178" t="s">
+        <v>320</v>
+      </c>
+      <c r="D178" t="s">
+        <v>666</v>
+      </c>
+      <c r="E178" t="s">
+        <v>318</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+      <c r="I178" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A179" t="s">
+        <v>315</v>
+      </c>
+      <c r="B179" t="s">
+        <v>667</v>
+      </c>
+      <c r="C179" t="s">
+        <v>320</v>
+      </c>
+      <c r="D179" t="s">
+        <v>668</v>
+      </c>
+      <c r="E179" t="s">
+        <v>318</v>
+      </c>
+      <c r="F179">
+        <v>0</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+      <c r="I179" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A180" t="s">
+        <v>315</v>
+      </c>
+      <c r="B180" t="s">
+        <v>669</v>
+      </c>
+      <c r="C180" t="s">
+        <v>296</v>
+      </c>
+      <c r="D180" t="s">
+        <v>670</v>
+      </c>
+      <c r="E180" t="s">
+        <v>318</v>
+      </c>
+      <c r="F180">
+        <v>0</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>1</v>
+      </c>
+      <c r="I180" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>315</v>
+      </c>
+      <c r="B181" t="s">
+        <v>671</v>
+      </c>
+      <c r="C181" t="s">
+        <v>296</v>
+      </c>
+      <c r="D181" t="s">
+        <v>672</v>
+      </c>
+      <c r="E181" t="s">
+        <v>318</v>
+      </c>
+      <c r="F181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>1</v>
+      </c>
+      <c r="I181" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A182" t="s">
+        <v>315</v>
+      </c>
+      <c r="B182" t="s">
+        <v>351</v>
+      </c>
+      <c r="C182" t="s">
+        <v>296</v>
+      </c>
+      <c r="D182" t="s">
+        <v>352</v>
+      </c>
+      <c r="E182" t="s">
+        <v>318</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>1</v>
+      </c>
+      <c r="I182" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>315</v>
+      </c>
+      <c r="B183" t="s">
+        <v>673</v>
+      </c>
+      <c r="C183" t="s">
+        <v>296</v>
+      </c>
+      <c r="D183" t="s">
+        <v>674</v>
+      </c>
+      <c r="E183" t="s">
+        <v>318</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>1</v>
+      </c>
+      <c r="I183" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>315</v>
+      </c>
+      <c r="B184" t="s">
+        <v>675</v>
+      </c>
+      <c r="C184" t="s">
+        <v>296</v>
+      </c>
+      <c r="D184" t="s">
+        <v>676</v>
+      </c>
+      <c r="E184" t="s">
+        <v>318</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>1</v>
+      </c>
+      <c r="I184" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A185" t="s">
+        <v>315</v>
+      </c>
+      <c r="B185" t="s">
+        <v>677</v>
+      </c>
+      <c r="C185" t="s">
+        <v>296</v>
+      </c>
+      <c r="D185" t="s">
+        <v>678</v>
+      </c>
+      <c r="E185" t="s">
+        <v>318</v>
+      </c>
+      <c r="F185">
+        <v>0</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>1</v>
+      </c>
+      <c r="I185" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A186" t="s">
+        <v>315</v>
+      </c>
+      <c r="B186" t="s">
+        <v>353</v>
+      </c>
+      <c r="C186" t="s">
+        <v>296</v>
+      </c>
+      <c r="D186" t="s">
+        <v>354</v>
+      </c>
+      <c r="E186" t="s">
+        <v>318</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A187" t="s">
+        <v>315</v>
+      </c>
+      <c r="B187" t="s">
+        <v>679</v>
+      </c>
+      <c r="C187" t="s">
+        <v>296</v>
+      </c>
+      <c r="D187" t="s">
+        <v>680</v>
+      </c>
+      <c r="E187" t="s">
+        <v>318</v>
+      </c>
+      <c r="F187">
+        <v>0</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+      <c r="I187" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A188" t="s">
+        <v>315</v>
+      </c>
+      <c r="B188" t="s">
+        <v>681</v>
+      </c>
+      <c r="C188" t="s">
+        <v>296</v>
+      </c>
+      <c r="D188" t="s">
+        <v>682</v>
+      </c>
+      <c r="E188" t="s">
+        <v>318</v>
+      </c>
+      <c r="F188">
+        <v>0</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
+      <c r="I188" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A189" t="s">
+        <v>315</v>
+      </c>
+      <c r="B189" t="s">
+        <v>683</v>
+      </c>
+      <c r="C189" t="s">
+        <v>296</v>
+      </c>
+      <c r="D189" t="s">
+        <v>684</v>
+      </c>
+      <c r="E189" t="s">
+        <v>318</v>
+      </c>
+      <c r="F189">
+        <v>0</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>1</v>
+      </c>
+      <c r="I189" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A190" t="s">
+        <v>315</v>
+      </c>
+      <c r="B190" t="s">
+        <v>685</v>
+      </c>
+      <c r="C190" t="s">
+        <v>296</v>
+      </c>
+      <c r="D190" t="s">
+        <v>686</v>
+      </c>
+      <c r="E190" t="s">
+        <v>318</v>
+      </c>
+      <c r="F190">
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>1</v>
+      </c>
+      <c r="I190" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A191" t="s">
+        <v>315</v>
+      </c>
+      <c r="B191" t="s">
+        <v>687</v>
+      </c>
+      <c r="C191" t="s">
+        <v>296</v>
+      </c>
+      <c r="D191" t="s">
+        <v>688</v>
+      </c>
+      <c r="E191" t="s">
+        <v>318</v>
+      </c>
+      <c r="F191">
+        <v>0</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>1</v>
+      </c>
+      <c r="I191" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A192" t="s">
+        <v>315</v>
+      </c>
+      <c r="B192" t="s">
+        <v>689</v>
+      </c>
+      <c r="C192" t="s">
+        <v>690</v>
+      </c>
+      <c r="D192" t="s">
+        <v>691</v>
+      </c>
+      <c r="E192" t="s">
+        <v>318</v>
+      </c>
+      <c r="F192">
+        <v>0</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A193" t="s">
+        <v>315</v>
+      </c>
+      <c r="B193" t="s">
+        <v>692</v>
+      </c>
+      <c r="C193" t="s">
+        <v>690</v>
+      </c>
+      <c r="D193" t="s">
+        <v>693</v>
+      </c>
+      <c r="E193" t="s">
+        <v>318</v>
+      </c>
+      <c r="F193">
+        <v>0</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A194" t="s">
+        <v>315</v>
+      </c>
+      <c r="B194" t="s">
+        <v>694</v>
+      </c>
+      <c r="C194" t="s">
+        <v>690</v>
+      </c>
+      <c r="D194" t="s">
+        <v>695</v>
+      </c>
+      <c r="E194" t="s">
+        <v>318</v>
+      </c>
+      <c r="F194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A195" t="s">
+        <v>315</v>
+      </c>
+      <c r="B195" t="s">
+        <v>697</v>
+      </c>
+      <c r="C195" t="s">
+        <v>690</v>
+      </c>
+      <c r="D195" t="s">
+        <v>698</v>
+      </c>
+      <c r="E195" t="s">
+        <v>318</v>
+      </c>
+      <c r="F195">
+        <v>0</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A196" t="s">
+        <v>315</v>
+      </c>
+      <c r="B196" t="s">
+        <v>699</v>
+      </c>
+      <c r="C196" t="s">
+        <v>690</v>
+      </c>
+      <c r="D196" t="s">
+        <v>700</v>
+      </c>
+      <c r="E196" t="s">
+        <v>318</v>
+      </c>
+      <c r="F196">
+        <v>0</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A197" t="s">
+        <v>315</v>
+      </c>
+      <c r="B197" t="s">
+        <v>701</v>
+      </c>
+      <c r="C197" t="s">
+        <v>690</v>
+      </c>
+      <c r="D197" t="s">
+        <v>702</v>
+      </c>
+      <c r="E197" t="s">
+        <v>318</v>
+      </c>
+      <c r="F197">
+        <v>0</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A198" t="s">
+        <v>315</v>
+      </c>
+      <c r="B198" t="s">
+        <v>703</v>
+      </c>
+      <c r="C198" t="s">
+        <v>690</v>
+      </c>
+      <c r="D198" t="s">
+        <v>704</v>
+      </c>
+      <c r="E198" t="s">
+        <v>318</v>
+      </c>
+      <c r="F198">
+        <v>0</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A199" t="s">
+        <v>315</v>
+      </c>
+      <c r="B199" t="s">
+        <v>705</v>
+      </c>
+      <c r="C199" t="s">
+        <v>690</v>
+      </c>
+      <c r="D199" t="s">
+        <v>706</v>
+      </c>
+      <c r="E199" t="s">
+        <v>318</v>
+      </c>
+      <c r="F199">
+        <v>0</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A200" t="s">
+        <v>315</v>
+      </c>
+      <c r="B200" t="s">
+        <v>707</v>
+      </c>
+      <c r="C200" t="s">
+        <v>296</v>
+      </c>
+      <c r="D200" t="s">
+        <v>708</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A201" t="s">
+        <v>294</v>
+      </c>
+      <c r="B201" t="s">
+        <v>709</v>
+      </c>
+      <c r="C201" t="s">
+        <v>303</v>
+      </c>
+      <c r="D201" t="s">
+        <v>710</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A202" t="s">
+        <v>315</v>
+      </c>
+      <c r="B202" t="s">
+        <v>711</v>
+      </c>
+      <c r="C202" t="s">
+        <v>296</v>
+      </c>
+      <c r="D202" t="s">
+        <v>712</v>
+      </c>
+      <c r="F202">
+        <v>0</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A203" t="s">
+        <v>315</v>
+      </c>
+      <c r="B203" t="s">
+        <v>713</v>
+      </c>
+      <c r="C203" t="s">
+        <v>296</v>
+      </c>
+      <c r="D203" t="s">
+        <v>714</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>315</v>
+      </c>
+      <c r="B204" t="s">
+        <v>715</v>
+      </c>
+      <c r="C204" t="s">
+        <v>296</v>
+      </c>
+      <c r="D204" t="s">
+        <v>716</v>
+      </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A205" t="s">
+        <v>315</v>
+      </c>
+      <c r="B205" t="s">
+        <v>717</v>
+      </c>
+      <c r="C205" t="s">
+        <v>296</v>
+      </c>
+      <c r="D205" t="s">
+        <v>718</v>
+      </c>
+      <c r="F205">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A206" t="s">
+        <v>315</v>
+      </c>
+      <c r="B206" t="s">
+        <v>719</v>
+      </c>
+      <c r="C206" t="s">
+        <v>296</v>
+      </c>
+      <c r="D206" t="s">
+        <v>720</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A207" t="s">
+        <v>315</v>
+      </c>
+      <c r="B207" t="s">
+        <v>721</v>
+      </c>
+      <c r="C207" t="s">
+        <v>296</v>
+      </c>
+      <c r="D207" t="s">
+        <v>722</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A208" t="s">
+        <v>315</v>
+      </c>
+      <c r="B208" t="s">
+        <v>723</v>
+      </c>
+      <c r="C208" t="s">
+        <v>296</v>
+      </c>
+      <c r="D208" t="s">
+        <v>724</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A209" t="s">
+        <v>315</v>
+      </c>
+      <c r="B209" t="s">
+        <v>725</v>
+      </c>
+      <c r="C209" t="s">
+        <v>296</v>
+      </c>
+      <c r="D209" t="s">
+        <v>726</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
+        <v>315</v>
+      </c>
+      <c r="B210" t="s">
+        <v>727</v>
+      </c>
+      <c r="C210" t="s">
+        <v>296</v>
+      </c>
+      <c r="D210" t="s">
+        <v>728</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
+        <v>315</v>
+      </c>
+      <c r="B211" t="s">
+        <v>729</v>
+      </c>
+      <c r="C211" t="s">
+        <v>296</v>
+      </c>
+      <c r="D211" t="s">
+        <v>730</v>
+      </c>
+      <c r="F211">
+        <v>0</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
+        <v>315</v>
+      </c>
+      <c r="B212" t="s">
+        <v>731</v>
+      </c>
+      <c r="C212" t="s">
+        <v>296</v>
+      </c>
+      <c r="D212" t="s">
+        <v>732</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A213" t="s">
+        <v>315</v>
+      </c>
+      <c r="B213" t="s">
+        <v>733</v>
+      </c>
+      <c r="C213" t="s">
+        <v>296</v>
+      </c>
+      <c r="D213" t="s">
+        <v>734</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>315</v>
+      </c>
+      <c r="B214" t="s">
+        <v>735</v>
+      </c>
+      <c r="C214" t="s">
+        <v>296</v>
+      </c>
+      <c r="D214" t="s">
+        <v>736</v>
+      </c>
+      <c r="F214">
+        <v>0</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
+        <v>315</v>
+      </c>
+      <c r="B215" t="s">
+        <v>737</v>
+      </c>
+      <c r="C215" t="s">
+        <v>509</v>
+      </c>
+      <c r="D215" t="s">
+        <v>738</v>
+      </c>
+      <c r="F215">
+        <v>0</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A216" t="s">
+        <v>315</v>
+      </c>
+      <c r="B216" t="s">
+        <v>355</v>
+      </c>
+      <c r="C216" t="s">
+        <v>296</v>
+      </c>
+      <c r="D216" t="s">
+        <v>356</v>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A217" t="s">
+        <v>315</v>
+      </c>
+      <c r="B217" t="s">
+        <v>739</v>
+      </c>
+      <c r="C217" t="s">
+        <v>740</v>
+      </c>
+      <c r="D217" t="s">
+        <v>741</v>
+      </c>
+      <c r="F217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
+        <v>315</v>
+      </c>
+      <c r="B218" t="s">
+        <v>742</v>
+      </c>
+      <c r="C218" t="s">
+        <v>296</v>
+      </c>
+      <c r="D218" t="s">
+        <v>743</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+      <c r="G218">
+        <v>0</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A219" t="s">
+        <v>315</v>
+      </c>
+      <c r="B219" t="s">
+        <v>744</v>
+      </c>
+      <c r="C219" t="s">
+        <v>296</v>
+      </c>
+      <c r="D219" t="s">
+        <v>745</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
+        <v>315</v>
+      </c>
+      <c r="B220" t="s">
+        <v>746</v>
+      </c>
+      <c r="C220" t="s">
+        <v>296</v>
+      </c>
+      <c r="D220" t="s">
+        <v>747</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A221" t="s">
+        <v>315</v>
+      </c>
+      <c r="B221" t="s">
+        <v>369</v>
+      </c>
+      <c r="C221" t="s">
+        <v>296</v>
+      </c>
+      <c r="D221" t="s">
+        <v>370</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
+        <v>315</v>
+      </c>
+      <c r="B222" t="s">
+        <v>372</v>
+      </c>
+      <c r="C222" t="s">
+        <v>296</v>
+      </c>
+      <c r="D222" t="s">
+        <v>373</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>294</v>
+      </c>
+      <c r="B223" t="s">
+        <v>748</v>
+      </c>
+      <c r="C223" t="s">
+        <v>303</v>
+      </c>
+      <c r="D223" t="s">
+        <v>749</v>
+      </c>
+      <c r="F223">
+        <v>0</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A224" t="s">
+        <v>294</v>
+      </c>
+      <c r="B224" t="s">
+        <v>750</v>
+      </c>
+      <c r="C224" t="s">
+        <v>303</v>
+      </c>
+      <c r="D224" t="s">
+        <v>751</v>
+      </c>
+      <c r="F224">
+        <v>0</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A225" t="s">
+        <v>294</v>
+      </c>
+      <c r="B225" t="s">
+        <v>752</v>
+      </c>
+      <c r="C225" t="s">
+        <v>303</v>
+      </c>
+      <c r="D225" t="s">
+        <v>753</v>
+      </c>
+      <c r="F225">
+        <v>0</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A226" t="s">
+        <v>294</v>
+      </c>
+      <c r="B226" t="s">
+        <v>754</v>
+      </c>
+      <c r="C226" t="s">
+        <v>303</v>
+      </c>
+      <c r="D226" t="s">
+        <v>755</v>
+      </c>
+      <c r="F226">
+        <v>0</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A227" t="s">
+        <v>294</v>
+      </c>
+      <c r="B227" t="s">
+        <v>756</v>
+      </c>
+      <c r="C227" t="s">
+        <v>303</v>
+      </c>
+      <c r="D227" t="s">
+        <v>757</v>
+      </c>
+      <c r="F227">
+        <v>0</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A228" t="s">
+        <v>294</v>
+      </c>
+      <c r="B228" t="s">
+        <v>758</v>
+      </c>
+      <c r="C228" t="s">
+        <v>303</v>
+      </c>
+      <c r="D228" t="s">
+        <v>759</v>
+      </c>
+      <c r="F228">
+        <v>0</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A229" t="s">
+        <v>315</v>
+      </c>
+      <c r="B229" t="s">
+        <v>760</v>
+      </c>
+      <c r="C229" t="s">
+        <v>320</v>
+      </c>
+      <c r="D229" t="s">
+        <v>761</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229" t="s">
+        <v>760</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11407588-E088-4B98-BB26-FD952B01C3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCB0FF5-7CD0-44EA-98D0-BD7564EE9E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28905" yWindow="1620" windowWidth="19845" windowHeight="11910" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="33390" yWindow="1215" windowWidth="19845" windowHeight="11910" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="983">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -2757,28 +2757,6 @@
     <t>D00905</t>
   </si>
   <si>
-    <t>D00910</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D00911</t>
-  </si>
-  <si>
-    <t>D00912</t>
-  </si>
-  <si>
-    <t>D00913</t>
-  </si>
-  <si>
-    <t>D00914</t>
-  </si>
-  <si>
-    <t>D00915</t>
-  </si>
-  <si>
-    <t>D00916</t>
-  </si>
-  <si>
     <t>변압기 별 선풍기 기동온도 및 정지온도를 변경하변 그때마다 PC에서 PLC로 전송하여 업데이트함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2984,16 +2962,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>D00920</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D00921</t>
-  </si>
-  <si>
-    <t>D00922</t>
-  </si>
-  <si>
     <t>* 변압기 3상의 온도가 달라서 낮은 상의 온도와 높은 상의 온도차가 3네지 5도가 나서 선풍기 제어가 잘 안되어서 최고값을 기준으로 선풍기 운영 예정임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3012,13 +2980,93 @@
   <si>
     <t>오류 신호가 들어오면 오류내용을 오류목록에 기록하고 알람창에 오류 내용 띄움, M215는 M115 에러 크리어 신호와 연계 함</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_010_W_TR3_temp_high_set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_010_W_TR3_temp_low_set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아날로그입력 모듈: 모듈 에러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>온도입력모듈 : 모듈 에러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>온도입력모듈 : 채널0 단선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF_local_manual_selection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF_local_manual_selection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M00116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M00117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00906</t>
+  </si>
+  <si>
+    <t>D00907</t>
+  </si>
+  <si>
+    <t>D00908</t>
+  </si>
+  <si>
+    <t>D00909</t>
+  </si>
+  <si>
+    <t>D00950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00951</t>
+  </si>
+  <si>
+    <t>D00952</t>
+  </si>
+  <si>
+    <t>D00953</t>
+  </si>
+  <si>
+    <t>D00954</t>
+  </si>
+  <si>
+    <t>D00955</t>
+  </si>
+  <si>
+    <t>D00956</t>
+  </si>
+  <si>
+    <t>D00980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00981</t>
+  </si>
+  <si>
+    <t>D00982</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3060,13 +3108,35 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3083,7 +3153,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3104,6 +3174,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6651,7 +6739,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2836F51-32CE-4EC5-A2A6-D682AE17D0BB}">
-  <dimension ref="A1:M243"/>
+  <dimension ref="A1:M251"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -6675,25 +6763,25 @@
         <v>290</v>
       </c>
       <c r="D1" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="E1" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="F1" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="J1" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="K1" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="L1" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -6724,17 +6812,17 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="K2" t="s">
-        <v>927</v>
-      </c>
-      <c r="L2" t="s">
-        <v>902</v>
+      <c r="K2" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>895</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -6765,14 +6853,14 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="K3" t="s">
-        <v>927</v>
-      </c>
-      <c r="L3" t="s">
-        <v>903</v>
+      <c r="K3" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>896</v>
       </c>
       <c r="M3" s="6"/>
     </row>
@@ -6781,7 +6869,7 @@
         <v>862</v>
       </c>
       <c r="C4" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="D4" t="s">
         <v>303</v>
@@ -6789,14 +6877,14 @@
       <c r="E4" t="s">
         <v>767</v>
       </c>
-      <c r="J4" t="s">
-        <v>928</v>
-      </c>
-      <c r="K4" t="s">
-        <v>927</v>
-      </c>
-      <c r="L4" t="s">
-        <v>904</v>
+      <c r="J4" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>897</v>
       </c>
       <c r="M4" s="6"/>
     </row>
@@ -6805,7 +6893,7 @@
         <v>863</v>
       </c>
       <c r="C5" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="D5" t="s">
         <v>303</v>
@@ -6813,14 +6901,14 @@
       <c r="E5" t="s">
         <v>400</v>
       </c>
-      <c r="J5" t="s">
-        <v>929</v>
-      </c>
-      <c r="K5" t="s">
-        <v>927</v>
-      </c>
-      <c r="L5" t="s">
-        <v>905</v>
+      <c r="J5" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>898</v>
       </c>
       <c r="M5" s="6"/>
     </row>
@@ -6828,23 +6916,27 @@
       <c r="A6" t="s">
         <v>864</v>
       </c>
-      <c r="C6" t="s">
-        <v>930</v>
-      </c>
-      <c r="D6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C6" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="J6" t="s">
-        <v>930</v>
-      </c>
-      <c r="K6" t="s">
-        <v>927</v>
-      </c>
-      <c r="L6" t="s">
-        <v>906</v>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>920</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>899</v>
       </c>
       <c r="M6" s="6"/>
     </row>
@@ -6873,14 +6965,14 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="K7" t="s">
-        <v>918</v>
-      </c>
-      <c r="L7" t="s">
-        <v>907</v>
+      <c r="K7" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>900</v>
       </c>
       <c r="M7" s="6"/>
     </row>
@@ -6891,8 +6983,8 @@
       <c r="B8" t="s">
         <v>294</v>
       </c>
-      <c r="C8" t="s">
-        <v>446</v>
+      <c r="C8" s="4" t="s">
+        <v>965</v>
       </c>
       <c r="D8" t="s">
         <v>303</v>
@@ -6909,68 +7001,66 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="K8" t="s">
-        <v>918</v>
-      </c>
-      <c r="L8" t="s">
-        <v>908</v>
+      <c r="K8" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>901</v>
       </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>842</v>
-      </c>
       <c r="B9" t="s">
         <v>294</v>
       </c>
-      <c r="C9" t="s">
-        <v>454</v>
-      </c>
-      <c r="D9" t="s">
-        <v>303</v>
-      </c>
-      <c r="E9" t="s">
-        <v>455</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>454</v>
-      </c>
-      <c r="K9" t="s">
-        <v>918</v>
-      </c>
-      <c r="L9" t="s">
-        <v>909</v>
+      <c r="C9" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>967</v>
       </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B10" t="s">
         <v>294</v>
       </c>
       <c r="C10" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D10" t="s">
         <v>303</v>
       </c>
       <c r="E10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -6981,32 +7071,32 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" t="s">
-        <v>458</v>
-      </c>
-      <c r="K10" t="s">
-        <v>918</v>
-      </c>
-      <c r="L10" t="s">
-        <v>910</v>
+      <c r="J10" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>902</v>
       </c>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B11" t="s">
         <v>294</v>
       </c>
       <c r="C11" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D11" t="s">
         <v>303</v>
       </c>
       <c r="E11" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -7017,32 +7107,32 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" t="s">
-        <v>466</v>
-      </c>
-      <c r="K11" t="s">
-        <v>918</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="J11" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>911</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>903</v>
       </c>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B12" t="s">
         <v>294</v>
       </c>
       <c r="C12" t="s">
-        <v>547</v>
+        <v>466</v>
       </c>
       <c r="D12" t="s">
         <v>303</v>
       </c>
       <c r="E12" t="s">
-        <v>548</v>
+        <v>467</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -7053,32 +7143,32 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" t="s">
-        <v>547</v>
-      </c>
-      <c r="K12" t="s">
-        <v>918</v>
-      </c>
-      <c r="L12" t="s">
-        <v>912</v>
+      <c r="J12" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>904</v>
       </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B13" t="s">
         <v>294</v>
       </c>
       <c r="C13" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D13" t="s">
         <v>303</v>
       </c>
       <c r="E13" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -7089,32 +7179,32 @@
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" t="s">
-        <v>553</v>
-      </c>
-      <c r="K13" t="s">
-        <v>918</v>
-      </c>
-      <c r="L13" t="s">
-        <v>913</v>
+      <c r="J13" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>905</v>
       </c>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B14" t="s">
         <v>294</v>
       </c>
-      <c r="C14" t="s">
-        <v>561</v>
+      <c r="C14" s="4" t="s">
+        <v>966</v>
       </c>
       <c r="D14" t="s">
         <v>303</v>
       </c>
       <c r="E14" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -7125,71 +7215,66 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" t="s">
-        <v>561</v>
-      </c>
-      <c r="K14" t="s">
-        <v>918</v>
-      </c>
-      <c r="L14" t="s">
-        <v>914</v>
+      <c r="J14" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>906</v>
       </c>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>854</v>
-      </c>
       <c r="B15" t="s">
         <v>294</v>
       </c>
-      <c r="C15" t="s">
-        <v>565</v>
-      </c>
-      <c r="D15" t="s">
-        <v>303</v>
-      </c>
-      <c r="E15" t="s">
-        <v>566</v>
-      </c>
-      <c r="F15" t="s">
-        <v>318</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>565</v>
-      </c>
-      <c r="K15" t="s">
-        <v>918</v>
-      </c>
-      <c r="L15" t="s">
-        <v>915</v>
+      <c r="C15" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>968</v>
       </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B16" t="s">
         <v>294</v>
       </c>
       <c r="C16" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D16" t="s">
         <v>303</v>
       </c>
       <c r="E16" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -7200,35 +7285,38 @@
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" t="s">
-        <v>573</v>
-      </c>
-      <c r="K16" t="s">
-        <v>918</v>
-      </c>
-      <c r="L16" t="s">
-        <v>916</v>
+      <c r="J16" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>907</v>
       </c>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="1:13" ht="87" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>887</v>
+        <v>854</v>
       </c>
       <c r="B17" t="s">
-        <v>771</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
-        <v>832</v>
+        <v>565</v>
       </c>
       <c r="D17" t="s">
         <v>303</v>
       </c>
       <c r="E17" t="s">
-        <v>833</v>
+        <v>566</v>
+      </c>
+      <c r="F17" t="s">
+        <v>318</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -7236,37 +7324,32 @@
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" t="s">
-        <v>834</v>
-      </c>
-      <c r="K17" t="s">
-        <v>918</v>
-      </c>
-      <c r="L17" t="s">
-        <v>917</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>967</v>
-      </c>
+      <c r="J17" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="B18" t="s">
         <v>294</v>
       </c>
       <c r="C18" t="s">
-        <v>442</v>
+        <v>573</v>
       </c>
       <c r="D18" t="s">
         <v>303</v>
       </c>
       <c r="E18" t="s">
-        <v>443</v>
-      </c>
-      <c r="F18" t="s">
-        <v>318</v>
+        <v>574</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -7277,37 +7360,35 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" t="s">
-        <v>442</v>
-      </c>
-      <c r="K18" t="s">
-        <v>919</v>
-      </c>
-      <c r="L18" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J18" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="M18" s="6"/>
+    </row>
+    <row r="19" spans="1:13" ht="87" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>841</v>
+        <v>887</v>
       </c>
       <c r="B19" t="s">
-        <v>294</v>
+        <v>771</v>
       </c>
       <c r="C19" t="s">
-        <v>448</v>
+        <v>832</v>
       </c>
       <c r="D19" t="s">
         <v>303</v>
       </c>
       <c r="E19" t="s">
-        <v>449</v>
-      </c>
-      <c r="F19" t="s">
-        <v>318</v>
+        <v>833</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -7315,95 +7396,47 @@
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" t="s">
-        <v>448</v>
-      </c>
-      <c r="K19" t="s">
-        <v>919</v>
-      </c>
-      <c r="L19" t="s">
-        <v>937</v>
+      <c r="J19" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>957</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>843</v>
-      </c>
-      <c r="B20" t="s">
-        <v>294</v>
-      </c>
-      <c r="C20" t="s">
-        <v>456</v>
-      </c>
-      <c r="D20" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" t="s">
-        <v>457</v>
-      </c>
-      <c r="F20" t="s">
-        <v>318</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>456</v>
-      </c>
-      <c r="K20" t="s">
-        <v>919</v>
-      </c>
-      <c r="L20" t="s">
-        <v>938</v>
-      </c>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>859</v>
-      </c>
-      <c r="C21" t="s">
-        <v>765</v>
-      </c>
-      <c r="D21" t="s">
-        <v>303</v>
-      </c>
-      <c r="E21" t="s">
-        <v>764</v>
-      </c>
-      <c r="J21" t="s">
-        <v>765</v>
-      </c>
-      <c r="K21" t="s">
-        <v>919</v>
-      </c>
-      <c r="L21" t="s">
-        <v>939</v>
-      </c>
-      <c r="M21" t="s">
-        <v>933</v>
-      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="B22" t="s">
         <v>294</v>
       </c>
       <c r="C22" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="D22" t="s">
         <v>303</v>
       </c>
       <c r="E22" t="s">
-        <v>461</v>
+        <v>443</v>
+      </c>
+      <c r="F22" t="s">
+        <v>318</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -7414,32 +7447,34 @@
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" t="s">
-        <v>460</v>
-      </c>
-      <c r="K22" t="s">
-        <v>919</v>
-      </c>
-      <c r="L22" t="s">
-        <v>940</v>
-      </c>
-      <c r="M22"/>
+      <c r="J22" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B23" t="s">
         <v>294</v>
       </c>
       <c r="C23" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="D23" t="s">
         <v>303</v>
       </c>
       <c r="E23" t="s">
-        <v>465</v>
+        <v>449</v>
+      </c>
+      <c r="F23" t="s">
+        <v>318</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -7450,32 +7485,31 @@
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23" t="s">
-        <v>464</v>
-      </c>
-      <c r="K23" t="s">
-        <v>919</v>
-      </c>
-      <c r="L23" t="s">
-        <v>941</v>
-      </c>
-      <c r="M23"/>
+      <c r="J23" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="B24" t="s">
         <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>549</v>
+        <v>456</v>
       </c>
       <c r="D24" t="s">
         <v>303</v>
       </c>
       <c r="E24" t="s">
-        <v>550</v>
+        <v>457</v>
       </c>
       <c r="F24" t="s">
         <v>318</v>
@@ -7489,74 +7523,57 @@
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" t="s">
-        <v>549</v>
-      </c>
-      <c r="K24" t="s">
-        <v>919</v>
-      </c>
-      <c r="L24" t="s">
-        <v>942</v>
-      </c>
-      <c r="M24"/>
+      <c r="J24" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>851</v>
-      </c>
-      <c r="B25" t="s">
-        <v>294</v>
+        <v>859</v>
       </c>
       <c r="C25" t="s">
-        <v>555</v>
+        <v>765</v>
       </c>
       <c r="D25" t="s">
         <v>303</v>
       </c>
       <c r="E25" t="s">
-        <v>556</v>
-      </c>
-      <c r="F25" t="s">
-        <v>318</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>555</v>
-      </c>
-      <c r="K25" t="s">
-        <v>919</v>
-      </c>
-      <c r="L25" t="s">
-        <v>943</v>
-      </c>
-      <c r="M25"/>
+        <v>764</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>932</v>
+      </c>
+      <c r="M25" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="B26" t="s">
         <v>294</v>
       </c>
       <c r="C26" t="s">
-        <v>563</v>
+        <v>460</v>
       </c>
       <c r="D26" t="s">
         <v>303</v>
       </c>
       <c r="E26" t="s">
-        <v>564</v>
-      </c>
-      <c r="F26" t="s">
-        <v>318</v>
+        <v>461</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -7567,58 +7584,71 @@
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" t="s">
-        <v>563</v>
-      </c>
-      <c r="K26" t="s">
-        <v>919</v>
-      </c>
-      <c r="L26" t="s">
-        <v>944</v>
+      <c r="J26" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>933</v>
       </c>
       <c r="M26"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>858</v>
+        <v>846</v>
+      </c>
+      <c r="B27" t="s">
+        <v>294</v>
       </c>
       <c r="C27" t="s">
-        <v>763</v>
+        <v>464</v>
       </c>
       <c r="D27" t="s">
         <v>303</v>
       </c>
       <c r="E27" t="s">
-        <v>762</v>
-      </c>
-      <c r="J27" t="s">
-        <v>763</v>
-      </c>
-      <c r="K27" t="s">
-        <v>919</v>
-      </c>
-      <c r="L27" t="s">
-        <v>945</v>
-      </c>
-      <c r="M27" t="s">
-        <v>932</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="M27"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B28" t="s">
         <v>294</v>
       </c>
       <c r="C28" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="D28" t="s">
         <v>303</v>
       </c>
       <c r="E28" t="s">
-        <v>568</v>
+        <v>550</v>
+      </c>
+      <c r="F28" t="s">
+        <v>318</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -7629,32 +7659,35 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" t="s">
-        <v>567</v>
-      </c>
-      <c r="K28" t="s">
-        <v>919</v>
-      </c>
-      <c r="L28" t="s">
-        <v>946</v>
+      <c r="J28" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>935</v>
       </c>
       <c r="M28"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="B29" t="s">
         <v>294</v>
       </c>
       <c r="C29" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="D29" t="s">
         <v>303</v>
       </c>
       <c r="E29" t="s">
-        <v>572</v>
+        <v>556</v>
+      </c>
+      <c r="F29" t="s">
+        <v>318</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -7665,113 +7698,136 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" t="s">
-        <v>571</v>
-      </c>
-      <c r="K29" t="s">
-        <v>919</v>
-      </c>
-      <c r="L29" t="s">
-        <v>947</v>
+      <c r="J29" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>936</v>
       </c>
       <c r="M29"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>865</v>
+        <v>853</v>
+      </c>
+      <c r="B30" t="s">
+        <v>294</v>
       </c>
       <c r="C30" t="s">
-        <v>769</v>
+        <v>563</v>
       </c>
       <c r="D30" t="s">
         <v>303</v>
       </c>
       <c r="E30" t="s">
-        <v>768</v>
-      </c>
-      <c r="J30" t="s">
-        <v>769</v>
-      </c>
-      <c r="K30" t="s">
-        <v>919</v>
-      </c>
-      <c r="L30" t="s">
-        <v>948</v>
-      </c>
-      <c r="M30" t="s">
-        <v>931</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="F30" t="s">
+        <v>318</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>937</v>
+      </c>
+      <c r="M30"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C31" t="s">
-        <v>396</v>
+        <v>763</v>
       </c>
       <c r="D31" t="s">
         <v>303</v>
       </c>
       <c r="E31" t="s">
-        <v>394</v>
-      </c>
-      <c r="J31" t="s">
-        <v>396</v>
-      </c>
-      <c r="K31" t="s">
-        <v>919</v>
-      </c>
-      <c r="L31" t="s">
-        <v>949</v>
+        <v>762</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>938</v>
       </c>
       <c r="M31" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>867</v>
+        <v>855</v>
+      </c>
+      <c r="B32" t="s">
+        <v>294</v>
       </c>
       <c r="C32" t="s">
-        <v>397</v>
+        <v>567</v>
       </c>
       <c r="D32" t="s">
         <v>303</v>
       </c>
       <c r="E32" t="s">
-        <v>770</v>
-      </c>
-      <c r="J32" t="s">
-        <v>397</v>
-      </c>
-      <c r="K32" t="s">
-        <v>919</v>
-      </c>
-      <c r="L32" t="s">
-        <v>950</v>
-      </c>
-      <c r="M32" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+        <v>568</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="M32"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>886</v>
+        <v>856</v>
       </c>
       <c r="B33" t="s">
-        <v>771</v>
+        <v>294</v>
       </c>
       <c r="C33" t="s">
-        <v>829</v>
+        <v>571</v>
       </c>
       <c r="D33" t="s">
         <v>303</v>
       </c>
       <c r="E33" t="s">
-        <v>830</v>
+        <v>572</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -7779,142 +7835,110 @@
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" t="s">
-        <v>831</v>
-      </c>
-      <c r="K33" t="s">
-        <v>919</v>
-      </c>
-      <c r="L33" t="s">
-        <v>951</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>969</v>
-      </c>
+      <c r="J33" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>940</v>
+      </c>
+      <c r="M33"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>882</v>
-      </c>
-      <c r="B34" t="s">
-        <v>771</v>
+        <v>865</v>
       </c>
       <c r="C34" t="s">
-        <v>808</v>
+        <v>769</v>
       </c>
       <c r="D34" t="s">
         <v>303</v>
       </c>
       <c r="E34" t="s">
-        <v>809</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
-        <v>810</v>
-      </c>
-      <c r="K34" t="s">
-        <v>919</v>
-      </c>
-      <c r="L34" t="s">
-        <v>952</v>
-      </c>
-      <c r="M34" s="6"/>
+        <v>768</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="M34" t="s">
+        <v>924</v>
+      </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>874</v>
-      </c>
-      <c r="B35" t="s">
-        <v>771</v>
+        <v>866</v>
       </c>
       <c r="C35" t="s">
-        <v>775</v>
+        <v>396</v>
       </c>
       <c r="D35" t="s">
         <v>303</v>
       </c>
       <c r="E35" t="s">
-        <v>776</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35" t="s">
-        <v>777</v>
-      </c>
-      <c r="K35" t="s">
-        <v>919</v>
-      </c>
-      <c r="L35" t="s">
-        <v>953</v>
-      </c>
-      <c r="M35" s="6"/>
+        <v>394</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>942</v>
+      </c>
+      <c r="M35" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>876</v>
-      </c>
-      <c r="B36" t="s">
-        <v>771</v>
+        <v>867</v>
       </c>
       <c r="C36" t="s">
-        <v>784</v>
+        <v>397</v>
       </c>
       <c r="D36" t="s">
         <v>303</v>
       </c>
       <c r="E36" t="s">
-        <v>785</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36" t="s">
-        <v>786</v>
-      </c>
-      <c r="K36" t="s">
-        <v>919</v>
-      </c>
-      <c r="L36" t="s">
-        <v>954</v>
-      </c>
-      <c r="M36" s="6"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+        <v>770</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>943</v>
+      </c>
+      <c r="M36" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>878</v>
-      </c>
-      <c r="B37" t="s">
-        <v>771</v>
+        <v>886</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>793</v>
+        <v>829</v>
       </c>
       <c r="D37" t="s">
         <v>303</v>
       </c>
       <c r="E37" t="s">
-        <v>794</v>
+        <v>830</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -7925,32 +7949,34 @@
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37" t="s">
-        <v>795</v>
-      </c>
-      <c r="K37" t="s">
-        <v>919</v>
-      </c>
-      <c r="L37" t="s">
-        <v>955</v>
-      </c>
-      <c r="M37" s="6"/>
+      <c r="J37" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B38" t="s">
         <v>771</v>
       </c>
       <c r="C38" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="D38" t="s">
         <v>303</v>
       </c>
       <c r="E38" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -7961,35 +7987,35 @@
       <c r="I38">
         <v>0</v>
       </c>
-      <c r="J38" t="s">
-        <v>804</v>
-      </c>
-      <c r="K38" t="s">
-        <v>919</v>
-      </c>
-      <c r="L38" t="s">
-        <v>956</v>
+      <c r="J38" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>945</v>
       </c>
       <c r="M38" s="6"/>
     </row>
-    <row r="39" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="B39" t="s">
-        <v>315</v>
+        <v>771</v>
       </c>
       <c r="C39" t="s">
-        <v>357</v>
+        <v>775</v>
       </c>
       <c r="D39" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E39" t="s">
-        <v>358</v>
+        <v>776</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -7997,34 +8023,35 @@
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39" t="s">
-        <v>357</v>
-      </c>
-      <c r="K39" t="s">
-        <v>888</v>
-      </c>
-      <c r="M39" s="6" t="s">
-        <v>901</v>
-      </c>
+      <c r="J39" s="7" t="s">
+        <v>964</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="B40" t="s">
-        <v>315</v>
+        <v>771</v>
       </c>
       <c r="C40" t="s">
-        <v>359</v>
+        <v>784</v>
       </c>
       <c r="D40" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E40" t="s">
-        <v>360</v>
+        <v>785</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -8032,32 +8059,35 @@
       <c r="I40">
         <v>0</v>
       </c>
-      <c r="J40" t="s">
-        <v>359</v>
-      </c>
-      <c r="K40" t="s">
-        <v>889</v>
+      <c r="J40" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>947</v>
       </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="B41" t="s">
-        <v>315</v>
+        <v>771</v>
       </c>
       <c r="C41" t="s">
-        <v>361</v>
+        <v>793</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E41" t="s">
-        <v>362</v>
+        <v>794</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -8065,32 +8095,35 @@
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41" t="s">
-        <v>361</v>
-      </c>
-      <c r="K41" t="s">
-        <v>890</v>
+      <c r="J41" s="7" t="s">
+        <v>795</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>948</v>
       </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="B42" t="s">
-        <v>315</v>
+        <v>771</v>
       </c>
       <c r="C42" t="s">
-        <v>363</v>
+        <v>802</v>
       </c>
       <c r="D42" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E42" t="s">
-        <v>364</v>
+        <v>803</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -8098,29 +8131,32 @@
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42" t="s">
-        <v>363</v>
-      </c>
-      <c r="K42" t="s">
-        <v>891</v>
+      <c r="J42" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>949</v>
       </c>
       <c r="M42" s="6"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B43" t="s">
         <v>315</v>
       </c>
       <c r="C43" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="D43" t="s">
         <v>296</v>
       </c>
       <c r="E43" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -8131,29 +8167,32 @@
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43" t="s">
-        <v>365</v>
-      </c>
-      <c r="K43" t="s">
-        <v>892</v>
-      </c>
-      <c r="M43" s="6"/>
+      <c r="J43" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="L43" s="7"/>
+      <c r="M43" s="6" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B44" t="s">
         <v>315</v>
       </c>
       <c r="C44" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D44" t="s">
         <v>296</v>
       </c>
       <c r="E44" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -8164,32 +8203,33 @@
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44" t="s">
-        <v>367</v>
-      </c>
-      <c r="K44" t="s">
-        <v>893</v>
-      </c>
+      <c r="J44" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="L44" s="7"/>
       <c r="M44" s="6"/>
     </row>
-    <row r="45" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="B45" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C45" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D45" t="s">
         <v>296</v>
       </c>
       <c r="E45" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -8197,32 +8237,33 @@
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45" t="s">
-        <v>371</v>
-      </c>
-      <c r="K45" t="s">
-        <v>894</v>
-      </c>
+      <c r="J45" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="L45" s="7"/>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="B46" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="D46" t="s">
         <v>296</v>
       </c>
       <c r="E46" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -8230,31 +8271,30 @@
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" t="s">
-        <v>374</v>
-      </c>
-      <c r="K46" t="s">
-        <v>895</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>961</v>
-      </c>
+      <c r="J46" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="L46" s="7"/>
+      <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="B47" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C47" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="D47" t="s">
         <v>296</v>
       </c>
       <c r="E47" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -8265,377 +8305,440 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47" t="s">
-        <v>957</v>
-      </c>
-      <c r="K47" t="s">
-        <v>896</v>
-      </c>
+      <c r="J47" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="L47" s="7"/>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="B48" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C48" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="D48" t="s">
         <v>296</v>
       </c>
       <c r="E48" t="s">
+        <v>368</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="L48" s="7"/>
+      <c r="M48" s="6"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B49" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <v>0</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="L49" s="7"/>
+      <c r="M49" s="6"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B50" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4">
+        <v>0</v>
+      </c>
+      <c r="I50" s="4">
+        <v>0</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>970</v>
+      </c>
+      <c r="L50" s="7"/>
+      <c r="M50" s="6"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B51" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4">
+        <v>0</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="L51" s="7"/>
+      <c r="M51" s="6"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B52" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4">
+        <v>0</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="L52" s="7"/>
+      <c r="M52" s="6"/>
+    </row>
+    <row r="53" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>875</v>
+      </c>
+      <c r="B53" t="s">
+        <v>771</v>
+      </c>
+      <c r="C53" t="s">
+        <v>369</v>
+      </c>
+      <c r="D53" t="s">
+        <v>296</v>
+      </c>
+      <c r="E53" t="s">
+        <v>370</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>973</v>
+      </c>
+      <c r="L53" s="9"/>
+      <c r="M53" s="6"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>877</v>
+      </c>
+      <c r="B54" t="s">
+        <v>771</v>
+      </c>
+      <c r="C54" t="s">
+        <v>372</v>
+      </c>
+      <c r="D54" t="s">
+        <v>296</v>
+      </c>
+      <c r="E54" t="s">
+        <v>373</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>974</v>
+      </c>
+      <c r="L54" s="9"/>
+      <c r="M54" s="6" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>879</v>
+      </c>
+      <c r="B55" t="s">
+        <v>771</v>
+      </c>
+      <c r="C55" t="s">
+        <v>375</v>
+      </c>
+      <c r="D55" t="s">
+        <v>296</v>
+      </c>
+      <c r="E55" t="s">
+        <v>376</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>975</v>
+      </c>
+      <c r="L55" s="9"/>
+      <c r="M55" s="6"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>881</v>
+      </c>
+      <c r="B56" t="s">
+        <v>771</v>
+      </c>
+      <c r="C56" t="s">
+        <v>378</v>
+      </c>
+      <c r="D56" t="s">
+        <v>296</v>
+      </c>
+      <c r="E56" t="s">
         <v>379</v>
       </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48" t="s">
-        <v>958</v>
-      </c>
-      <c r="K48" t="s">
-        <v>897</v>
-      </c>
-      <c r="M48" s="6"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="L56" s="9"/>
+      <c r="M56" s="6"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
         <v>883</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B57" t="s">
         <v>771</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C57" t="s">
         <v>381</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D57" t="s">
         <v>296</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E57" t="s">
         <v>382</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49" t="s">
-        <v>959</v>
-      </c>
-      <c r="K49" t="s">
-        <v>898</v>
-      </c>
-      <c r="L49" t="s">
-        <v>962</v>
-      </c>
-      <c r="M49" s="6"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>977</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>980</v>
+      </c>
+      <c r="M57" s="6"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
         <v>884</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B58" t="s">
         <v>771</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C58" t="s">
         <v>384</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D58" t="s">
         <v>296</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E58" t="s">
         <v>385</v>
       </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50" t="s">
-        <v>960</v>
-      </c>
-      <c r="K50" t="s">
-        <v>899</v>
-      </c>
-      <c r="L50" t="s">
-        <v>963</v>
-      </c>
-      <c r="M50" s="6"/>
-    </row>
-    <row r="51" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>981</v>
+      </c>
+      <c r="M58" s="6"/>
+    </row>
+    <row r="59" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
         <v>885</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B59" t="s">
         <v>771</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C59" t="s">
         <v>387</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D59" t="s">
         <v>296</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E59" t="s">
         <v>388</v>
       </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51" t="s">
-        <v>966</v>
-      </c>
-      <c r="K51" t="s">
-        <v>900</v>
-      </c>
-      <c r="L51" t="s">
-        <v>964</v>
-      </c>
-      <c r="M51" s="6"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="D52" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B65" t="s">
-        <v>315</v>
-      </c>
-      <c r="C65" t="s">
-        <v>405</v>
-      </c>
-      <c r="D65" t="s">
-        <v>303</v>
-      </c>
-      <c r="E65" t="s">
-        <v>406</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>1</v>
-      </c>
-      <c r="J65" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B66" t="s">
-        <v>294</v>
-      </c>
-      <c r="C66" t="s">
-        <v>408</v>
-      </c>
-      <c r="D66" t="s">
-        <v>303</v>
-      </c>
-      <c r="E66" t="s">
-        <v>409</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B67" t="s">
-        <v>294</v>
-      </c>
-      <c r="C67" t="s">
-        <v>410</v>
-      </c>
-      <c r="D67" t="s">
-        <v>303</v>
-      </c>
-      <c r="E67" t="s">
-        <v>411</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B68" t="s">
-        <v>294</v>
-      </c>
-      <c r="C68" t="s">
-        <v>412</v>
-      </c>
-      <c r="D68" t="s">
-        <v>303</v>
-      </c>
-      <c r="E68" t="s">
-        <v>413</v>
-      </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B69" t="s">
-        <v>294</v>
-      </c>
-      <c r="C69" t="s">
-        <v>414</v>
-      </c>
-      <c r="D69" t="s">
-        <v>303</v>
-      </c>
-      <c r="E69" t="s">
-        <v>415</v>
-      </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B70" t="s">
-        <v>294</v>
-      </c>
-      <c r="C70" t="s">
-        <v>416</v>
-      </c>
-      <c r="D70" t="s">
-        <v>303</v>
-      </c>
-      <c r="E70" t="s">
-        <v>417</v>
-      </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B71" t="s">
-        <v>294</v>
-      </c>
-      <c r="C71" t="s">
-        <v>418</v>
-      </c>
-      <c r="D71" t="s">
-        <v>303</v>
-      </c>
-      <c r="E71" t="s">
-        <v>419</v>
-      </c>
-      <c r="G71">
-        <v>1</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B72" t="s">
-        <v>315</v>
-      </c>
-      <c r="C72" t="s">
-        <v>420</v>
-      </c>
-      <c r="D72" t="s">
-        <v>303</v>
-      </c>
-      <c r="E72" t="s">
-        <v>421</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>982</v>
+      </c>
+      <c r="M59" s="6"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B73" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C73" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="D73" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E73" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -8644,10 +8747,10 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.4">
@@ -8655,16 +8758,16 @@
         <v>294</v>
       </c>
       <c r="C74" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="D74" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E74" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -8673,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.4">
@@ -8681,16 +8784,16 @@
         <v>294</v>
       </c>
       <c r="C75" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="D75" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E75" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -8699,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.4">
@@ -8707,16 +8810,16 @@
         <v>294</v>
       </c>
       <c r="C76" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="D76" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E76" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -8725,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.4">
@@ -8733,16 +8836,16 @@
         <v>294</v>
       </c>
       <c r="C77" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="D77" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E77" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -8751,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.4">
@@ -8759,16 +8862,16 @@
         <v>294</v>
       </c>
       <c r="C78" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="D78" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E78" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -8777,24 +8880,24 @@
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B79" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C79" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="D79" t="s">
         <v>303</v>
       </c>
       <c r="E79" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -8803,21 +8906,21 @@
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B80" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C80" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="D80" t="s">
         <v>303</v>
       </c>
       <c r="E80" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -8827,9 +8930,6 @@
       </c>
       <c r="I80">
         <v>0</v>
-      </c>
-      <c r="J80" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.4">
@@ -8837,16 +8937,16 @@
         <v>294</v>
       </c>
       <c r="C81" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="D81" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E81" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -8855,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.4">
@@ -8863,19 +8963,16 @@
         <v>294</v>
       </c>
       <c r="C82" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="D82" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E82" t="s">
-        <v>443</v>
-      </c>
-      <c r="F82" t="s">
-        <v>318</v>
+        <v>426</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -8884,7 +8981,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.4">
@@ -8892,13 +8989,13 @@
         <v>294</v>
       </c>
       <c r="C83" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="D83" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E83" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8910,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.4">
@@ -8918,16 +9015,16 @@
         <v>294</v>
       </c>
       <c r="C84" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="D84" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E84" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -8936,7 +9033,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.4">
@@ -8944,19 +9041,16 @@
         <v>294</v>
       </c>
       <c r="C85" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="D85" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E85" t="s">
-        <v>449</v>
-      </c>
-      <c r="F85" t="s">
-        <v>318</v>
+        <v>432</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -8965,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.4">
@@ -8973,16 +9067,16 @@
         <v>294</v>
       </c>
       <c r="C86" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="D86" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E86" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -8991,21 +9085,21 @@
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B87" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C87" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="D87" t="s">
         <v>303</v>
       </c>
       <c r="E87" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -9017,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.4">
@@ -9025,16 +9119,16 @@
         <v>294</v>
       </c>
       <c r="C88" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="D88" t="s">
         <v>303</v>
       </c>
       <c r="E88" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -9043,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.4">
@@ -9051,16 +9145,13 @@
         <v>294</v>
       </c>
       <c r="C89" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="D89" t="s">
         <v>303</v>
       </c>
       <c r="E89" t="s">
-        <v>457</v>
-      </c>
-      <c r="F89" t="s">
-        <v>318</v>
+        <v>441</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -9072,7 +9163,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.4">
@@ -9080,13 +9171,16 @@
         <v>294</v>
       </c>
       <c r="C90" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="D90" t="s">
         <v>303</v>
       </c>
       <c r="E90" t="s">
-        <v>459</v>
+        <v>443</v>
+      </c>
+      <c r="F90" t="s">
+        <v>318</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -9098,7 +9192,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.4">
@@ -9106,16 +9200,16 @@
         <v>294</v>
       </c>
       <c r="C91" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="D91" t="s">
         <v>303</v>
       </c>
       <c r="E91" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -9124,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.4">
@@ -9132,16 +9226,16 @@
         <v>294</v>
       </c>
       <c r="C92" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="D92" t="s">
         <v>303</v>
       </c>
       <c r="E92" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -9150,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.4">
@@ -9158,13 +9252,16 @@
         <v>294</v>
       </c>
       <c r="C93" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="D93" t="s">
         <v>303</v>
       </c>
       <c r="E93" t="s">
-        <v>465</v>
+        <v>449</v>
+      </c>
+      <c r="F93" t="s">
+        <v>318</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -9176,7 +9273,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.4">
@@ -9184,13 +9281,13 @@
         <v>294</v>
       </c>
       <c r="C94" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="D94" t="s">
         <v>303</v>
       </c>
       <c r="E94" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -9202,44 +9299,47 @@
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B95" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C95" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="D95" t="s">
         <v>303</v>
       </c>
       <c r="E95" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
       <c r="I95">
         <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B96" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C96" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="D96" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E96" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -9249,20 +9349,26 @@
       </c>
       <c r="I96">
         <v>0</v>
+      </c>
+      <c r="J96" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B97" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C97" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="D97" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="E97" t="s">
-        <v>473</v>
+        <v>457</v>
+      </c>
+      <c r="F97" t="s">
+        <v>318</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -9272,6 +9378,9 @@
       </c>
       <c r="I97">
         <v>0</v>
+      </c>
+      <c r="J97" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.4">
@@ -9279,16 +9388,16 @@
         <v>294</v>
       </c>
       <c r="C98" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="D98" t="s">
         <v>303</v>
       </c>
       <c r="E98" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -9297,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.4">
@@ -9305,16 +9414,16 @@
         <v>294</v>
       </c>
       <c r="C99" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="D99" t="s">
         <v>303</v>
       </c>
       <c r="E99" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -9323,7 +9432,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.4">
@@ -9331,13 +9440,13 @@
         <v>294</v>
       </c>
       <c r="C100" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="D100" t="s">
         <v>303</v>
       </c>
       <c r="E100" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9349,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.4">
@@ -9357,16 +9466,16 @@
         <v>294</v>
       </c>
       <c r="C101" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="D101" t="s">
         <v>303</v>
       </c>
       <c r="E101" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -9375,7 +9484,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.4">
@@ -9383,16 +9492,16 @@
         <v>294</v>
       </c>
       <c r="C102" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="D102" t="s">
         <v>303</v>
       </c>
       <c r="E102" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -9401,85 +9510,76 @@
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B103" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C103" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="D103" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E103" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103">
         <v>0</v>
       </c>
       <c r="I103">
         <v>0</v>
-      </c>
-      <c r="J103" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B104" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C104" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="D104" t="s">
         <v>296</v>
       </c>
       <c r="E104" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104">
         <v>0</v>
       </c>
       <c r="I104">
         <v>0</v>
-      </c>
-      <c r="J104" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B105" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C105" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="D105" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="E105" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105">
         <v>0</v>
       </c>
       <c r="I105">
         <v>0</v>
-      </c>
-      <c r="J105" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.4">
@@ -9487,13 +9587,13 @@
         <v>294</v>
       </c>
       <c r="C106" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="D106" t="s">
         <v>303</v>
       </c>
       <c r="E106" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -9505,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.4">
@@ -9513,16 +9613,16 @@
         <v>294</v>
       </c>
       <c r="C107" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="D107" t="s">
         <v>303</v>
       </c>
       <c r="E107" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -9531,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.4">
@@ -9539,13 +9639,13 @@
         <v>294</v>
       </c>
       <c r="C108" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="D108" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E108" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -9557,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.4">
@@ -9565,13 +9665,13 @@
         <v>294</v>
       </c>
       <c r="C109" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D109" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E109" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -9583,7 +9683,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.4">
@@ -9591,13 +9691,13 @@
         <v>294</v>
       </c>
       <c r="C110" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="D110" t="s">
         <v>303</v>
       </c>
       <c r="E110" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -9609,7 +9709,7 @@
         <v>0</v>
       </c>
       <c r="J110" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.4">
@@ -9617,13 +9717,13 @@
         <v>294</v>
       </c>
       <c r="C111" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="D111" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E111" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -9635,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.4">
@@ -9643,16 +9743,16 @@
         <v>294</v>
       </c>
       <c r="C112" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="D112" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E112" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -9661,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.4">
@@ -9669,22 +9769,25 @@
         <v>294</v>
       </c>
       <c r="C113" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="D113" t="s">
         <v>303</v>
       </c>
       <c r="E113" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
         <v>0</v>
+      </c>
+      <c r="J113" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.4">
@@ -9692,22 +9795,25 @@
         <v>294</v>
       </c>
       <c r="C114" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="D114" t="s">
         <v>303</v>
       </c>
       <c r="E114" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
         <v>0</v>
+      </c>
+      <c r="J114" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.4">
@@ -9715,16 +9821,16 @@
         <v>294</v>
       </c>
       <c r="C115" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="D115" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E115" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -9733,7 +9839,7 @@
         <v>0</v>
       </c>
       <c r="J115" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.4">
@@ -9741,13 +9847,13 @@
         <v>294</v>
       </c>
       <c r="C116" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="D116" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E116" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -9759,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.4">
@@ -9767,13 +9873,13 @@
         <v>294</v>
       </c>
       <c r="C117" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="D117" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E117" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -9785,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="J117" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.4">
@@ -9793,13 +9899,13 @@
         <v>294</v>
       </c>
       <c r="C118" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="D118" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E118" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -9811,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="J118" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.4">
@@ -9819,13 +9925,13 @@
         <v>294</v>
       </c>
       <c r="C119" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="D119" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E119" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -9837,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.4">
@@ -9845,16 +9951,16 @@
         <v>294</v>
       </c>
       <c r="C120" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="D120" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E120" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -9863,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.4">
@@ -9871,25 +9977,22 @@
         <v>294</v>
       </c>
       <c r="C121" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="D121" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E121" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121">
         <v>0</v>
       </c>
       <c r="I121">
         <v>0</v>
-      </c>
-      <c r="J121" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.4">
@@ -9897,25 +10000,22 @@
         <v>294</v>
       </c>
       <c r="C122" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="D122" t="s">
         <v>303</v>
       </c>
       <c r="E122" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
       <c r="I122">
         <v>0</v>
-      </c>
-      <c r="J122" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.4">
@@ -9923,13 +10023,13 @@
         <v>294</v>
       </c>
       <c r="C123" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="D123" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E123" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -9941,7 +10041,7 @@
         <v>0</v>
       </c>
       <c r="J123" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.4">
@@ -9949,13 +10049,13 @@
         <v>294</v>
       </c>
       <c r="C124" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="D124" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E124" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -9967,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.4">
@@ -9975,16 +10075,16 @@
         <v>294</v>
       </c>
       <c r="C125" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="D125" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E125" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -9993,7 +10093,7 @@
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.4">
@@ -10001,13 +10101,13 @@
         <v>294</v>
       </c>
       <c r="C126" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="D126" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E126" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -10019,7 +10119,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.4">
@@ -10027,13 +10127,13 @@
         <v>294</v>
       </c>
       <c r="C127" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="D127" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E127" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -10045,7 +10145,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.4">
@@ -10053,13 +10153,13 @@
         <v>294</v>
       </c>
       <c r="C128" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="D128" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E128" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -10071,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.4">
@@ -10079,13 +10179,13 @@
         <v>294</v>
       </c>
       <c r="C129" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="D129" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E129" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -10097,7 +10197,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.4">
@@ -10105,16 +10205,16 @@
         <v>294</v>
       </c>
       <c r="C130" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="D130" t="s">
         <v>303</v>
       </c>
       <c r="E130" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -10123,7 +10223,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.4">
@@ -10131,16 +10231,16 @@
         <v>294</v>
       </c>
       <c r="C131" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="D131" t="s">
         <v>303</v>
       </c>
       <c r="E131" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="G131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -10149,7 +10249,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.4">
@@ -10157,16 +10257,16 @@
         <v>294</v>
       </c>
       <c r="C132" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="D132" t="s">
         <v>303</v>
       </c>
       <c r="E132" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132">
         <v>0</v>
@@ -10175,7 +10275,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.4">
@@ -10183,16 +10283,16 @@
         <v>294</v>
       </c>
       <c r="C133" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="D133" t="s">
         <v>303</v>
       </c>
       <c r="E133" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -10201,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="J133" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.4">
@@ -10209,16 +10309,16 @@
         <v>294</v>
       </c>
       <c r="C134" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="D134" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E134" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="G134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -10227,7 +10327,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.4">
@@ -10235,19 +10335,16 @@
         <v>294</v>
       </c>
       <c r="C135" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="D135" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E135" t="s">
-        <v>550</v>
-      </c>
-      <c r="F135" t="s">
-        <v>318</v>
+        <v>534</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -10256,7 +10353,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.4">
@@ -10264,13 +10361,13 @@
         <v>294</v>
       </c>
       <c r="C136" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="D136" t="s">
         <v>303</v>
       </c>
       <c r="E136" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -10282,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.4">
@@ -10290,16 +10387,16 @@
         <v>294</v>
       </c>
       <c r="C137" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="D137" t="s">
         <v>303</v>
       </c>
       <c r="E137" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -10308,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="J137" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.4">
@@ -10316,16 +10413,13 @@
         <v>294</v>
       </c>
       <c r="C138" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="D138" t="s">
         <v>303</v>
       </c>
       <c r="E138" t="s">
-        <v>556</v>
-      </c>
-      <c r="F138" t="s">
-        <v>318</v>
+        <v>540</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -10337,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="J138" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.4">
@@ -10345,13 +10439,13 @@
         <v>294</v>
       </c>
       <c r="C139" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="D139" t="s">
         <v>303</v>
       </c>
       <c r="E139" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -10363,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.4">
@@ -10371,16 +10465,16 @@
         <v>294</v>
       </c>
       <c r="C140" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="D140" t="s">
         <v>303</v>
       </c>
       <c r="E140" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -10389,7 +10483,7 @@
         <v>0</v>
       </c>
       <c r="J140" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.4">
@@ -10397,16 +10491,16 @@
         <v>294</v>
       </c>
       <c r="C141" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="D141" t="s">
         <v>303</v>
       </c>
       <c r="E141" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -10415,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.4">
@@ -10423,16 +10517,13 @@
         <v>294</v>
       </c>
       <c r="C142" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="D142" t="s">
         <v>303</v>
       </c>
       <c r="E142" t="s">
-        <v>564</v>
-      </c>
-      <c r="F142" t="s">
-        <v>318</v>
+        <v>548</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -10444,7 +10535,7 @@
         <v>0</v>
       </c>
       <c r="J142" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.4">
@@ -10452,13 +10543,13 @@
         <v>294</v>
       </c>
       <c r="C143" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="D143" t="s">
         <v>303</v>
       </c>
       <c r="E143" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="F143" t="s">
         <v>318</v>
@@ -10473,7 +10564,7 @@
         <v>0</v>
       </c>
       <c r="J143" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.4">
@@ -10481,16 +10572,16 @@
         <v>294</v>
       </c>
       <c r="C144" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="D144" t="s">
         <v>303</v>
       </c>
       <c r="E144" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="G144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -10499,7 +10590,7 @@
         <v>0</v>
       </c>
       <c r="J144" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.4">
@@ -10507,16 +10598,16 @@
         <v>294</v>
       </c>
       <c r="C145" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="D145" t="s">
         <v>303</v>
       </c>
       <c r="E145" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -10525,7 +10616,7 @@
         <v>0</v>
       </c>
       <c r="J145" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.4">
@@ -10533,13 +10624,16 @@
         <v>294</v>
       </c>
       <c r="C146" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="D146" t="s">
         <v>303</v>
       </c>
       <c r="E146" t="s">
-        <v>572</v>
+        <v>556</v>
+      </c>
+      <c r="F146" t="s">
+        <v>318</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -10551,7 +10645,7 @@
         <v>0</v>
       </c>
       <c r="J146" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.4">
@@ -10559,13 +10653,13 @@
         <v>294</v>
       </c>
       <c r="C147" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="D147" t="s">
         <v>303</v>
       </c>
       <c r="E147" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -10577,21 +10671,21 @@
         <v>0</v>
       </c>
       <c r="J147" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B148" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C148" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="D148" t="s">
         <v>303</v>
       </c>
       <c r="E148" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -10603,24 +10697,24 @@
         <v>0</v>
       </c>
       <c r="J148" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B149" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C149" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="D149" t="s">
         <v>303</v>
       </c>
       <c r="E149" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -10629,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.4">
@@ -10637,16 +10731,19 @@
         <v>294</v>
       </c>
       <c r="C150" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="D150" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E150" t="s">
-        <v>581</v>
+        <v>564</v>
+      </c>
+      <c r="F150" t="s">
+        <v>318</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -10655,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="J150" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.4">
@@ -10663,16 +10760,19 @@
         <v>294</v>
       </c>
       <c r="C151" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
       <c r="D151" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E151" t="s">
-        <v>583</v>
+        <v>566</v>
+      </c>
+      <c r="F151" t="s">
+        <v>318</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -10681,7 +10781,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.4">
@@ -10689,16 +10789,16 @@
         <v>294</v>
       </c>
       <c r="C152" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
       <c r="D152" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E152" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -10707,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
     </row>
     <row r="153" spans="2:10" x14ac:dyDescent="0.4">
@@ -10715,13 +10815,13 @@
         <v>294</v>
       </c>
       <c r="C153" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="D153" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E153" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -10733,7 +10833,7 @@
         <v>0</v>
       </c>
       <c r="J153" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.4">
@@ -10741,16 +10841,16 @@
         <v>294</v>
       </c>
       <c r="C154" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="D154" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E154" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -10759,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.4">
@@ -10767,16 +10867,16 @@
         <v>294</v>
       </c>
       <c r="C155" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E155" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -10785,21 +10885,21 @@
         <v>0</v>
       </c>
       <c r="J155" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B156" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C156" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="D156" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E156" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -10811,21 +10911,21 @@
         <v>0</v>
       </c>
       <c r="J156" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B157" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C157" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="D157" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E157" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -10837,7 +10937,7 @@
         <v>0</v>
       </c>
       <c r="J157" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.4">
@@ -10845,13 +10945,13 @@
         <v>294</v>
       </c>
       <c r="C158" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="D158" t="s">
         <v>423</v>
       </c>
       <c r="E158" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -10863,7 +10963,7 @@
         <v>0</v>
       </c>
       <c r="J158" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.4">
@@ -10871,13 +10971,13 @@
         <v>294</v>
       </c>
       <c r="C159" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="D159" t="s">
         <v>509</v>
       </c>
       <c r="E159" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -10889,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.4">
@@ -10897,13 +10997,13 @@
         <v>294</v>
       </c>
       <c r="C160" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D160" t="s">
-        <v>509</v>
+        <v>423</v>
       </c>
       <c r="E160" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -10915,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="J160" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.4">
@@ -10923,13 +11023,13 @@
         <v>294</v>
       </c>
       <c r="C161" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="D161" t="s">
         <v>509</v>
       </c>
       <c r="E161" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -10941,7 +11041,7 @@
         <v>0</v>
       </c>
       <c r="J161" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.4">
@@ -10949,16 +11049,16 @@
         <v>294</v>
       </c>
       <c r="C162" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="D162" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E162" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="G162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -10967,7 +11067,7 @@
         <v>0</v>
       </c>
       <c r="J162" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.4">
@@ -10975,16 +11075,16 @@
         <v>294</v>
       </c>
       <c r="C163" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="D163" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E163" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="G163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -10993,7 +11093,7 @@
         <v>0</v>
       </c>
       <c r="J163" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.4">
@@ -11001,16 +11101,16 @@
         <v>294</v>
       </c>
       <c r="C164" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="D164" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E164" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="G164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -11019,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="J164" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.4">
@@ -11027,16 +11127,16 @@
         <v>294</v>
       </c>
       <c r="C165" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="D165" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E165" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="G165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -11045,7 +11145,7 @@
         <v>0</v>
       </c>
       <c r="J165" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.4">
@@ -11053,16 +11153,16 @@
         <v>294</v>
       </c>
       <c r="C166" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="D166" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E166" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="G166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -11071,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="J166" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.4">
@@ -11079,16 +11179,16 @@
         <v>294</v>
       </c>
       <c r="C167" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="D167" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E167" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="G167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -11097,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="J167" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.4">
@@ -11105,16 +11205,16 @@
         <v>294</v>
       </c>
       <c r="C168" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="D168" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E168" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -11123,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="J168" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.4">
@@ -11131,13 +11231,13 @@
         <v>294</v>
       </c>
       <c r="C169" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="D169" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E169" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -11149,7 +11249,7 @@
         <v>0</v>
       </c>
       <c r="J169" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.4">
@@ -11157,16 +11257,16 @@
         <v>294</v>
       </c>
       <c r="C170" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="D170" t="s">
         <v>303</v>
       </c>
       <c r="E170" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -11175,7 +11275,7 @@
         <v>0</v>
       </c>
       <c r="J170" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.4">
@@ -11183,13 +11283,13 @@
         <v>294</v>
       </c>
       <c r="C171" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="D171" t="s">
         <v>303</v>
       </c>
       <c r="E171" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -11201,7 +11301,7 @@
         <v>0</v>
       </c>
       <c r="J171" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.4">
@@ -11209,13 +11309,13 @@
         <v>294</v>
       </c>
       <c r="C172" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="D172" t="s">
         <v>303</v>
       </c>
       <c r="E172" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -11227,7 +11327,7 @@
         <v>0</v>
       </c>
       <c r="J172" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.4">
@@ -11235,13 +11335,13 @@
         <v>294</v>
       </c>
       <c r="C173" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="D173" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E173" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -11253,24 +11353,24 @@
         <v>0</v>
       </c>
       <c r="J173" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B174" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C174" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="D174" t="s">
         <v>303</v>
       </c>
       <c r="E174" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -11279,7 +11379,7 @@
         <v>0</v>
       </c>
       <c r="J174" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.4">
@@ -11287,13 +11387,13 @@
         <v>294</v>
       </c>
       <c r="C175" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="D175" t="s">
         <v>303</v>
       </c>
       <c r="E175" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -11305,7 +11405,7 @@
         <v>0</v>
       </c>
       <c r="J175" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.4">
@@ -11313,13 +11413,13 @@
         <v>294</v>
       </c>
       <c r="C176" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="D176" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E176" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -11331,7 +11431,7 @@
         <v>0</v>
       </c>
       <c r="J176" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.4">
@@ -11339,13 +11439,13 @@
         <v>294</v>
       </c>
       <c r="C177" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="D177" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E177" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -11357,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="J177" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.4">
@@ -11365,13 +11465,13 @@
         <v>294</v>
       </c>
       <c r="C178" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="D178" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E178" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -11383,7 +11483,7 @@
         <v>0</v>
       </c>
       <c r="J178" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.4">
@@ -11391,16 +11491,16 @@
         <v>294</v>
       </c>
       <c r="C179" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="D179" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E179" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -11409,7 +11509,7 @@
         <v>0</v>
       </c>
       <c r="J179" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.4">
@@ -11417,16 +11517,16 @@
         <v>294</v>
       </c>
       <c r="C180" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="D180" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E180" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -11435,7 +11535,7 @@
         <v>0</v>
       </c>
       <c r="J180" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.4">
@@ -11443,16 +11543,16 @@
         <v>294</v>
       </c>
       <c r="C181" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="D181" t="s">
         <v>296</v>
       </c>
       <c r="E181" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -11461,21 +11561,21 @@
         <v>0</v>
       </c>
       <c r="J181" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B182" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C182" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="D182" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E182" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -11487,7 +11587,7 @@
         <v>0</v>
       </c>
       <c r="J182" t="s">
-        <v>645</v>
+        <v>630</v>
       </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.4">
@@ -11495,16 +11595,16 @@
         <v>294</v>
       </c>
       <c r="C183" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="D183" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E183" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -11513,7 +11613,7 @@
         <v>0</v>
       </c>
       <c r="J183" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.4">
@@ -11521,16 +11621,16 @@
         <v>294</v>
       </c>
       <c r="C184" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="D184" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E184" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -11539,7 +11639,7 @@
         <v>0</v>
       </c>
       <c r="J184" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.4">
@@ -11547,13 +11647,13 @@
         <v>294</v>
       </c>
       <c r="C185" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="D185" t="s">
         <v>296</v>
       </c>
       <c r="E185" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="G185">
         <v>0</v>
@@ -11565,24 +11665,21 @@
         <v>0</v>
       </c>
       <c r="J185" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B186" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C186" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="D186" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E186" t="s">
-        <v>654</v>
-      </c>
-      <c r="F186" t="s">
-        <v>318</v>
+        <v>638</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -11591,27 +11688,24 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J186" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B187" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C187" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="D187" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E187" t="s">
-        <v>656</v>
-      </c>
-      <c r="F187" t="s">
-        <v>318</v>
+        <v>640</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -11620,27 +11714,24 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J187" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B188" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C188" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="D188" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E188" t="s">
-        <v>658</v>
-      </c>
-      <c r="F188" t="s">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="G188">
         <v>0</v>
@@ -11649,27 +11740,24 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J188" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B189" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C189" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="D189" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E189" t="s">
-        <v>660</v>
-      </c>
-      <c r="F189" t="s">
-        <v>318</v>
+        <v>644</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -11678,27 +11766,24 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J189" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B190" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C190" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="D190" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E190" t="s">
-        <v>662</v>
-      </c>
-      <c r="F190" t="s">
-        <v>318</v>
+        <v>646</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -11707,27 +11792,24 @@
         <v>0</v>
       </c>
       <c r="I190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B191" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C191" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="D191" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E191" t="s">
-        <v>664</v>
-      </c>
-      <c r="F191" t="s">
-        <v>318</v>
+        <v>648</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -11736,27 +11818,24 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J191" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B192" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C192" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="D192" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E192" t="s">
-        <v>666</v>
-      </c>
-      <c r="F192" t="s">
-        <v>318</v>
+        <v>650</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -11765,27 +11844,24 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J192" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
     </row>
     <row r="193" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B193" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C193" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="D193" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E193" t="s">
-        <v>668</v>
-      </c>
-      <c r="F193" t="s">
-        <v>318</v>
+        <v>652</v>
       </c>
       <c r="G193">
         <v>0</v>
@@ -11794,10 +11870,10 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
     </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.4">
@@ -11805,13 +11881,13 @@
         <v>315</v>
       </c>
       <c r="C194" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="D194" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E194" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="F194" t="s">
         <v>318</v>
@@ -11826,7 +11902,7 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.4">
@@ -11834,13 +11910,13 @@
         <v>315</v>
       </c>
       <c r="C195" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="D195" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E195" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="F195" t="s">
         <v>318</v>
@@ -11855,7 +11931,7 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.4">
@@ -11863,13 +11939,13 @@
         <v>315</v>
       </c>
       <c r="C196" t="s">
-        <v>351</v>
+        <v>657</v>
       </c>
       <c r="D196" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E196" t="s">
-        <v>352</v>
+        <v>658</v>
       </c>
       <c r="F196" t="s">
         <v>318</v>
@@ -11884,7 +11960,7 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>351</v>
+        <v>657</v>
       </c>
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.4">
@@ -11892,13 +11968,13 @@
         <v>315</v>
       </c>
       <c r="C197" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="D197" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E197" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="F197" t="s">
         <v>318</v>
@@ -11913,7 +11989,7 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.4">
@@ -11921,13 +11997,13 @@
         <v>315</v>
       </c>
       <c r="C198" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="D198" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E198" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="F198" t="s">
         <v>318</v>
@@ -11942,7 +12018,7 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.4">
@@ -11950,13 +12026,13 @@
         <v>315</v>
       </c>
       <c r="C199" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="D199" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E199" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="F199" t="s">
         <v>318</v>
@@ -11971,7 +12047,7 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.4">
@@ -11979,13 +12055,13 @@
         <v>315</v>
       </c>
       <c r="C200" t="s">
-        <v>353</v>
+        <v>665</v>
       </c>
       <c r="D200" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E200" t="s">
-        <v>354</v>
+        <v>666</v>
       </c>
       <c r="F200" t="s">
         <v>318</v>
@@ -12000,7 +12076,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>353</v>
+        <v>665</v>
       </c>
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.4">
@@ -12008,13 +12084,13 @@
         <v>315</v>
       </c>
       <c r="C201" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="D201" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E201" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="F201" t="s">
         <v>318</v>
@@ -12029,7 +12105,7 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.4">
@@ -12037,13 +12113,13 @@
         <v>315</v>
       </c>
       <c r="C202" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="D202" t="s">
         <v>296</v>
       </c>
       <c r="E202" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="F202" t="s">
         <v>318</v>
@@ -12058,7 +12134,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.4">
@@ -12066,13 +12142,13 @@
         <v>315</v>
       </c>
       <c r="C203" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="D203" t="s">
         <v>296</v>
       </c>
       <c r="E203" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="F203" t="s">
         <v>318</v>
@@ -12087,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
     </row>
     <row r="204" spans="2:10" x14ac:dyDescent="0.4">
@@ -12095,13 +12171,13 @@
         <v>315</v>
       </c>
       <c r="C204" t="s">
-        <v>685</v>
+        <v>351</v>
       </c>
       <c r="D204" t="s">
         <v>296</v>
       </c>
       <c r="E204" t="s">
-        <v>686</v>
+        <v>352</v>
       </c>
       <c r="F204" t="s">
         <v>318</v>
@@ -12116,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>685</v>
+        <v>351</v>
       </c>
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.4">
@@ -12124,13 +12200,13 @@
         <v>315</v>
       </c>
       <c r="C205" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="D205" t="s">
         <v>296</v>
       </c>
       <c r="E205" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="F205" t="s">
         <v>318</v>
@@ -12145,7 +12221,7 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.4">
@@ -12153,13 +12229,13 @@
         <v>315</v>
       </c>
       <c r="C206" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="D206" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E206" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="F206" t="s">
         <v>318</v>
@@ -12171,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="I206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.4">
@@ -12182,13 +12258,13 @@
         <v>315</v>
       </c>
       <c r="C207" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="D207" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E207" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="F207" t="s">
         <v>318</v>
@@ -12200,10 +12276,10 @@
         <v>0</v>
       </c>
       <c r="I207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.4">
@@ -12211,13 +12287,13 @@
         <v>315</v>
       </c>
       <c r="C208" t="s">
-        <v>694</v>
+        <v>353</v>
       </c>
       <c r="D208" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E208" t="s">
-        <v>695</v>
+        <v>354</v>
       </c>
       <c r="F208" t="s">
         <v>318</v>
@@ -12229,10 +12305,10 @@
         <v>0</v>
       </c>
       <c r="I208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>696</v>
+        <v>353</v>
       </c>
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.4">
@@ -12240,13 +12316,13 @@
         <v>315</v>
       </c>
       <c r="C209" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="D209" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E209" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="F209" t="s">
         <v>318</v>
@@ -12258,10 +12334,10 @@
         <v>0</v>
       </c>
       <c r="I209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
     </row>
     <row r="210" spans="2:10" x14ac:dyDescent="0.4">
@@ -12269,13 +12345,13 @@
         <v>315</v>
       </c>
       <c r="C210" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="D210" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E210" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="F210" t="s">
         <v>318</v>
@@ -12287,10 +12363,10 @@
         <v>0</v>
       </c>
       <c r="I210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
     </row>
     <row r="211" spans="2:10" x14ac:dyDescent="0.4">
@@ -12298,13 +12374,13 @@
         <v>315</v>
       </c>
       <c r="C211" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="D211" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E211" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="F211" t="s">
         <v>318</v>
@@ -12316,10 +12392,10 @@
         <v>0</v>
       </c>
       <c r="I211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.4">
@@ -12327,13 +12403,13 @@
         <v>315</v>
       </c>
       <c r="C212" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="D212" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E212" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="F212" t="s">
         <v>318</v>
@@ -12345,10 +12421,10 @@
         <v>0</v>
       </c>
       <c r="I212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.4">
@@ -12356,13 +12432,13 @@
         <v>315</v>
       </c>
       <c r="C213" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="D213" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E213" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="F213" t="s">
         <v>318</v>
@@ -12374,10 +12450,10 @@
         <v>0</v>
       </c>
       <c r="I213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.4">
@@ -12385,13 +12461,16 @@
         <v>315</v>
       </c>
       <c r="C214" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="D214" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E214" t="s">
-        <v>708</v>
+        <v>691</v>
+      </c>
+      <c r="F214" t="s">
+        <v>318</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -12403,21 +12482,24 @@
         <v>0</v>
       </c>
       <c r="J214" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B215" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C215" t="s">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="D215" t="s">
-        <v>303</v>
+        <v>690</v>
       </c>
       <c r="E215" t="s">
-        <v>710</v>
+        <v>693</v>
+      </c>
+      <c r="F215" t="s">
+        <v>318</v>
       </c>
       <c r="G215">
         <v>0</v>
@@ -12427,6 +12509,9 @@
       </c>
       <c r="I215">
         <v>0</v>
+      </c>
+      <c r="J215" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="216" spans="2:10" x14ac:dyDescent="0.4">
@@ -12434,13 +12519,16 @@
         <v>315</v>
       </c>
       <c r="C216" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="D216" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E216" t="s">
-        <v>712</v>
+        <v>695</v>
+      </c>
+      <c r="F216" t="s">
+        <v>318</v>
       </c>
       <c r="G216">
         <v>0</v>
@@ -12452,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="J216" t="s">
-        <v>711</v>
+        <v>696</v>
       </c>
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.4">
@@ -12460,16 +12548,19 @@
         <v>315</v>
       </c>
       <c r="C217" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="D217" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E217" t="s">
-        <v>714</v>
+        <v>698</v>
+      </c>
+      <c r="F217" t="s">
+        <v>318</v>
       </c>
       <c r="G217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217">
         <v>0</v>
@@ -12478,7 +12569,7 @@
         <v>0</v>
       </c>
       <c r="J217" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.4">
@@ -12486,13 +12577,16 @@
         <v>315</v>
       </c>
       <c r="C218" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="D218" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E218" t="s">
-        <v>716</v>
+        <v>700</v>
+      </c>
+      <c r="F218" t="s">
+        <v>318</v>
       </c>
       <c r="G218">
         <v>0</v>
@@ -12504,7 +12598,7 @@
         <v>0</v>
       </c>
       <c r="J218" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.4">
@@ -12512,13 +12606,16 @@
         <v>315</v>
       </c>
       <c r="C219" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="D219" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E219" t="s">
-        <v>718</v>
+        <v>702</v>
+      </c>
+      <c r="F219" t="s">
+        <v>318</v>
       </c>
       <c r="G219">
         <v>0</v>
@@ -12530,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="J219" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.4">
@@ -12538,16 +12635,19 @@
         <v>315</v>
       </c>
       <c r="C220" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="D220" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E220" t="s">
-        <v>720</v>
+        <v>704</v>
+      </c>
+      <c r="F220" t="s">
+        <v>318</v>
       </c>
       <c r="G220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H220">
         <v>0</v>
@@ -12556,7 +12656,7 @@
         <v>0</v>
       </c>
       <c r="J220" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.4">
@@ -12564,13 +12664,16 @@
         <v>315</v>
       </c>
       <c r="C221" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="D221" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E221" t="s">
-        <v>722</v>
+        <v>706</v>
+      </c>
+      <c r="F221" t="s">
+        <v>318</v>
       </c>
       <c r="G221">
         <v>0</v>
@@ -12582,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="J221" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
     </row>
     <row r="222" spans="2:10" x14ac:dyDescent="0.4">
@@ -12590,13 +12693,13 @@
         <v>315</v>
       </c>
       <c r="C222" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="D222" t="s">
         <v>296</v>
       </c>
       <c r="E222" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="G222">
         <v>0</v>
@@ -12608,33 +12711,30 @@
         <v>0</v>
       </c>
       <c r="J222" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B223" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C223" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="D223" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E223" t="s">
-        <v>726</v>
+        <v>710</v>
       </c>
       <c r="G223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H223">
         <v>0</v>
       </c>
       <c r="I223">
         <v>0</v>
-      </c>
-      <c r="J223" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.4">
@@ -12642,13 +12742,13 @@
         <v>315</v>
       </c>
       <c r="C224" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="D224" t="s">
         <v>296</v>
       </c>
       <c r="E224" t="s">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="G224">
         <v>0</v>
@@ -12660,7 +12760,7 @@
         <v>0</v>
       </c>
       <c r="J224" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.4">
@@ -12668,16 +12768,16 @@
         <v>315</v>
       </c>
       <c r="C225" t="s">
-        <v>729</v>
+        <v>713</v>
       </c>
       <c r="D225" t="s">
         <v>296</v>
       </c>
       <c r="E225" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="G225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -12686,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="J225" t="s">
-        <v>729</v>
+        <v>713</v>
       </c>
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.4">
@@ -12694,16 +12794,16 @@
         <v>315</v>
       </c>
       <c r="C226" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="D226" t="s">
         <v>296</v>
       </c>
       <c r="E226" t="s">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="G226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -12712,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="J226" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.4">
@@ -12720,13 +12820,13 @@
         <v>315</v>
       </c>
       <c r="C227" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
       <c r="D227" t="s">
         <v>296</v>
       </c>
       <c r="E227" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="G227">
         <v>0</v>
@@ -12738,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="J227" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.4">
@@ -12746,16 +12846,16 @@
         <v>315</v>
       </c>
       <c r="C228" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
       <c r="D228" t="s">
         <v>296</v>
       </c>
       <c r="E228" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -12764,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="J228" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.4">
@@ -12772,13 +12872,13 @@
         <v>315</v>
       </c>
       <c r="C229" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="D229" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E229" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -12790,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="J229" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.4">
@@ -12798,13 +12898,13 @@
         <v>315</v>
       </c>
       <c r="C230" t="s">
-        <v>355</v>
+        <v>723</v>
       </c>
       <c r="D230" t="s">
         <v>296</v>
       </c>
       <c r="E230" t="s">
-        <v>356</v>
+        <v>724</v>
       </c>
       <c r="G230">
         <v>0</v>
@@ -12816,7 +12916,7 @@
         <v>0</v>
       </c>
       <c r="J230" t="s">
-        <v>355</v>
+        <v>723</v>
       </c>
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.4">
@@ -12824,16 +12924,16 @@
         <v>315</v>
       </c>
       <c r="C231" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="D231" t="s">
-        <v>740</v>
+        <v>296</v>
       </c>
       <c r="E231" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -12842,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="J231" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.4">
@@ -12850,13 +12950,13 @@
         <v>315</v>
       </c>
       <c r="C232" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="D232" t="s">
         <v>296</v>
       </c>
       <c r="E232" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -12868,7 +12968,7 @@
         <v>0</v>
       </c>
       <c r="J232" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.4">
@@ -12876,13 +12976,13 @@
         <v>315</v>
       </c>
       <c r="C233" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="D233" t="s">
         <v>296</v>
       </c>
       <c r="E233" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -12894,7 +12994,7 @@
         <v>0</v>
       </c>
       <c r="J233" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.4">
@@ -12902,13 +13002,13 @@
         <v>315</v>
       </c>
       <c r="C234" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="D234" t="s">
         <v>296</v>
       </c>
       <c r="E234" t="s">
-        <v>747</v>
+        <v>732</v>
       </c>
       <c r="G234">
         <v>1</v>
@@ -12920,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="J234" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.4">
@@ -12928,16 +13028,16 @@
         <v>315</v>
       </c>
       <c r="C235" t="s">
-        <v>369</v>
+        <v>733</v>
       </c>
       <c r="D235" t="s">
         <v>296</v>
       </c>
       <c r="E235" t="s">
-        <v>370</v>
+        <v>734</v>
       </c>
       <c r="G235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -12946,7 +13046,7 @@
         <v>0</v>
       </c>
       <c r="J235" t="s">
-        <v>371</v>
+        <v>733</v>
       </c>
     </row>
     <row r="236" spans="2:10" x14ac:dyDescent="0.4">
@@ -12954,16 +13054,16 @@
         <v>315</v>
       </c>
       <c r="C236" t="s">
-        <v>372</v>
+        <v>735</v>
       </c>
       <c r="D236" t="s">
         <v>296</v>
       </c>
       <c r="E236" t="s">
-        <v>373</v>
+        <v>736</v>
       </c>
       <c r="G236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -12972,21 +13072,21 @@
         <v>0</v>
       </c>
       <c r="J236" t="s">
-        <v>374</v>
+        <v>735</v>
       </c>
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B237" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C237" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="D237" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E237" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="G237">
         <v>0</v>
@@ -12998,21 +13098,21 @@
         <v>0</v>
       </c>
       <c r="J237" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B238" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C238" t="s">
-        <v>750</v>
+        <v>355</v>
       </c>
       <c r="D238" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E238" t="s">
-        <v>751</v>
+        <v>356</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -13024,21 +13124,21 @@
         <v>0</v>
       </c>
       <c r="J238" t="s">
-        <v>750</v>
+        <v>355</v>
       </c>
     </row>
     <row r="239" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B239" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C239" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="D239" t="s">
-        <v>303</v>
+        <v>740</v>
       </c>
       <c r="E239" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -13050,21 +13150,21 @@
         <v>0</v>
       </c>
       <c r="J239" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B240" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C240" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="D240" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E240" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G240">
         <v>0</v>
@@ -13076,21 +13176,21 @@
         <v>0</v>
       </c>
       <c r="J240" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
     </row>
     <row r="241" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B241" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C241" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="D241" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E241" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="G241">
         <v>0</v>
@@ -13102,24 +13202,24 @@
         <v>0</v>
       </c>
       <c r="J241" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
     </row>
     <row r="242" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B242" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C242" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="D242" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E242" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="G242">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H242">
         <v>0</v>
@@ -13128,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="J242" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.4">
@@ -13136,24 +13236,232 @@
         <v>315</v>
       </c>
       <c r="C243" t="s">
+        <v>369</v>
+      </c>
+      <c r="D243" t="s">
+        <v>296</v>
+      </c>
+      <c r="E243" t="s">
+        <v>370</v>
+      </c>
+      <c r="G243">
+        <v>1</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="244" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B244" t="s">
+        <v>315</v>
+      </c>
+      <c r="C244" t="s">
+        <v>372</v>
+      </c>
+      <c r="D244" t="s">
+        <v>296</v>
+      </c>
+      <c r="E244" t="s">
+        <v>373</v>
+      </c>
+      <c r="G244">
+        <v>1</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="245" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B245" t="s">
+        <v>294</v>
+      </c>
+      <c r="C245" t="s">
+        <v>748</v>
+      </c>
+      <c r="D245" t="s">
+        <v>303</v>
+      </c>
+      <c r="E245" t="s">
+        <v>749</v>
+      </c>
+      <c r="G245">
+        <v>0</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="246" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B246" t="s">
+        <v>294</v>
+      </c>
+      <c r="C246" t="s">
+        <v>750</v>
+      </c>
+      <c r="D246" t="s">
+        <v>303</v>
+      </c>
+      <c r="E246" t="s">
+        <v>751</v>
+      </c>
+      <c r="G246">
+        <v>0</v>
+      </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="247" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B247" t="s">
+        <v>294</v>
+      </c>
+      <c r="C247" t="s">
+        <v>752</v>
+      </c>
+      <c r="D247" t="s">
+        <v>303</v>
+      </c>
+      <c r="E247" t="s">
+        <v>753</v>
+      </c>
+      <c r="G247">
+        <v>0</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+      <c r="J247" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="248" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B248" t="s">
+        <v>294</v>
+      </c>
+      <c r="C248" t="s">
+        <v>754</v>
+      </c>
+      <c r="D248" t="s">
+        <v>303</v>
+      </c>
+      <c r="E248" t="s">
+        <v>755</v>
+      </c>
+      <c r="G248">
+        <v>0</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="249" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B249" t="s">
+        <v>294</v>
+      </c>
+      <c r="C249" t="s">
+        <v>756</v>
+      </c>
+      <c r="D249" t="s">
+        <v>303</v>
+      </c>
+      <c r="E249" t="s">
+        <v>757</v>
+      </c>
+      <c r="G249">
+        <v>0</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="250" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B250" t="s">
+        <v>294</v>
+      </c>
+      <c r="C250" t="s">
+        <v>758</v>
+      </c>
+      <c r="D250" t="s">
+        <v>303</v>
+      </c>
+      <c r="E250" t="s">
+        <v>759</v>
+      </c>
+      <c r="G250">
+        <v>0</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="251" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B251" t="s">
+        <v>315</v>
+      </c>
+      <c r="C251" t="s">
         <v>760</v>
       </c>
-      <c r="D243" t="s">
+      <c r="D251" t="s">
         <v>320</v>
       </c>
-      <c r="E243" t="s">
+      <c r="E251" t="s">
         <v>761</v>
       </c>
-      <c r="G243">
-        <v>1</v>
-      </c>
-      <c r="H243">
-        <v>0</v>
-      </c>
-      <c r="I243">
-        <v>0</v>
-      </c>
-      <c r="J243" t="s">
+      <c r="G251">
+        <v>1</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251" t="s">
         <v>760</v>
       </c>
     </row>
@@ -13164,10 +13472,10 @@
     </sortState>
   </autoFilter>
   <mergeCells count="4">
-    <mergeCell ref="M46:M51"/>
-    <mergeCell ref="M2:M16"/>
-    <mergeCell ref="M33:M38"/>
-    <mergeCell ref="M39:M45"/>
+    <mergeCell ref="M54:M59"/>
+    <mergeCell ref="M2:M18"/>
+    <mergeCell ref="M37:M42"/>
+    <mergeCell ref="M43:M53"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCB0FF5-7CD0-44EA-98D0-BD7564EE9E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB09F3A-2D78-4A01-AC55-59319FC4FCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33390" yWindow="1215" windowWidth="19845" windowHeight="11910" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="2160" yWindow="228" windowWidth="19848" windowHeight="11916" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2810,10 +2810,6 @@
     <t>M00115</t>
   </si>
   <si>
-    <t>누를때만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>동작확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3060,6 +3056,10 @@
   </si>
   <si>
     <t>D00982</t>
+  </si>
+  <si>
+    <t>누를때 on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3172,9 +3172,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -3192,6 +3189,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6763,25 +6763,25 @@
         <v>290</v>
       </c>
       <c r="D1" t="s">
+        <v>916</v>
+      </c>
+      <c r="E1" t="s">
+        <v>915</v>
+      </c>
+      <c r="F1" t="s">
+        <v>914</v>
+      </c>
+      <c r="J1" t="s">
         <v>917</v>
       </c>
-      <c r="E1" t="s">
-        <v>916</v>
-      </c>
-      <c r="F1" t="s">
-        <v>915</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>913</v>
+      </c>
+      <c r="L1" t="s">
+        <v>912</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="K1" t="s">
-        <v>914</v>
-      </c>
-      <c r="L1" t="s">
-        <v>913</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -6812,17 +6812,17 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="L2" s="7" t="s">
+      <c r="K2" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>958</v>
+      <c r="M2" s="12" t="s">
+        <v>957</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -6853,23 +6853,23 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="M3" s="6"/>
+      <c r="M3" s="12"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>862</v>
       </c>
       <c r="C4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D4" t="s">
         <v>303</v>
@@ -6877,23 +6877,23 @@
       <c r="E4" t="s">
         <v>767</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="M4" s="6"/>
+      <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>863</v>
       </c>
       <c r="C5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D5" t="s">
         <v>303</v>
@@ -6901,44 +6901,44 @@
       <c r="E5" t="s">
         <v>400</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>922</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="J5" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>898</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="12"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>864</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>923</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="C6" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11" t="s">
-        <v>923</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>920</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>919</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>899</v>
       </c>
-      <c r="M6" s="6"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
@@ -6965,16 +6965,16 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="K7" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L7" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="M7" s="6"/>
+      <c r="M7" s="12"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
@@ -6984,7 +6984,7 @@
         <v>294</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D8" t="s">
         <v>303</v>
@@ -7001,16 +7001,16 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="M8" s="6"/>
+      <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
@@ -7019,32 +7019,32 @@
       <c r="C9" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="K9" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>967</v>
-      </c>
-      <c r="M9" s="6"/>
+      <c r="K9" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="M9" s="12"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
@@ -7071,16 +7071,16 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="M10" s="6"/>
+      <c r="M10" s="12"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
@@ -7107,16 +7107,16 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="M11" s="6"/>
+      <c r="M11" s="12"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
@@ -7143,16 +7143,16 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L12" s="7" t="s">
+      <c r="K12" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>904</v>
       </c>
-      <c r="M12" s="6"/>
+      <c r="M12" s="12"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
@@ -7179,16 +7179,16 @@
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="M13" s="6"/>
+      <c r="M13" s="12"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
@@ -7198,7 +7198,7 @@
         <v>294</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D14" t="s">
         <v>303</v>
@@ -7215,16 +7215,16 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="M14" s="6"/>
+      <c r="M14" s="12"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
@@ -7233,32 +7233,32 @@
       <c r="C15" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>968</v>
-      </c>
-      <c r="M15" s="6"/>
+      <c r="K15" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="M15" s="12"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
@@ -7285,16 +7285,16 @@
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L16" s="7" t="s">
+      <c r="K16" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>907</v>
       </c>
-      <c r="M16" s="6"/>
+      <c r="M16" s="12"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
@@ -7324,16 +7324,16 @@
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L17" s="7" t="s">
+      <c r="K17" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="M17" s="6"/>
+      <c r="M17" s="12"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
@@ -7360,16 +7360,16 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L18" s="7" t="s">
+      <c r="K18" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="M18" s="6"/>
+      <c r="M18" s="12"/>
     </row>
     <row r="19" spans="1:13" ht="87" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
@@ -7396,28 +7396,28 @@
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="6" t="s">
         <v>834</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="L19" s="7" t="s">
+      <c r="K19" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>910</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
@@ -7447,14 +7447,14 @@
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>929</v>
+      <c r="K22" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -7485,14 +7485,14 @@
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="K23" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>930</v>
+      <c r="K23" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -7523,14 +7523,14 @@
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>931</v>
+      <c r="K24" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>930</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -7546,17 +7546,17 @@
       <c r="E25" t="s">
         <v>764</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>932</v>
+      <c r="K25" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>931</v>
       </c>
       <c r="M25" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -7584,14 +7584,14 @@
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J26" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="K26" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>933</v>
+      <c r="K26" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>932</v>
       </c>
       <c r="M26"/>
     </row>
@@ -7620,14 +7620,14 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>934</v>
+      <c r="K27" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>933</v>
       </c>
       <c r="M27"/>
     </row>
@@ -7659,14 +7659,14 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J28" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>935</v>
+      <c r="K28" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>934</v>
       </c>
       <c r="M28"/>
     </row>
@@ -7698,14 +7698,14 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>936</v>
+      <c r="K29" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>935</v>
       </c>
       <c r="M29"/>
     </row>
@@ -7737,14 +7737,14 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="K30" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>937</v>
+      <c r="K30" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>936</v>
       </c>
       <c r="M30"/>
     </row>
@@ -7761,17 +7761,17 @@
       <c r="E31" t="s">
         <v>762</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="6" t="s">
         <v>763</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>938</v>
+      <c r="K31" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>937</v>
       </c>
       <c r="M31" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -7799,14 +7799,14 @@
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="J32" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="K32" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>939</v>
+      <c r="K32" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>938</v>
       </c>
       <c r="M32"/>
     </row>
@@ -7835,14 +7835,14 @@
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="K33" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>940</v>
+      <c r="K33" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>939</v>
       </c>
       <c r="M33"/>
     </row>
@@ -7859,17 +7859,17 @@
       <c r="E34" t="s">
         <v>768</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="6" t="s">
         <v>769</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>941</v>
+      <c r="K34" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>940</v>
       </c>
       <c r="M34" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -7885,17 +7885,17 @@
       <c r="E35" t="s">
         <v>394</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="K35" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>942</v>
+      <c r="K35" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>941</v>
       </c>
       <c r="M35" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -7911,17 +7911,17 @@
       <c r="E36" t="s">
         <v>770</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J36" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="K36" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>943</v>
+      <c r="K36" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>942</v>
       </c>
       <c r="M36" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -7949,17 +7949,17 @@
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37" s="7" t="s">
-        <v>962</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L37" s="7" t="s">
-        <v>944</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>959</v>
+      <c r="J37" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -7987,16 +7987,16 @@
       <c r="I38">
         <v>0</v>
       </c>
-      <c r="J38" s="7" t="s">
-        <v>963</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L38" s="7" t="s">
-        <v>945</v>
-      </c>
-      <c r="M38" s="6"/>
+      <c r="J38" s="6" t="s">
+        <v>962</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
@@ -8023,16 +8023,16 @@
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>946</v>
-      </c>
-      <c r="M39" s="6"/>
+      <c r="J39" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="M39" s="12"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
@@ -8059,16 +8059,16 @@
       <c r="I40">
         <v>0</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="K40" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>947</v>
-      </c>
-      <c r="M40" s="6"/>
+      <c r="K40" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="M40" s="12"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
@@ -8095,16 +8095,16 @@
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="J41" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="K41" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>948</v>
-      </c>
-      <c r="M41" s="6"/>
+      <c r="K41" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="M41" s="12"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
@@ -8131,16 +8131,16 @@
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J42" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="K42" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="L42" s="7" t="s">
-        <v>949</v>
-      </c>
-      <c r="M42" s="6"/>
+      <c r="K42" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="M42" s="12"/>
     </row>
     <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
@@ -8167,14 +8167,14 @@
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="K43" s="7" t="s">
+      <c r="K43" s="6" t="s">
         <v>888</v>
       </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="6" t="s">
+      <c r="L43" s="6"/>
+      <c r="M43" s="12" t="s">
         <v>894</v>
       </c>
     </row>
@@ -8203,14 +8203,14 @@
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="K44" s="7" t="s">
+      <c r="K44" s="6" t="s">
         <v>889</v>
       </c>
-      <c r="L44" s="7"/>
-      <c r="M44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="12"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
@@ -8237,14 +8237,14 @@
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45" s="7" t="s">
+      <c r="J45" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="K45" s="7" t="s">
+      <c r="K45" s="6" t="s">
         <v>890</v>
       </c>
-      <c r="L45" s="7"/>
-      <c r="M45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="12"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
@@ -8271,14 +8271,14 @@
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="J46" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="K46" s="7" t="s">
+      <c r="K46" s="6" t="s">
         <v>891</v>
       </c>
-      <c r="L46" s="7"/>
-      <c r="M46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="12"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
@@ -8305,14 +8305,14 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47" s="7" t="s">
-        <v>960</v>
-      </c>
-      <c r="K47" s="7" t="s">
+      <c r="J47" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="K47" s="6" t="s">
         <v>892</v>
       </c>
-      <c r="L47" s="7"/>
-      <c r="M47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="12"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
@@ -8339,14 +8339,14 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48" s="7" t="s">
-        <v>961</v>
-      </c>
-      <c r="K48" s="7" t="s">
+      <c r="J48" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="K48" s="6" t="s">
         <v>893</v>
       </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="12"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B49" s="4" t="s">
@@ -8359,7 +8359,7 @@
         <v>296</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4">
@@ -8371,14 +8371,14 @@
       <c r="I49" s="4">
         <v>0</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="8" t="s">
         <v>713</v>
       </c>
-      <c r="K49" s="9" t="s">
-        <v>969</v>
-      </c>
-      <c r="L49" s="7"/>
-      <c r="M49" s="6"/>
+      <c r="K49" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="L49" s="6"/>
+      <c r="M49" s="12"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B50" s="4" t="s">
@@ -8391,7 +8391,7 @@
         <v>296</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4">
@@ -8403,14 +8403,14 @@
       <c r="I50" s="4">
         <v>0</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="J50" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="K50" s="9" t="s">
-        <v>970</v>
-      </c>
-      <c r="L50" s="7"/>
-      <c r="M50" s="6"/>
+      <c r="K50" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="L50" s="6"/>
+      <c r="M50" s="12"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B51" s="4" t="s">
@@ -8423,7 +8423,7 @@
         <v>296</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4">
@@ -8435,14 +8435,14 @@
       <c r="I51" s="4">
         <v>0</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="J51" s="8" t="s">
         <v>725</v>
       </c>
-      <c r="K51" s="9" t="s">
-        <v>971</v>
-      </c>
-      <c r="L51" s="7"/>
-      <c r="M51" s="6"/>
+      <c r="K51" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="L51" s="6"/>
+      <c r="M51" s="12"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B52" s="4" t="s">
@@ -8455,7 +8455,7 @@
         <v>296</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4">
@@ -8467,14 +8467,14 @@
       <c r="I52" s="4">
         <v>0</v>
       </c>
-      <c r="J52" s="9" t="s">
+      <c r="J52" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="K52" s="9" t="s">
-        <v>972</v>
-      </c>
-      <c r="L52" s="7"/>
-      <c r="M52" s="6"/>
+      <c r="K52" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="L52" s="6"/>
+      <c r="M52" s="12"/>
     </row>
     <row r="53" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
@@ -8501,14 +8501,14 @@
       <c r="I53">
         <v>0</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="J53" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="K53" s="12" t="s">
-        <v>973</v>
-      </c>
-      <c r="L53" s="9"/>
-      <c r="M53" s="6"/>
+      <c r="K53" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="L53" s="8"/>
+      <c r="M53" s="12"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
@@ -8535,15 +8535,15 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54" s="7" t="s">
+      <c r="J54" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="K54" s="9" t="s">
-        <v>974</v>
-      </c>
-      <c r="L54" s="9"/>
-      <c r="M54" s="6" t="s">
-        <v>954</v>
+      <c r="K54" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="L54" s="8"/>
+      <c r="M54" s="12" t="s">
+        <v>953</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.4">
@@ -8571,14 +8571,14 @@
       <c r="I55">
         <v>0</v>
       </c>
-      <c r="J55" s="7" t="s">
-        <v>950</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>975</v>
-      </c>
-      <c r="L55" s="9"/>
-      <c r="M55" s="6"/>
+      <c r="J55" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="L55" s="8"/>
+      <c r="M55" s="12"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
@@ -8605,14 +8605,14 @@
       <c r="I56">
         <v>0</v>
       </c>
-      <c r="J56" s="7" t="s">
-        <v>951</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>976</v>
-      </c>
-      <c r="L56" s="9"/>
-      <c r="M56" s="6"/>
+      <c r="J56" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="L56" s="8"/>
+      <c r="M56" s="12"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
@@ -8639,16 +8639,16 @@
       <c r="I57">
         <v>0</v>
       </c>
-      <c r="J57" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>977</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>980</v>
-      </c>
-      <c r="M57" s="6"/>
+      <c r="J57" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="M57" s="12"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
@@ -8675,16 +8675,16 @@
       <c r="I58">
         <v>0</v>
       </c>
-      <c r="J58" s="7" t="s">
-        <v>953</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>978</v>
-      </c>
-      <c r="L58" s="9" t="s">
-        <v>981</v>
-      </c>
-      <c r="M58" s="6"/>
+      <c r="J58" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="M58" s="12"/>
     </row>
     <row r="59" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
@@ -8711,20 +8711,20 @@
       <c r="I59">
         <v>0</v>
       </c>
-      <c r="J59" s="7" t="s">
-        <v>956</v>
-      </c>
-      <c r="K59" s="9" t="s">
-        <v>979</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>982</v>
-      </c>
-      <c r="M59" s="6"/>
+      <c r="J59" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="M59" s="12"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.4">

--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB09F3A-2D78-4A01-AC55-59319FC4FCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F97AE8D-80B4-4154-BABB-76D38EE50384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="228" windowWidth="19848" windowHeight="11916" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="28395" yWindow="1665" windowWidth="19845" windowHeight="11910" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6968,10 +6968,10 @@
       <c r="J7" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="8" t="s">
         <v>900</v>
       </c>
       <c r="M7" s="12"/>
@@ -7004,10 +7004,10 @@
       <c r="J8" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="8" t="s">
         <v>901</v>
       </c>
       <c r="M8" s="12"/>
@@ -7074,10 +7074,10 @@
       <c r="J10" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="8" t="s">
         <v>902</v>
       </c>
       <c r="M10" s="12"/>
@@ -7110,10 +7110,10 @@
       <c r="J11" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="8" t="s">
         <v>903</v>
       </c>
       <c r="M11" s="12"/>
@@ -7146,10 +7146,10 @@
       <c r="J12" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="8" t="s">
         <v>904</v>
       </c>
       <c r="M12" s="12"/>
@@ -7182,10 +7182,10 @@
       <c r="J13" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="8" t="s">
         <v>905</v>
       </c>
       <c r="M13" s="12"/>
@@ -7218,10 +7218,10 @@
       <c r="J14" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="8" t="s">
         <v>906</v>
       </c>
       <c r="M14" s="12"/>
@@ -7288,10 +7288,10 @@
       <c r="J16" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="8" t="s">
         <v>907</v>
       </c>
       <c r="M16" s="12"/>
@@ -7327,10 +7327,10 @@
       <c r="J17" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="8" t="s">
         <v>908</v>
       </c>
       <c r="M17" s="12"/>
@@ -7363,10 +7363,10 @@
       <c r="J18" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="8" t="s">
         <v>909</v>
       </c>
       <c r="M18" s="12"/>
@@ -7399,10 +7399,10 @@
       <c r="J19" s="6" t="s">
         <v>834</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="8" t="s">
         <v>910</v>
       </c>
       <c r="M19" s="5" t="s">

--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F97AE8D-80B4-4154-BABB-76D38EE50384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D6A29-0F35-4700-9DDA-01FB1E8860E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28395" yWindow="1665" windowWidth="19845" windowHeight="11910" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="1236" yWindow="1116" windowWidth="19848" windowHeight="11916" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D6A29-0F35-4700-9DDA-01FB1E8860E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5E0EEC-35AE-46B0-805A-B6D6D698A75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1236" yWindow="1116" windowWidth="19848" windowHeight="11916" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="30990" yWindow="1125" windowWidth="19845" windowHeight="11910" activeTab="5" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet4!$A$1:$M$1</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="1004">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -3059,6 +3060,90 @@
   </si>
   <si>
     <t>누를때 on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR 온도입력모듈 오류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">외기온도 센서 단선 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전기실 온도 센서 단선 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에어컨01 온도 센서 단선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에어컨02 온도 센서 단선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTD 입력모듈 에러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR01 휀 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR02 휀 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TR03 휀 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배기 현장 자동 모드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배기 현장 수동 모드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배기 방재실 모드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배기휀 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배기 운전 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급기 현장 자동 모드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급기 현장 수동 모드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급기 방재실 모드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급기휀 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급기 운전 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급기 휀 써멀 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배기휀 써멀 동작</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6739,6 +6824,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2836F51-32CE-4EC5-A2A6-D682AE17D0BB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M251"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -13478,7 +13566,8 @@
     <mergeCell ref="M43:M53"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="16" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14643,4 +14732,556 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC195326-45FC-43A2-B143-9923CE975B7F}">
+  <dimension ref="A2:H22"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>843</v>
+      </c>
+      <c r="B4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4" t="s">
+        <v>456</v>
+      </c>
+      <c r="D4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>859</v>
+      </c>
+      <c r="C5" t="s">
+        <v>765</v>
+      </c>
+      <c r="D5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>845</v>
+      </c>
+      <c r="B6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>846</v>
+      </c>
+      <c r="B7" t="s">
+        <v>294</v>
+      </c>
+      <c r="C7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>849</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>549</v>
+      </c>
+      <c r="D8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>851</v>
+      </c>
+      <c r="B9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" t="s">
+        <v>555</v>
+      </c>
+      <c r="D9" t="s">
+        <v>303</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>853</v>
+      </c>
+      <c r="B10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" t="s">
+        <v>563</v>
+      </c>
+      <c r="D10" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>858</v>
+      </c>
+      <c r="C11" t="s">
+        <v>763</v>
+      </c>
+      <c r="D11" t="s">
+        <v>303</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>855</v>
+      </c>
+      <c r="B12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C12" t="s">
+        <v>567</v>
+      </c>
+      <c r="D12" t="s">
+        <v>303</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>856</v>
+      </c>
+      <c r="B13" t="s">
+        <v>294</v>
+      </c>
+      <c r="C13" t="s">
+        <v>571</v>
+      </c>
+      <c r="D13" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>865</v>
+      </c>
+      <c r="C14" t="s">
+        <v>769</v>
+      </c>
+      <c r="D14" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>866</v>
+      </c>
+      <c r="C15" t="s">
+        <v>396</v>
+      </c>
+      <c r="D15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>867</v>
+      </c>
+      <c r="C16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D16" t="s">
+        <v>303</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>886</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>829</v>
+      </c>
+      <c r="D17" t="s">
+        <v>303</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>882</v>
+      </c>
+      <c r="B18" t="s">
+        <v>771</v>
+      </c>
+      <c r="C18" t="s">
+        <v>808</v>
+      </c>
+      <c r="D18" t="s">
+        <v>303</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>962</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>874</v>
+      </c>
+      <c r="B19" t="s">
+        <v>771</v>
+      </c>
+      <c r="C19" t="s">
+        <v>775</v>
+      </c>
+      <c r="D19" t="s">
+        <v>303</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>876</v>
+      </c>
+      <c r="B20" t="s">
+        <v>771</v>
+      </c>
+      <c r="C20" t="s">
+        <v>784</v>
+      </c>
+      <c r="D20" t="s">
+        <v>303</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>878</v>
+      </c>
+      <c r="B21" t="s">
+        <v>771</v>
+      </c>
+      <c r="C21" t="s">
+        <v>793</v>
+      </c>
+      <c r="D21" t="s">
+        <v>303</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>880</v>
+      </c>
+      <c r="B22" t="s">
+        <v>771</v>
+      </c>
+      <c r="C22" t="s">
+        <v>802</v>
+      </c>
+      <c r="D22" t="s">
+        <v>303</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>987</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5E0EEC-35AE-46B0-805A-B6D6D698A75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F66E2A1-AE05-4AF9-82EA-E825E8913B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30990" yWindow="1125" windowWidth="19845" windowHeight="11910" activeTab="5" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="2985" yWindow="2220" windowWidth="23415" windowHeight="11295" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="1004">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -3593,12 +3593,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39EDAB4-4F9F-43D7-A646-D97796DCEFC3}">
   <dimension ref="B2:G21"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>20</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>23</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>26</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>29</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>31</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>34</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>37</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>40</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>43</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>46</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>49</v>
       </c>
@@ -3967,16 +3967,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F70ADEE-C5E8-4BF1-B083-ED91F0E7FD88}">
   <dimension ref="A1:E150"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>287</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>56</v>
       </c>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>57</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>58</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>59</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>60</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>61</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>62</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>63</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>64</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>65</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>66</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>67</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>68</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>69</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>70</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>71</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>72</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>73</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>74</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>75</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>76</v>
       </c>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>77</v>
       </c>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>78</v>
       </c>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>79</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>80</v>
       </c>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>81</v>
       </c>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>82</v>
       </c>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>83</v>
       </c>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="2:5" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>84</v>
       </c>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>85</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>86</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>131</v>
       </c>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>56</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>57</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>58</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>59</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>60</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>61</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>62</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>63</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>64</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>65</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>66</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>67</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>68</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>69</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>70</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>71</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>72</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>73</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>74</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>75</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>76</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>77</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>78</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>79</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>80</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>81</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>82</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>83</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>84</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>85</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>86</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>132</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>133</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>134</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>170</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>172</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>174</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
         <v>186</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>187</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>56</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>57</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>58</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>59</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>60</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>61</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>62</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>63</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>64</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>65</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>66</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>67</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>68</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
         <v>69</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>70</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>71</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>72</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>73</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>74</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>75</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>76</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>77</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>78</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>79</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>80</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>81</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>82</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>83</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>84</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>85</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>86</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>132</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>133</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>134</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>170</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>172</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>174</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
         <v>226</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>237</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="113" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>56</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="114" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>57</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="115" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>58</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="116" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>59</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="117" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>60</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="118" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>61</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="119" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>62</v>
       </c>
@@ -5097,7 +5097,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="120" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>63</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="121" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>64</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="122" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>65</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="123" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>66</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="124" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>67</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="125" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>68</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="126" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>69</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="127" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>70</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="128" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>71</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>72</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>73</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>74</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>75</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>76</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>77</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>78</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>79</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>80</v>
       </c>
@@ -5262,7 +5262,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>81</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>82</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>83</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>84</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>85</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>86</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>132</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>133</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>134</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>170</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>172</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>174</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
         <v>286</v>
       </c>
@@ -5375,19 +5375,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8CB00BD-499D-452F-8901-A9EC4B3FAAEA}">
   <dimension ref="A1:J72"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>294</v>
       </c>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>294</v>
       </c>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
@@ -5464,7 +5464,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
@@ -5481,7 +5481,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
@@ -5498,7 +5498,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>398</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>398</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>398</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>315</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>315</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>315</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>315</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>315</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>294</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>294</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>294</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>294</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>294</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>294</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>294</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>294</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>294</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>315</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>315</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>315</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>315</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>315</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>315</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>294</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>294</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>294</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>294</v>
       </c>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>294</v>
       </c>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>294</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>294</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>294</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>315</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>294</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>294</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>315</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>315</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>315</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>315</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>315</v>
       </c>
@@ -6507,7 +6507,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>315</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>315</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>315</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>315</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>315</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>315</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>315</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>315</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>315</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>315</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>315</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>315</v>
       </c>
@@ -6827,23 +6827,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M251"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q251"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.25" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="49.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="49.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.3984375" style="5" customWidth="1"/>
-    <col min="14" max="14" width="16.796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>766</v>
       </c>
@@ -6872,7 +6875,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>860</v>
       </c>
@@ -6912,8 +6915,17 @@
       <c r="M2" s="12" t="s">
         <v>957</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="O2" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>861</v>
       </c>
@@ -6951,8 +6963,17 @@
         <v>896</v>
       </c>
       <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="O3" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>862</v>
       </c>
@@ -6975,8 +6996,17 @@
         <v>897</v>
       </c>
       <c r="M4" s="12"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="O4" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>863</v>
       </c>
@@ -6999,8 +7029,17 @@
         <v>898</v>
       </c>
       <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="O5" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>864</v>
       </c>
@@ -7027,8 +7066,17 @@
         <v>899</v>
       </c>
       <c r="M6" s="12"/>
-    </row>
-    <row r="7" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="O6" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>838</v>
       </c>
@@ -7063,8 +7111,17 @@
         <v>900</v>
       </c>
       <c r="M7" s="12"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="O7" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>840</v>
       </c>
@@ -7099,8 +7156,17 @@
         <v>901</v>
       </c>
       <c r="M8" s="12"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="O8" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>294</v>
       </c>
@@ -7134,7 +7200,7 @@
       </c>
       <c r="M9" s="12"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>842</v>
       </c>
@@ -7170,7 +7236,7 @@
       </c>
       <c r="M10" s="12"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>844</v>
       </c>
@@ -7206,7 +7272,7 @@
       </c>
       <c r="M11" s="12"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>847</v>
       </c>
@@ -7242,7 +7308,7 @@
       </c>
       <c r="M12" s="12"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>848</v>
       </c>
@@ -7278,7 +7344,7 @@
       </c>
       <c r="M13" s="12"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>850</v>
       </c>
@@ -7314,7 +7380,7 @@
       </c>
       <c r="M14" s="12"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>294</v>
       </c>
@@ -7348,7 +7414,7 @@
       </c>
       <c r="M15" s="12"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>852</v>
       </c>
@@ -7384,7 +7450,7 @@
       </c>
       <c r="M16" s="12"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>854</v>
       </c>
@@ -7423,7 +7489,7 @@
       </c>
       <c r="M17" s="12"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>857</v>
       </c>
@@ -7459,7 +7525,7 @@
       </c>
       <c r="M18" s="12"/>
     </row>
-    <row r="19" spans="1:13" ht="87" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>887</v>
       </c>
@@ -7497,17 +7563,17 @@
         <v>956</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>839</v>
       </c>
@@ -7545,7 +7611,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>841</v>
       </c>
@@ -7583,7 +7649,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>843</v>
       </c>
@@ -7621,7 +7687,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>859</v>
       </c>
@@ -7647,7 +7713,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>845</v>
       </c>
@@ -7683,7 +7749,7 @@
       </c>
       <c r="M26"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>846</v>
       </c>
@@ -7719,7 +7785,7 @@
       </c>
       <c r="M27"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>849</v>
       </c>
@@ -7758,7 +7824,7 @@
       </c>
       <c r="M28"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>851</v>
       </c>
@@ -7797,7 +7863,7 @@
       </c>
       <c r="M29"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>853</v>
       </c>
@@ -7836,7 +7902,7 @@
       </c>
       <c r="M30"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>858</v>
       </c>
@@ -7862,7 +7928,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>855</v>
       </c>
@@ -7898,7 +7964,7 @@
       </c>
       <c r="M32"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>856</v>
       </c>
@@ -7934,7 +8000,7 @@
       </c>
       <c r="M33"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>865</v>
       </c>
@@ -7960,7 +8026,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>866</v>
       </c>
@@ -7986,7 +8052,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>867</v>
       </c>
@@ -8012,7 +8078,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>886</v>
       </c>
@@ -8050,7 +8116,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>882</v>
       </c>
@@ -8086,7 +8152,7 @@
       </c>
       <c r="M38" s="12"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>874</v>
       </c>
@@ -8122,7 +8188,7 @@
       </c>
       <c r="M39" s="12"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>876</v>
       </c>
@@ -8158,7 +8224,7 @@
       </c>
       <c r="M40" s="12"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>878</v>
       </c>
@@ -8194,7 +8260,7 @@
       </c>
       <c r="M41" s="12"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>880</v>
       </c>
@@ -8230,7 +8296,7 @@
       </c>
       <c r="M42" s="12"/>
     </row>
-    <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>868</v>
       </c>
@@ -8266,7 +8332,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>869</v>
       </c>
@@ -8300,7 +8366,7 @@
       <c r="L44" s="6"/>
       <c r="M44" s="12"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>870</v>
       </c>
@@ -8334,7 +8400,7 @@
       <c r="L45" s="6"/>
       <c r="M45" s="12"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>871</v>
       </c>
@@ -8368,7 +8434,7 @@
       <c r="L46" s="6"/>
       <c r="M46" s="12"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>872</v>
       </c>
@@ -8402,7 +8468,7 @@
       <c r="L47" s="6"/>
       <c r="M47" s="12"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>873</v>
       </c>
@@ -8436,7 +8502,7 @@
       <c r="L48" s="6"/>
       <c r="M48" s="12"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>771</v>
       </c>
@@ -8468,7 +8534,7 @@
       <c r="L49" s="6"/>
       <c r="M49" s="12"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>771</v>
       </c>
@@ -8500,7 +8566,7 @@
       <c r="L50" s="6"/>
       <c r="M50" s="12"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>771</v>
       </c>
@@ -8532,7 +8598,7 @@
       <c r="L51" s="6"/>
       <c r="M51" s="12"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>771</v>
       </c>
@@ -8564,7 +8630,7 @@
       <c r="L52" s="6"/>
       <c r="M52" s="12"/>
     </row>
-    <row r="53" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>875</v>
       </c>
@@ -8598,7 +8664,7 @@
       <c r="L53" s="8"/>
       <c r="M53" s="12"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>877</v>
       </c>
@@ -8634,7 +8700,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>879</v>
       </c>
@@ -8668,7 +8734,7 @@
       <c r="L55" s="8"/>
       <c r="M55" s="12"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>881</v>
       </c>
@@ -8702,7 +8768,7 @@
       <c r="L56" s="8"/>
       <c r="M56" s="12"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>883</v>
       </c>
@@ -8738,7 +8804,7 @@
       </c>
       <c r="M57" s="12"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>884</v>
       </c>
@@ -8774,7 +8840,7 @@
       </c>
       <c r="M58" s="12"/>
     </row>
-    <row r="59" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" ht="82.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>885</v>
       </c>
@@ -8810,12 +8876,12 @@
       </c>
       <c r="M59" s="12"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>315</v>
       </c>
@@ -8841,7 +8907,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>294</v>
       </c>
@@ -8867,7 +8933,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>294</v>
       </c>
@@ -8893,7 +8959,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>294</v>
       </c>
@@ -8919,7 +8985,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>294</v>
       </c>
@@ -8945,7 +9011,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>294</v>
       </c>
@@ -8971,7 +9037,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>294</v>
       </c>
@@ -8997,7 +9063,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>315</v>
       </c>
@@ -9020,7 +9086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>294</v>
       </c>
@@ -9046,7 +9112,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>294</v>
       </c>
@@ -9072,7 +9138,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>294</v>
       </c>
@@ -9098,7 +9164,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>294</v>
       </c>
@@ -9124,7 +9190,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>294</v>
       </c>
@@ -9150,7 +9216,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>294</v>
       </c>
@@ -9176,7 +9242,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
         <v>315</v>
       </c>
@@ -9202,7 +9268,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>294</v>
       </c>
@@ -9228,7 +9294,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>294</v>
       </c>
@@ -9254,7 +9320,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>294</v>
       </c>
@@ -9283,7 +9349,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>294</v>
       </c>
@@ -9309,7 +9375,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>294</v>
       </c>
@@ -9335,7 +9401,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>294</v>
       </c>
@@ -9364,7 +9430,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>294</v>
       </c>
@@ -9390,7 +9456,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>294</v>
       </c>
@@ -9416,7 +9482,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>294</v>
       </c>
@@ -9442,7 +9508,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>294</v>
       </c>
@@ -9471,7 +9537,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>294</v>
       </c>
@@ -9497,7 +9563,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>294</v>
       </c>
@@ -9523,7 +9589,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>294</v>
       </c>
@@ -9549,7 +9615,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>294</v>
       </c>
@@ -9575,7 +9641,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>294</v>
       </c>
@@ -9601,7 +9667,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>315</v>
       </c>
@@ -9624,7 +9690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>315</v>
       </c>
@@ -9647,7 +9713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>315</v>
       </c>
@@ -9670,7 +9736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>294</v>
       </c>
@@ -9696,7 +9762,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>294</v>
       </c>
@@ -9722,7 +9788,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>294</v>
       </c>
@@ -9748,7 +9814,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>294</v>
       </c>
@@ -9774,7 +9840,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>294</v>
       </c>
@@ -9800,7 +9866,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>294</v>
       </c>
@@ -9826,7 +9892,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>294</v>
       </c>
@@ -9852,7 +9918,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>294</v>
       </c>
@@ -9878,7 +9944,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>294</v>
       </c>
@@ -9904,7 +9970,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>294</v>
       </c>
@@ -9930,7 +9996,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>294</v>
       </c>
@@ -9956,7 +10022,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>294</v>
       </c>
@@ -9982,7 +10048,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>294</v>
       </c>
@@ -10008,7 +10074,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>294</v>
       </c>
@@ -10034,7 +10100,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>294</v>
       </c>
@@ -10060,7 +10126,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>294</v>
       </c>
@@ -10083,7 +10149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>294</v>
       </c>
@@ -10106,7 +10172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>294</v>
       </c>
@@ -10132,7 +10198,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>294</v>
       </c>
@@ -10158,7 +10224,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>294</v>
       </c>
@@ -10184,7 +10250,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>294</v>
       </c>
@@ -10210,7 +10276,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>294</v>
       </c>
@@ -10236,7 +10302,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>294</v>
       </c>
@@ -10262,7 +10328,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>294</v>
       </c>
@@ -10288,7 +10354,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>294</v>
       </c>
@@ -10314,7 +10380,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>294</v>
       </c>
@@ -10340,7 +10406,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>294</v>
       </c>
@@ -10366,7 +10432,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>294</v>
       </c>
@@ -10392,7 +10458,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>294</v>
       </c>
@@ -10418,7 +10484,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>294</v>
       </c>
@@ -10444,7 +10510,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>294</v>
       </c>
@@ -10470,7 +10536,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>294</v>
       </c>
@@ -10496,7 +10562,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>294</v>
       </c>
@@ -10522,7 +10588,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>294</v>
       </c>
@@ -10548,7 +10614,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>294</v>
       </c>
@@ -10574,7 +10640,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>294</v>
       </c>
@@ -10600,7 +10666,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>294</v>
       </c>
@@ -10626,7 +10692,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>294</v>
       </c>
@@ -10655,7 +10721,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>294</v>
       </c>
@@ -10681,7 +10747,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>294</v>
       </c>
@@ -10707,7 +10773,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>294</v>
       </c>
@@ -10736,7 +10802,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>294</v>
       </c>
@@ -10762,7 +10828,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>294</v>
       </c>
@@ -10788,7 +10854,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>294</v>
       </c>
@@ -10814,7 +10880,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>294</v>
       </c>
@@ -10843,7 +10909,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>294</v>
       </c>
@@ -10872,7 +10938,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>294</v>
       </c>
@@ -10898,7 +10964,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>294</v>
       </c>
@@ -10924,7 +10990,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>294</v>
       </c>
@@ -10950,7 +11016,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>294</v>
       </c>
@@ -10976,7 +11042,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>315</v>
       </c>
@@ -11002,7 +11068,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>315</v>
       </c>
@@ -11028,7 +11094,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>294</v>
       </c>
@@ -11054,7 +11120,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>294</v>
       </c>
@@ -11080,7 +11146,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>294</v>
       </c>
@@ -11106,7 +11172,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>294</v>
       </c>
@@ -11132,7 +11198,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>294</v>
       </c>
@@ -11158,7 +11224,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>294</v>
       </c>
@@ -11184,7 +11250,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>294</v>
       </c>
@@ -11210,7 +11276,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>294</v>
       </c>
@@ -11236,7 +11302,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>294</v>
       </c>
@@ -11262,7 +11328,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
         <v>294</v>
       </c>
@@ -11288,7 +11354,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
         <v>294</v>
       </c>
@@ -11314,7 +11380,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
         <v>294</v>
       </c>
@@ -11340,7 +11406,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B170" t="s">
         <v>294</v>
       </c>
@@ -11366,7 +11432,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>294</v>
       </c>
@@ -11392,7 +11458,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
         <v>294</v>
       </c>
@@ -11418,7 +11484,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>294</v>
       </c>
@@ -11444,7 +11510,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>294</v>
       </c>
@@ -11470,7 +11536,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>294</v>
       </c>
@@ -11496,7 +11562,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>294</v>
       </c>
@@ -11522,7 +11588,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>294</v>
       </c>
@@ -11548,7 +11614,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>294</v>
       </c>
@@ -11574,7 +11640,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>294</v>
       </c>
@@ -11600,7 +11666,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>294</v>
       </c>
@@ -11626,7 +11692,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>294</v>
       </c>
@@ -11652,7 +11718,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>315</v>
       </c>
@@ -11678,7 +11744,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>294</v>
       </c>
@@ -11704,7 +11770,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>294</v>
       </c>
@@ -11730,7 +11796,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>294</v>
       </c>
@@ -11756,7 +11822,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>294</v>
       </c>
@@ -11782,7 +11848,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>294</v>
       </c>
@@ -11808,7 +11874,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>294</v>
       </c>
@@ -11834,7 +11900,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>294</v>
       </c>
@@ -11860,7 +11926,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>294</v>
       </c>
@@ -11886,7 +11952,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>294</v>
       </c>
@@ -11912,7 +11978,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>294</v>
       </c>
@@ -11938,7 +12004,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>294</v>
       </c>
@@ -11964,7 +12030,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>315</v>
       </c>
@@ -11993,7 +12059,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>315</v>
       </c>
@@ -12022,7 +12088,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>315</v>
       </c>
@@ -12051,7 +12117,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>315</v>
       </c>
@@ -12080,7 +12146,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>315</v>
       </c>
@@ -12109,7 +12175,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>315</v>
       </c>
@@ -12138,7 +12204,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>315</v>
       </c>
@@ -12167,7 +12233,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>315</v>
       </c>
@@ -12196,7 +12262,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>315</v>
       </c>
@@ -12225,7 +12291,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>315</v>
       </c>
@@ -12254,7 +12320,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>315</v>
       </c>
@@ -12283,7 +12349,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>315</v>
       </c>
@@ -12312,7 +12378,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>315</v>
       </c>
@@ -12341,7 +12407,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>315</v>
       </c>
@@ -12370,7 +12436,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>315</v>
       </c>
@@ -12399,7 +12465,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>315</v>
       </c>
@@ -12428,7 +12494,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>315</v>
       </c>
@@ -12457,7 +12523,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>315</v>
       </c>
@@ -12486,7 +12552,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>315</v>
       </c>
@@ -12515,7 +12581,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>315</v>
       </c>
@@ -12544,7 +12610,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>315</v>
       </c>
@@ -12573,7 +12639,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>315</v>
       </c>
@@ -12602,7 +12668,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>315</v>
       </c>
@@ -12631,7 +12697,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>315</v>
       </c>
@@ -12660,7 +12726,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>315</v>
       </c>
@@ -12689,7 +12755,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>315</v>
       </c>
@@ -12718,7 +12784,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>315</v>
       </c>
@@ -12747,7 +12813,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>315</v>
       </c>
@@ -12776,7 +12842,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B222" t="s">
         <v>315</v>
       </c>
@@ -12802,7 +12868,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
         <v>294</v>
       </c>
@@ -12825,7 +12891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B224" t="s">
         <v>315</v>
       </c>
@@ -12851,7 +12917,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B225" t="s">
         <v>315</v>
       </c>
@@ -12877,7 +12943,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>315</v>
       </c>
@@ -12903,7 +12969,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>315</v>
       </c>
@@ -12929,7 +12995,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B228" t="s">
         <v>315</v>
       </c>
@@ -12955,7 +13021,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>315</v>
       </c>
@@ -12981,7 +13047,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
         <v>315</v>
       </c>
@@ -13007,7 +13073,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
         <v>315</v>
       </c>
@@ -13033,7 +13099,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
         <v>315</v>
       </c>
@@ -13059,7 +13125,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B233" t="s">
         <v>315</v>
       </c>
@@ -13085,7 +13151,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B234" t="s">
         <v>315</v>
       </c>
@@ -13111,7 +13177,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B235" t="s">
         <v>315</v>
       </c>
@@ -13137,7 +13203,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B236" t="s">
         <v>315</v>
       </c>
@@ -13163,7 +13229,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>315</v>
       </c>
@@ -13189,7 +13255,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>315</v>
       </c>
@@ -13215,7 +13281,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>315</v>
       </c>
@@ -13241,7 +13307,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>315</v>
       </c>
@@ -13267,7 +13333,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B241" t="s">
         <v>315</v>
       </c>
@@ -13293,7 +13359,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B242" t="s">
         <v>315</v>
       </c>
@@ -13319,7 +13385,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>315</v>
       </c>
@@ -13345,7 +13411,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B244" t="s">
         <v>315</v>
       </c>
@@ -13371,7 +13437,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B245" t="s">
         <v>294</v>
       </c>
@@ -13397,7 +13463,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B246" t="s">
         <v>294</v>
       </c>
@@ -13423,7 +13489,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="247" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="247" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B247" t="s">
         <v>294</v>
       </c>
@@ -13449,7 +13515,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="248" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B248" t="s">
         <v>294</v>
       </c>
@@ -13475,7 +13541,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B249" t="s">
         <v>294</v>
       </c>
@@ -13501,7 +13567,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B250" t="s">
         <v>294</v>
       </c>
@@ -13527,7 +13593,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B251" t="s">
         <v>315</v>
       </c>
@@ -13574,17 +13640,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F669793C-4477-44E3-ACB7-6FC96DB8D598}">
   <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="2.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>771</v>
       </c>
@@ -13610,7 +13676,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>771</v>
       </c>
@@ -13636,7 +13702,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>771</v>
       </c>
@@ -13662,7 +13728,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>771</v>
       </c>
@@ -13688,7 +13754,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>771</v>
       </c>
@@ -13714,7 +13780,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>771</v>
       </c>
@@ -13740,7 +13806,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>771</v>
       </c>
@@ -13766,7 +13832,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>771</v>
       </c>
@@ -13792,7 +13858,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>771</v>
       </c>
@@ -13818,7 +13884,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>771</v>
       </c>
@@ -13844,7 +13910,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>771</v>
       </c>
@@ -13870,7 +13936,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>771</v>
       </c>
@@ -13896,7 +13962,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>771</v>
       </c>
@@ -13922,7 +13988,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>771</v>
       </c>
@@ -13948,7 +14014,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>771</v>
       </c>
@@ -13974,7 +14040,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>771</v>
       </c>
@@ -14000,7 +14066,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>771</v>
       </c>
@@ -14026,7 +14092,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>771</v>
       </c>
@@ -14052,7 +14118,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>771</v>
       </c>
@@ -14078,7 +14144,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>771</v>
       </c>
@@ -14104,7 +14170,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>771</v>
       </c>
@@ -14130,7 +14196,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>771</v>
       </c>
@@ -14156,7 +14222,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>771</v>
       </c>
@@ -14182,7 +14248,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>771</v>
       </c>
@@ -14208,7 +14274,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>771</v>
       </c>
@@ -14234,7 +14300,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>771</v>
       </c>
@@ -14260,7 +14326,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>771</v>
       </c>
@@ -14286,7 +14352,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>771</v>
       </c>
@@ -14312,7 +14378,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>771</v>
       </c>
@@ -14338,7 +14404,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>771</v>
       </c>
@@ -14364,7 +14430,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>771</v>
       </c>
@@ -14390,7 +14456,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>771</v>
       </c>
@@ -14416,7 +14482,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>771</v>
       </c>
@@ -14442,7 +14508,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>771</v>
       </c>
@@ -14468,7 +14534,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>771</v>
       </c>
@@ -14494,7 +14560,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>771</v>
       </c>
@@ -14520,7 +14586,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>771</v>
       </c>
@@ -14546,7 +14612,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>771</v>
       </c>
@@ -14572,7 +14638,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>771</v>
       </c>
@@ -14598,7 +14664,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>771</v>
       </c>
@@ -14624,7 +14690,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>771</v>
       </c>
@@ -14650,7 +14716,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>771</v>
       </c>
@@ -14676,7 +14742,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>771</v>
       </c>
@@ -14702,7 +14768,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>771</v>
       </c>
@@ -14737,19 +14803,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC195326-45FC-43A2-B143-9923CE975B7F}">
   <dimension ref="A2:H22"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>839</v>
       </c>
@@ -14775,7 +14841,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>841</v>
       </c>
@@ -14801,7 +14867,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>843</v>
       </c>
@@ -14827,7 +14893,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>859</v>
       </c>
@@ -14850,7 +14916,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>845</v>
       </c>
@@ -14876,7 +14942,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>846</v>
       </c>
@@ -14902,7 +14968,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>849</v>
       </c>
@@ -14928,7 +14994,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>851</v>
       </c>
@@ -14954,7 +15020,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>853</v>
       </c>
@@ -14980,7 +15046,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>858</v>
       </c>
@@ -15003,7 +15069,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>855</v>
       </c>
@@ -15029,7 +15095,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>856</v>
       </c>
@@ -15055,7 +15121,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>865</v>
       </c>
@@ -15078,7 +15144,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>866</v>
       </c>
@@ -15101,7 +15167,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>867</v>
       </c>
@@ -15124,7 +15190,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>886</v>
       </c>
@@ -15150,7 +15216,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>882</v>
       </c>
@@ -15176,7 +15242,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>874</v>
       </c>
@@ -15202,7 +15268,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>876</v>
       </c>
@@ -15228,7 +15294,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>878</v>
       </c>
@@ -15254,7 +15320,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>880</v>
       </c>

--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5E0EEC-35AE-46B0-805A-B6D6D698A75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A0069F-5AC3-4061-ABFB-9A8BD8543893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30990" yWindow="1125" windowWidth="19845" windowHeight="11910" activeTab="5" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="576" yWindow="12" windowWidth="19848" windowHeight="11916" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="1010">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -3145,6 +3145,26 @@
   <si>
     <t>배기휀 써멀 동작</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aircon_operation</t>
+  </si>
+  <si>
+    <t>aircon_operation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M00221</t>
+  </si>
+  <si>
+    <t>aircon_OP_value</t>
+  </si>
+  <si>
+    <t>aircon_OP_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00957</t>
   </si>
 </sst>
 </file>
@@ -3238,7 +3258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3274,6 +3294,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6827,7 +6850,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M251"/>
+  <dimension ref="A1:M262"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -6909,7 +6932,7 @@
       <c r="L2" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>957</v>
       </c>
     </row>
@@ -6950,7 +6973,7 @@
       <c r="L3" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="M3" s="12"/>
+      <c r="M3" s="13"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -6974,7 +6997,7 @@
       <c r="L4" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="M4" s="12"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
@@ -6998,7 +7021,7 @@
       <c r="L5" s="6" t="s">
         <v>898</v>
       </c>
-      <c r="M5" s="12"/>
+      <c r="M5" s="13"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
@@ -7026,7 +7049,7 @@
       <c r="L6" s="10" t="s">
         <v>899</v>
       </c>
-      <c r="M6" s="12"/>
+      <c r="M6" s="13"/>
     </row>
     <row r="7" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
@@ -7062,7 +7085,7 @@
       <c r="L7" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="M7" s="12"/>
+      <c r="M7" s="13"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
@@ -7098,7 +7121,7 @@
       <c r="L8" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="M8" s="12"/>
+      <c r="M8" s="13"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
@@ -7132,7 +7155,7 @@
       <c r="L9" s="8" t="s">
         <v>966</v>
       </c>
-      <c r="M9" s="12"/>
+      <c r="M9" s="13"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
@@ -7168,7 +7191,7 @@
       <c r="L10" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="M10" s="12"/>
+      <c r="M10" s="13"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
@@ -7204,7 +7227,7 @@
       <c r="L11" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M11" s="12"/>
+      <c r="M11" s="13"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
@@ -7240,7 +7263,7 @@
       <c r="L12" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="M12" s="12"/>
+      <c r="M12" s="13"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
@@ -7276,7 +7299,7 @@
       <c r="L13" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="M13" s="12"/>
+      <c r="M13" s="13"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
@@ -7312,7 +7335,7 @@
       <c r="L14" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="M14" s="12"/>
+      <c r="M14" s="13"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
@@ -7346,7 +7369,7 @@
       <c r="L15" s="8" t="s">
         <v>967</v>
       </c>
-      <c r="M15" s="12"/>
+      <c r="M15" s="13"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
@@ -7382,7 +7405,7 @@
       <c r="L16" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="M16" s="12"/>
+      <c r="M16" s="13"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
@@ -7421,7 +7444,7 @@
       <c r="L17" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="M17" s="12"/>
+      <c r="M17" s="13"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
@@ -7457,7 +7480,7 @@
       <c r="L18" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="M18" s="12"/>
+      <c r="M18" s="13"/>
     </row>
     <row r="19" spans="1:13" ht="87" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
@@ -8046,7 +8069,7 @@
       <c r="L37" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="M37" s="12" t="s">
+      <c r="M37" s="13" t="s">
         <v>958</v>
       </c>
     </row>
@@ -8084,7 +8107,7 @@
       <c r="L38" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="M38" s="12"/>
+      <c r="M38" s="13"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
@@ -8120,7 +8143,7 @@
       <c r="L39" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="M39" s="12"/>
+      <c r="M39" s="13"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
@@ -8156,7 +8179,7 @@
       <c r="L40" s="6" t="s">
         <v>946</v>
       </c>
-      <c r="M40" s="12"/>
+      <c r="M40" s="13"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
@@ -8192,7 +8215,7 @@
       <c r="L41" s="6" t="s">
         <v>947</v>
       </c>
-      <c r="M41" s="12"/>
+      <c r="M41" s="13"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
@@ -8228,360 +8251,101 @@
       <c r="L42" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="M42" s="12"/>
-    </row>
-    <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>868</v>
-      </c>
+      <c r="M42" s="13"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>315</v>
+        <v>771</v>
       </c>
       <c r="C43" t="s">
-        <v>357</v>
+        <v>1005</v>
       </c>
       <c r="D43" t="s">
-        <v>296</v>
-      </c>
-      <c r="E43" t="s">
-        <v>358</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>357</v>
+        <v>1004</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>888</v>
-      </c>
-      <c r="L43" s="6"/>
-      <c r="M43" s="12" t="s">
-        <v>894</v>
-      </c>
+        <v>911</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="M43" s="12"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
-        <v>869</v>
-      </c>
-      <c r="B44" t="s">
-        <v>315</v>
-      </c>
-      <c r="C44" t="s">
-        <v>359</v>
-      </c>
-      <c r="D44" t="s">
-        <v>296</v>
-      </c>
-      <c r="E44" t="s">
-        <v>360</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>889</v>
-      </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
       <c r="L44" s="6"/>
       <c r="M44" s="12"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>870</v>
-      </c>
-      <c r="B45" t="s">
-        <v>315</v>
-      </c>
-      <c r="C45" t="s">
-        <v>361</v>
-      </c>
-      <c r="D45" t="s">
-        <v>296</v>
-      </c>
-      <c r="E45" t="s">
-        <v>362</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>890</v>
-      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
       <c r="L45" s="6"/>
       <c r="M45" s="12"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>871</v>
-      </c>
-      <c r="B46" t="s">
-        <v>315</v>
-      </c>
-      <c r="C46" t="s">
-        <v>363</v>
-      </c>
-      <c r="D46" t="s">
-        <v>296</v>
-      </c>
-      <c r="E46" t="s">
-        <v>364</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>891</v>
-      </c>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
       <c r="L46" s="6"/>
       <c r="M46" s="12"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>872</v>
-      </c>
-      <c r="B47" t="s">
-        <v>315</v>
-      </c>
-      <c r="C47" t="s">
-        <v>365</v>
-      </c>
-      <c r="D47" t="s">
-        <v>296</v>
-      </c>
-      <c r="E47" t="s">
-        <v>366</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>892</v>
-      </c>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
       <c r="L47" s="6"/>
       <c r="M47" s="12"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>873</v>
-      </c>
-      <c r="B48" t="s">
-        <v>315</v>
-      </c>
-      <c r="C48" t="s">
-        <v>367</v>
-      </c>
-      <c r="D48" t="s">
-        <v>296</v>
-      </c>
-      <c r="E48" t="s">
-        <v>368</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>960</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>893</v>
-      </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
       <c r="L48" s="6"/>
       <c r="M48" s="12"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B49" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4">
-        <v>1</v>
-      </c>
-      <c r="H49" s="4">
-        <v>0</v>
-      </c>
-      <c r="I49" s="4">
-        <v>0</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>968</v>
-      </c>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
       <c r="L49" s="6"/>
       <c r="M49" s="12"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B50" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>969</v>
-      </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4">
-        <v>1</v>
-      </c>
-      <c r="H50" s="4">
-        <v>0</v>
-      </c>
-      <c r="I50" s="4">
-        <v>0</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>969</v>
-      </c>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
       <c r="L50" s="6"/>
       <c r="M50" s="12"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B51" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4">
-        <v>1</v>
-      </c>
-      <c r="H51" s="4">
-        <v>0</v>
-      </c>
-      <c r="I51" s="4">
-        <v>0</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>970</v>
-      </c>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
       <c r="L51" s="6"/>
       <c r="M51" s="12"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B52" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>971</v>
-      </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4">
-        <v>1</v>
-      </c>
-      <c r="H52" s="4">
-        <v>0</v>
-      </c>
-      <c r="I52" s="4">
-        <v>0</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>731</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>971</v>
-      </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
       <c r="L52" s="6"/>
       <c r="M52" s="12"/>
     </row>
     <row r="53" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="B53" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C53" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D53" t="s">
         <v>296</v>
       </c>
       <c r="E53" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -8590,32 +8354,34 @@
         <v>0</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="L53" s="8"/>
-      <c r="M53" s="12"/>
+        <v>357</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="L53" s="6"/>
+      <c r="M53" s="13" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="B54" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C54" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="D54" t="s">
         <v>296</v>
       </c>
       <c r="E54" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -8624,31 +8390,29 @@
         <v>0</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>973</v>
-      </c>
-      <c r="L54" s="8"/>
-      <c r="M54" s="12" t="s">
-        <v>953</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="L54" s="6"/>
+      <c r="M54" s="13"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B55" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C55" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="D55" t="s">
         <v>296</v>
       </c>
       <c r="E55" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -8660,29 +8424,29 @@
         <v>0</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>949</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>974</v>
-      </c>
-      <c r="L55" s="8"/>
-      <c r="M55" s="12"/>
+        <v>361</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="L55" s="6"/>
+      <c r="M55" s="13"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="B56" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C56" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D56" t="s">
         <v>296</v>
       </c>
       <c r="E56" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -8694,32 +8458,32 @@
         <v>0</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>950</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>975</v>
-      </c>
-      <c r="L56" s="8"/>
-      <c r="M56" s="12"/>
+        <v>363</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="L56" s="6"/>
+      <c r="M56" s="13"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="B57" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C57" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="D57" t="s">
         <v>296</v>
       </c>
       <c r="E57" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -8728,388 +8492,452 @@
         <v>0</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>951</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="M57" s="12"/>
+        <v>959</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="L57" s="6"/>
+      <c r="M57" s="13"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B58" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C58" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="D58" t="s">
         <v>296</v>
       </c>
       <c r="E58" t="s">
+        <v>368</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="L58" s="6"/>
+      <c r="M58" s="13"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B59" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4">
+        <v>0</v>
+      </c>
+      <c r="I59" s="4">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="L59" s="6"/>
+      <c r="M59" s="13"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B60" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4">
+        <v>0</v>
+      </c>
+      <c r="I60" s="4">
+        <v>0</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="L60" s="6"/>
+      <c r="M60" s="13"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B61" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="L61" s="6"/>
+      <c r="M61" s="13"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B62" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4">
+        <v>0</v>
+      </c>
+      <c r="I62" s="4">
+        <v>0</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="L62" s="6"/>
+      <c r="M62" s="13"/>
+    </row>
+    <row r="63" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>875</v>
+      </c>
+      <c r="B63" t="s">
+        <v>771</v>
+      </c>
+      <c r="C63" t="s">
+        <v>369</v>
+      </c>
+      <c r="D63" t="s">
+        <v>296</v>
+      </c>
+      <c r="E63" t="s">
+        <v>370</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="L63" s="8"/>
+      <c r="M63" s="13"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>877</v>
+      </c>
+      <c r="B64" t="s">
+        <v>771</v>
+      </c>
+      <c r="C64" t="s">
+        <v>372</v>
+      </c>
+      <c r="D64" t="s">
+        <v>296</v>
+      </c>
+      <c r="E64" t="s">
+        <v>373</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="L64" s="8"/>
+      <c r="M64" s="13" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>879</v>
+      </c>
+      <c r="B65" t="s">
+        <v>771</v>
+      </c>
+      <c r="C65" t="s">
+        <v>375</v>
+      </c>
+      <c r="D65" t="s">
+        <v>296</v>
+      </c>
+      <c r="E65" t="s">
+        <v>376</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="L65" s="8"/>
+      <c r="M65" s="13"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>881</v>
+      </c>
+      <c r="B66" t="s">
+        <v>771</v>
+      </c>
+      <c r="C66" t="s">
+        <v>378</v>
+      </c>
+      <c r="D66" t="s">
+        <v>296</v>
+      </c>
+      <c r="E66" t="s">
+        <v>379</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="L66" s="8"/>
+      <c r="M66" s="13"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>883</v>
+      </c>
+      <c r="B67" t="s">
+        <v>771</v>
+      </c>
+      <c r="C67" t="s">
+        <v>381</v>
+      </c>
+      <c r="D67" t="s">
+        <v>296</v>
+      </c>
+      <c r="E67" t="s">
+        <v>382</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="M67" s="13"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>884</v>
+      </c>
+      <c r="B68" t="s">
+        <v>771</v>
+      </c>
+      <c r="C68" t="s">
+        <v>384</v>
+      </c>
+      <c r="D68" t="s">
+        <v>296</v>
+      </c>
+      <c r="E68" t="s">
         <v>385</v>
       </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="s">
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68" s="6" t="s">
         <v>952</v>
       </c>
-      <c r="K58" s="8" t="s">
+      <c r="K68" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L68" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="M58" s="12"/>
-    </row>
-    <row r="59" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
+      <c r="M68" s="13"/>
+    </row>
+    <row r="69" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
         <v>885</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B69" t="s">
         <v>771</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C69" t="s">
         <v>387</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D69" t="s">
         <v>296</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E69" t="s">
         <v>388</v>
       </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59" s="6" t="s">
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6" t="s">
         <v>955</v>
       </c>
-      <c r="K59" s="8" t="s">
+      <c r="K69" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="L59" s="8" t="s">
+      <c r="L69" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="M59" s="12"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
+      <c r="M69" s="13"/>
+    </row>
+    <row r="70" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C70" t="s">
+        <v>1008</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L70" s="8"/>
+      <c r="M70" s="12"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
         <v>954</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B73" t="s">
-        <v>315</v>
-      </c>
-      <c r="C73" t="s">
-        <v>405</v>
-      </c>
-      <c r="D73" t="s">
-        <v>303</v>
-      </c>
-      <c r="E73" t="s">
-        <v>406</v>
-      </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>1</v>
-      </c>
-      <c r="J73" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B74" t="s">
-        <v>294</v>
-      </c>
-      <c r="C74" t="s">
-        <v>408</v>
-      </c>
-      <c r="D74" t="s">
-        <v>303</v>
-      </c>
-      <c r="E74" t="s">
-        <v>409</v>
-      </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B75" t="s">
-        <v>294</v>
-      </c>
-      <c r="C75" t="s">
-        <v>410</v>
-      </c>
-      <c r="D75" t="s">
-        <v>303</v>
-      </c>
-      <c r="E75" t="s">
-        <v>411</v>
-      </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B76" t="s">
-        <v>294</v>
-      </c>
-      <c r="C76" t="s">
-        <v>412</v>
-      </c>
-      <c r="D76" t="s">
-        <v>303</v>
-      </c>
-      <c r="E76" t="s">
-        <v>413</v>
-      </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B77" t="s">
-        <v>294</v>
-      </c>
-      <c r="C77" t="s">
-        <v>414</v>
-      </c>
-      <c r="D77" t="s">
-        <v>303</v>
-      </c>
-      <c r="E77" t="s">
-        <v>415</v>
-      </c>
-      <c r="G77">
-        <v>1</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B78" t="s">
-        <v>294</v>
-      </c>
-      <c r="C78" t="s">
-        <v>416</v>
-      </c>
-      <c r="D78" t="s">
-        <v>303</v>
-      </c>
-      <c r="E78" t="s">
-        <v>417</v>
-      </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B79" t="s">
-        <v>294</v>
-      </c>
-      <c r="C79" t="s">
-        <v>418</v>
-      </c>
-      <c r="D79" t="s">
-        <v>303</v>
-      </c>
-      <c r="E79" t="s">
-        <v>419</v>
-      </c>
-      <c r="G79">
-        <v>1</v>
-      </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B80" t="s">
-        <v>315</v>
-      </c>
-      <c r="C80" t="s">
-        <v>420</v>
-      </c>
-      <c r="D80" t="s">
-        <v>303</v>
-      </c>
-      <c r="E80" t="s">
-        <v>421</v>
-      </c>
-      <c r="G80">
-        <v>0</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B81" t="s">
-        <v>294</v>
-      </c>
-      <c r="C81" t="s">
-        <v>422</v>
-      </c>
-      <c r="D81" t="s">
-        <v>423</v>
-      </c>
-      <c r="E81" t="s">
-        <v>424</v>
-      </c>
-      <c r="G81">
-        <v>0</v>
-      </c>
-      <c r="H81">
-        <v>0</v>
-      </c>
-      <c r="I81">
-        <v>0</v>
-      </c>
-      <c r="J81" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B82" t="s">
-        <v>294</v>
-      </c>
-      <c r="C82" t="s">
-        <v>425</v>
-      </c>
-      <c r="D82" t="s">
-        <v>423</v>
-      </c>
-      <c r="E82" t="s">
-        <v>426</v>
-      </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B83" t="s">
-        <v>294</v>
-      </c>
-      <c r="C83" t="s">
-        <v>427</v>
-      </c>
-      <c r="D83" t="s">
-        <v>423</v>
-      </c>
-      <c r="E83" t="s">
-        <v>428</v>
-      </c>
-      <c r="G83">
-        <v>0</v>
-      </c>
-      <c r="H83">
-        <v>0</v>
-      </c>
-      <c r="I83">
-        <v>0</v>
-      </c>
-      <c r="J83" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B84" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C84" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="D84" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E84" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -9118,10 +8946,10 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.4">
@@ -9129,16 +8957,16 @@
         <v>294</v>
       </c>
       <c r="C85" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="D85" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E85" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -9147,7 +8975,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.4">
@@ -9155,16 +8983,16 @@
         <v>294</v>
       </c>
       <c r="C86" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="D86" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E86" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -9173,24 +9001,24 @@
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B87" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C87" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="D87" t="s">
         <v>303</v>
       </c>
       <c r="E87" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -9199,7 +9027,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.4">
@@ -9207,16 +9035,16 @@
         <v>294</v>
       </c>
       <c r="C88" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="D88" t="s">
         <v>303</v>
       </c>
       <c r="E88" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -9225,7 +9053,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.4">
@@ -9233,13 +9061,13 @@
         <v>294</v>
       </c>
       <c r="C89" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="D89" t="s">
         <v>303</v>
       </c>
       <c r="E89" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -9251,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.4">
@@ -9259,16 +9087,13 @@
         <v>294</v>
       </c>
       <c r="C90" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="D90" t="s">
         <v>303</v>
       </c>
       <c r="E90" t="s">
-        <v>443</v>
-      </c>
-      <c r="F90" t="s">
-        <v>318</v>
+        <v>419</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -9280,21 +9105,21 @@
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B91" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C91" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="D91" t="s">
         <v>303</v>
       </c>
       <c r="E91" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -9304,9 +9129,6 @@
       </c>
       <c r="I91">
         <v>0</v>
-      </c>
-      <c r="J91" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.4">
@@ -9314,16 +9136,16 @@
         <v>294</v>
       </c>
       <c r="C92" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="D92" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E92" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -9332,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.4">
@@ -9340,19 +9162,16 @@
         <v>294</v>
       </c>
       <c r="C93" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="D93" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E93" t="s">
-        <v>449</v>
-      </c>
-      <c r="F93" t="s">
-        <v>318</v>
+        <v>426</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -9361,7 +9180,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.4">
@@ -9369,16 +9188,16 @@
         <v>294</v>
       </c>
       <c r="C94" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="D94" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E94" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -9387,7 +9206,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.4">
@@ -9395,13 +9214,13 @@
         <v>294</v>
       </c>
       <c r="C95" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="D95" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E95" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9413,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.4">
@@ -9421,16 +9240,16 @@
         <v>294</v>
       </c>
       <c r="C96" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="D96" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E96" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -9439,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.4">
@@ -9447,19 +9266,16 @@
         <v>294</v>
       </c>
       <c r="C97" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="D97" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E97" t="s">
-        <v>457</v>
-      </c>
-      <c r="F97" t="s">
-        <v>318</v>
+        <v>434</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -9468,24 +9284,24 @@
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B98" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C98" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="D98" t="s">
         <v>303</v>
       </c>
       <c r="E98" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -9494,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.4">
@@ -9502,16 +9318,16 @@
         <v>294</v>
       </c>
       <c r="C99" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="D99" t="s">
         <v>303</v>
       </c>
       <c r="E99" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -9520,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.4">
@@ -9528,16 +9344,16 @@
         <v>294</v>
       </c>
       <c r="C100" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="D100" t="s">
         <v>303</v>
       </c>
       <c r="E100" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -9546,7 +9362,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.4">
@@ -9554,13 +9370,16 @@
         <v>294</v>
       </c>
       <c r="C101" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="D101" t="s">
         <v>303</v>
       </c>
       <c r="E101" t="s">
-        <v>465</v>
+        <v>443</v>
+      </c>
+      <c r="F101" t="s">
+        <v>318</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -9572,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.4">
@@ -9580,16 +9399,16 @@
         <v>294</v>
       </c>
       <c r="C102" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="D102" t="s">
         <v>303</v>
       </c>
       <c r="E102" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -9598,21 +9417,21 @@
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B103" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C103" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="D103" t="s">
         <v>303</v>
       </c>
       <c r="E103" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -9622,20 +9441,26 @@
       </c>
       <c r="I103">
         <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B104" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C104" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="D104" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E104" t="s">
-        <v>471</v>
+        <v>449</v>
+      </c>
+      <c r="F104" t="s">
+        <v>318</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -9645,20 +9470,23 @@
       </c>
       <c r="I104">
         <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B105" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C105" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="D105" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="E105" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -9668,6 +9496,9 @@
       </c>
       <c r="I105">
         <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.4">
@@ -9675,13 +9506,13 @@
         <v>294</v>
       </c>
       <c r="C106" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="D106" t="s">
         <v>303</v>
       </c>
       <c r="E106" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -9693,7 +9524,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.4">
@@ -9701,16 +9532,16 @@
         <v>294</v>
       </c>
       <c r="C107" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="D107" t="s">
         <v>303</v>
       </c>
       <c r="E107" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -9719,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.4">
@@ -9727,16 +9558,19 @@
         <v>294</v>
       </c>
       <c r="C108" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="D108" t="s">
         <v>303</v>
       </c>
       <c r="E108" t="s">
-        <v>479</v>
+        <v>457</v>
+      </c>
+      <c r="F108" t="s">
+        <v>318</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -9745,7 +9579,7 @@
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.4">
@@ -9753,16 +9587,16 @@
         <v>294</v>
       </c>
       <c r="C109" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="D109" t="s">
         <v>303</v>
       </c>
       <c r="E109" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -9771,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.4">
@@ -9779,16 +9613,16 @@
         <v>294</v>
       </c>
       <c r="C110" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="D110" t="s">
         <v>303</v>
       </c>
       <c r="E110" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -9797,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="J110" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.4">
@@ -9805,13 +9639,13 @@
         <v>294</v>
       </c>
       <c r="C111" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="D111" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E111" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -9823,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.4">
@@ -9831,16 +9665,16 @@
         <v>294</v>
       </c>
       <c r="C112" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="D112" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E112" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -9849,7 +9683,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.4">
@@ -9857,16 +9691,16 @@
         <v>294</v>
       </c>
       <c r="C113" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="D113" t="s">
         <v>303</v>
       </c>
       <c r="E113" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -9875,47 +9709,44 @@
         <v>0</v>
       </c>
       <c r="J113" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B114" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C114" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="D114" t="s">
         <v>303</v>
       </c>
       <c r="E114" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
         <v>0</v>
-      </c>
-      <c r="J114" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B115" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C115" t="s">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="D115" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E115" t="s">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -9925,35 +9756,29 @@
       </c>
       <c r="I115">
         <v>0</v>
-      </c>
-      <c r="J115" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B116" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C116" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="D116" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E116" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
       <c r="I116">
         <v>0</v>
-      </c>
-      <c r="J116" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.4">
@@ -9961,13 +9786,13 @@
         <v>294</v>
       </c>
       <c r="C117" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="D117" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E117" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -9979,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="J117" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.4">
@@ -9987,13 +9812,13 @@
         <v>294</v>
       </c>
       <c r="C118" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="D118" t="s">
         <v>303</v>
       </c>
       <c r="E118" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -10005,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="J118" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.4">
@@ -10013,13 +9838,13 @@
         <v>294</v>
       </c>
       <c r="C119" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="D119" t="s">
         <v>303</v>
       </c>
       <c r="E119" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -10031,7 +9856,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.4">
@@ -10039,16 +9864,16 @@
         <v>294</v>
       </c>
       <c r="C120" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="D120" t="s">
         <v>303</v>
       </c>
       <c r="E120" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="G120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -10057,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.4">
@@ -10065,22 +9890,25 @@
         <v>294</v>
       </c>
       <c r="C121" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="D121" t="s">
         <v>303</v>
       </c>
       <c r="E121" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="G121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121">
         <v>0</v>
       </c>
       <c r="I121">
         <v>0</v>
+      </c>
+      <c r="J121" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.4">
@@ -10088,22 +9916,25 @@
         <v>294</v>
       </c>
       <c r="C122" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="D122" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E122" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
       <c r="I122">
         <v>0</v>
+      </c>
+      <c r="J122" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.4">
@@ -10111,13 +9942,13 @@
         <v>294</v>
       </c>
       <c r="C123" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="D123" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E123" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -10129,7 +9960,7 @@
         <v>0</v>
       </c>
       <c r="J123" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.4">
@@ -10137,13 +9968,13 @@
         <v>294</v>
       </c>
       <c r="C124" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="D124" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E124" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -10155,7 +9986,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.4">
@@ -10163,13 +9994,13 @@
         <v>294</v>
       </c>
       <c r="C125" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="D125" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E125" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -10181,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.4">
@@ -10189,16 +10020,16 @@
         <v>294</v>
       </c>
       <c r="C126" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="D126" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E126" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -10207,7 +10038,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.4">
@@ -10215,13 +10046,13 @@
         <v>294</v>
       </c>
       <c r="C127" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="D127" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E127" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -10233,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.4">
@@ -10241,13 +10072,13 @@
         <v>294</v>
       </c>
       <c r="C128" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="D128" t="s">
         <v>296</v>
       </c>
       <c r="E128" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -10259,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.4">
@@ -10267,13 +10098,13 @@
         <v>294</v>
       </c>
       <c r="C129" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="D129" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E129" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -10285,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.4">
@@ -10293,13 +10124,13 @@
         <v>294</v>
       </c>
       <c r="C130" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="D130" t="s">
         <v>303</v>
       </c>
       <c r="E130" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -10311,7 +10142,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.4">
@@ -10319,16 +10150,16 @@
         <v>294</v>
       </c>
       <c r="C131" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="D131" t="s">
         <v>303</v>
       </c>
       <c r="E131" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -10337,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.4">
@@ -10345,25 +10176,22 @@
         <v>294</v>
       </c>
       <c r="C132" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="D132" t="s">
         <v>303</v>
       </c>
       <c r="E132" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="G132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
         <v>0</v>
-      </c>
-      <c r="J132" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.4">
@@ -10371,13 +10199,13 @@
         <v>294</v>
       </c>
       <c r="C133" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="D133" t="s">
         <v>303</v>
       </c>
       <c r="E133" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -10387,9 +10215,6 @@
       </c>
       <c r="I133">
         <v>0</v>
-      </c>
-      <c r="J133" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.4">
@@ -10397,13 +10222,13 @@
         <v>294</v>
       </c>
       <c r="C134" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="D134" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E134" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -10415,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.4">
@@ -10423,13 +10248,13 @@
         <v>294</v>
       </c>
       <c r="C135" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="D135" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E135" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -10441,7 +10266,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.4">
@@ -10449,13 +10274,13 @@
         <v>294</v>
       </c>
       <c r="C136" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="D136" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E136" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -10467,7 +10292,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.4">
@@ -10475,13 +10300,13 @@
         <v>294</v>
       </c>
       <c r="C137" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="D137" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E137" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -10493,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="J137" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.4">
@@ -10501,16 +10326,16 @@
         <v>294</v>
       </c>
       <c r="C138" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="D138" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E138" t="s">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -10519,7 +10344,7 @@
         <v>0</v>
       </c>
       <c r="J138" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.4">
@@ -10527,16 +10352,16 @@
         <v>294</v>
       </c>
       <c r="C139" t="s">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="D139" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E139" t="s">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -10545,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="s">
-        <v>541</v>
+        <v>519</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.4">
@@ -10553,16 +10378,16 @@
         <v>294</v>
       </c>
       <c r="C140" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="D140" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E140" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -10571,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="J140" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.4">
@@ -10579,13 +10404,13 @@
         <v>294</v>
       </c>
       <c r="C141" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="D141" t="s">
         <v>303</v>
       </c>
       <c r="E141" t="s">
-        <v>546</v>
+        <v>524</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -10597,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.4">
@@ -10605,16 +10430,16 @@
         <v>294</v>
       </c>
       <c r="C142" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="D142" t="s">
         <v>303</v>
       </c>
       <c r="E142" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="G142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -10623,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="J142" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.4">
@@ -10631,19 +10456,16 @@
         <v>294</v>
       </c>
       <c r="C143" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="D143" t="s">
         <v>303</v>
       </c>
       <c r="E143" t="s">
-        <v>550</v>
-      </c>
-      <c r="F143" t="s">
-        <v>318</v>
+        <v>528</v>
       </c>
       <c r="G143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -10652,7 +10474,7 @@
         <v>0</v>
       </c>
       <c r="J143" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.4">
@@ -10660,16 +10482,16 @@
         <v>294</v>
       </c>
       <c r="C144" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="D144" t="s">
         <v>303</v>
       </c>
       <c r="E144" t="s">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -10678,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="J144" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.4">
@@ -10686,16 +10508,16 @@
         <v>294</v>
       </c>
       <c r="C145" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="D145" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E145" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -10704,7 +10526,7 @@
         <v>0</v>
       </c>
       <c r="J145" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.4">
@@ -10712,19 +10534,16 @@
         <v>294</v>
       </c>
       <c r="C146" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D146" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E146" t="s">
-        <v>556</v>
-      </c>
-      <c r="F146" t="s">
-        <v>318</v>
+        <v>534</v>
       </c>
       <c r="G146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -10733,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="J146" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.4">
@@ -10741,16 +10560,16 @@
         <v>294</v>
       </c>
       <c r="C147" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="D147" t="s">
         <v>303</v>
       </c>
       <c r="E147" t="s">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -10759,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.4">
@@ -10767,13 +10586,13 @@
         <v>294</v>
       </c>
       <c r="C148" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="D148" t="s">
         <v>303</v>
       </c>
       <c r="E148" t="s">
-        <v>560</v>
+        <v>538</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -10785,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="J148" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.4">
@@ -10793,13 +10612,13 @@
         <v>294</v>
       </c>
       <c r="C149" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="D149" t="s">
         <v>303</v>
       </c>
       <c r="E149" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -10811,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.4">
@@ -10819,16 +10638,13 @@
         <v>294</v>
       </c>
       <c r="C150" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="D150" t="s">
         <v>303</v>
       </c>
       <c r="E150" t="s">
-        <v>564</v>
-      </c>
-      <c r="F150" t="s">
-        <v>318</v>
+        <v>542</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -10840,7 +10656,7 @@
         <v>0</v>
       </c>
       <c r="J150" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.4">
@@ -10848,16 +10664,13 @@
         <v>294</v>
       </c>
       <c r="C151" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="D151" t="s">
         <v>303</v>
       </c>
       <c r="E151" t="s">
-        <v>566</v>
-      </c>
-      <c r="F151" t="s">
-        <v>318</v>
+        <v>544</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -10869,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.4">
@@ -10877,16 +10690,16 @@
         <v>294</v>
       </c>
       <c r="C152" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="D152" t="s">
         <v>303</v>
       </c>
       <c r="E152" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="G152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -10895,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
     </row>
     <row r="153" spans="2:10" x14ac:dyDescent="0.4">
@@ -10903,16 +10716,16 @@
         <v>294</v>
       </c>
       <c r="C153" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="D153" t="s">
         <v>303</v>
       </c>
       <c r="E153" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -10921,7 +10734,7 @@
         <v>0</v>
       </c>
       <c r="J153" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.4">
@@ -10929,13 +10742,16 @@
         <v>294</v>
       </c>
       <c r="C154" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="D154" t="s">
         <v>303</v>
       </c>
       <c r="E154" t="s">
-        <v>572</v>
+        <v>550</v>
+      </c>
+      <c r="F154" t="s">
+        <v>318</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -10947,7 +10763,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.4">
@@ -10955,16 +10771,16 @@
         <v>294</v>
       </c>
       <c r="C155" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="D155" t="s">
         <v>303</v>
       </c>
       <c r="E155" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -10973,24 +10789,24 @@
         <v>0</v>
       </c>
       <c r="J155" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B156" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C156" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="D156" t="s">
         <v>303</v>
       </c>
       <c r="E156" t="s">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -10999,24 +10815,27 @@
         <v>0</v>
       </c>
       <c r="J156" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B157" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C157" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="D157" t="s">
         <v>303</v>
       </c>
       <c r="E157" t="s">
-        <v>578</v>
+        <v>556</v>
+      </c>
+      <c r="F157" t="s">
+        <v>318</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -11025,7 +10844,7 @@
         <v>0</v>
       </c>
       <c r="J157" t="s">
-        <v>579</v>
+        <v>555</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.4">
@@ -11033,16 +10852,16 @@
         <v>294</v>
       </c>
       <c r="C158" t="s">
-        <v>580</v>
+        <v>557</v>
       </c>
       <c r="D158" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E158" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -11051,7 +10870,7 @@
         <v>0</v>
       </c>
       <c r="J158" t="s">
-        <v>580</v>
+        <v>557</v>
       </c>
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.4">
@@ -11059,13 +10878,13 @@
         <v>294</v>
       </c>
       <c r="C159" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="D159" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E159" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -11077,7 +10896,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.4">
@@ -11085,16 +10904,16 @@
         <v>294</v>
       </c>
       <c r="C160" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E160" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -11103,7 +10922,7 @@
         <v>0</v>
       </c>
       <c r="J160" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.4">
@@ -11111,16 +10930,19 @@
         <v>294</v>
       </c>
       <c r="C161" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
       <c r="D161" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E161" t="s">
-        <v>587</v>
+        <v>564</v>
+      </c>
+      <c r="F161" t="s">
+        <v>318</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -11129,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="J161" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.4">
@@ -11137,16 +10959,19 @@
         <v>294</v>
       </c>
       <c r="C162" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
       <c r="D162" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E162" t="s">
-        <v>589</v>
+        <v>566</v>
+      </c>
+      <c r="F162" t="s">
+        <v>318</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -11155,7 +10980,7 @@
         <v>0</v>
       </c>
       <c r="J162" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.4">
@@ -11163,16 +10988,16 @@
         <v>294</v>
       </c>
       <c r="C163" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="D163" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E163" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -11181,7 +11006,7 @@
         <v>0</v>
       </c>
       <c r="J163" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.4">
@@ -11189,13 +11014,13 @@
         <v>294</v>
       </c>
       <c r="C164" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="D164" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E164" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -11207,7 +11032,7 @@
         <v>0</v>
       </c>
       <c r="J164" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.4">
@@ -11215,16 +11040,16 @@
         <v>294</v>
       </c>
       <c r="C165" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="D165" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E165" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -11233,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="J165" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.4">
@@ -11241,16 +11066,16 @@
         <v>294</v>
       </c>
       <c r="C166" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="D166" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E166" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -11259,21 +11084,21 @@
         <v>0</v>
       </c>
       <c r="J166" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B167" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C167" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
       <c r="D167" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E167" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -11285,21 +11110,21 @@
         <v>0</v>
       </c>
       <c r="J167" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B168" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C168" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="D168" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E168" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -11311,7 +11136,7 @@
         <v>0</v>
       </c>
       <c r="J168" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.4">
@@ -11319,13 +11144,13 @@
         <v>294</v>
       </c>
       <c r="C169" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="D169" t="s">
-        <v>509</v>
+        <v>423</v>
       </c>
       <c r="E169" t="s">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -11337,7 +11162,7 @@
         <v>0</v>
       </c>
       <c r="J169" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.4">
@@ -11345,16 +11170,16 @@
         <v>294</v>
       </c>
       <c r="C170" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="D170" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E170" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -11363,7 +11188,7 @@
         <v>0</v>
       </c>
       <c r="J170" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.4">
@@ -11371,16 +11196,16 @@
         <v>294</v>
       </c>
       <c r="C171" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="D171" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E171" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="G171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -11389,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="J171" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.4">
@@ -11397,16 +11222,16 @@
         <v>294</v>
       </c>
       <c r="C172" t="s">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="D172" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E172" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -11415,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="J172" t="s">
-        <v>608</v>
+        <v>586</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.4">
@@ -11423,16 +11248,16 @@
         <v>294</v>
       </c>
       <c r="C173" t="s">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="D173" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E173" t="s">
-        <v>611</v>
+        <v>589</v>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -11441,7 +11266,7 @@
         <v>0</v>
       </c>
       <c r="J173" t="s">
-        <v>610</v>
+        <v>588</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.4">
@@ -11449,16 +11274,16 @@
         <v>294</v>
       </c>
       <c r="C174" t="s">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="D174" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E174" t="s">
-        <v>613</v>
+        <v>591</v>
       </c>
       <c r="G174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -11467,7 +11292,7 @@
         <v>0</v>
       </c>
       <c r="J174" t="s">
-        <v>612</v>
+        <v>590</v>
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.4">
@@ -11475,16 +11300,16 @@
         <v>294</v>
       </c>
       <c r="C175" t="s">
-        <v>614</v>
+        <v>592</v>
       </c>
       <c r="D175" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E175" t="s">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="G175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -11493,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="J175" t="s">
-        <v>614</v>
+        <v>592</v>
       </c>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.4">
@@ -11501,16 +11326,16 @@
         <v>294</v>
       </c>
       <c r="C176" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="D176" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E176" t="s">
-        <v>617</v>
+        <v>595</v>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -11519,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="J176" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.4">
@@ -11527,13 +11352,13 @@
         <v>294</v>
       </c>
       <c r="C177" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="D177" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E177" t="s">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -11545,7 +11370,7 @@
         <v>0</v>
       </c>
       <c r="J177" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.4">
@@ -11553,13 +11378,13 @@
         <v>294</v>
       </c>
       <c r="C178" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="D178" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E178" t="s">
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -11571,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="J178" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.4">
@@ -11579,16 +11404,16 @@
         <v>294</v>
       </c>
       <c r="C179" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="D179" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E179" t="s">
-        <v>623</v>
+        <v>601</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -11597,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="J179" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.4">
@@ -11605,16 +11430,16 @@
         <v>294</v>
       </c>
       <c r="C180" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
       <c r="D180" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E180" t="s">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="G180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -11623,7 +11448,7 @@
         <v>0</v>
       </c>
       <c r="J180" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.4">
@@ -11631,13 +11456,13 @@
         <v>294</v>
       </c>
       <c r="C181" t="s">
-        <v>626</v>
+        <v>604</v>
       </c>
       <c r="D181" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E181" t="s">
-        <v>627</v>
+        <v>605</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -11649,24 +11474,24 @@
         <v>0</v>
       </c>
       <c r="J181" t="s">
-        <v>626</v>
+        <v>604</v>
       </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B182" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C182" t="s">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="D182" t="s">
         <v>303</v>
       </c>
       <c r="E182" t="s">
-        <v>629</v>
+        <v>607</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -11675,7 +11500,7 @@
         <v>0</v>
       </c>
       <c r="J182" t="s">
-        <v>630</v>
+        <v>606</v>
       </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.4">
@@ -11683,13 +11508,13 @@
         <v>294</v>
       </c>
       <c r="C183" t="s">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="D183" t="s">
         <v>303</v>
       </c>
       <c r="E183" t="s">
-        <v>632</v>
+        <v>609</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -11701,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="J183" t="s">
-        <v>631</v>
+        <v>608</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.4">
@@ -11709,13 +11534,13 @@
         <v>294</v>
       </c>
       <c r="C184" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
       <c r="D184" t="s">
         <v>303</v>
       </c>
       <c r="E184" t="s">
-        <v>634</v>
+        <v>611</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -11727,7 +11552,7 @@
         <v>0</v>
       </c>
       <c r="J184" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.4">
@@ -11735,16 +11560,16 @@
         <v>294</v>
       </c>
       <c r="C185" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="D185" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E185" t="s">
-        <v>636</v>
+        <v>613</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -11753,7 +11578,7 @@
         <v>0</v>
       </c>
       <c r="J185" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.4">
@@ -11761,16 +11586,16 @@
         <v>294</v>
       </c>
       <c r="C186" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="D186" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E186" t="s">
-        <v>638</v>
+        <v>615</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -11779,7 +11604,7 @@
         <v>0</v>
       </c>
       <c r="J186" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.4">
@@ -11787,16 +11612,16 @@
         <v>294</v>
       </c>
       <c r="C187" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
       <c r="D187" t="s">
         <v>296</v>
       </c>
       <c r="E187" t="s">
-        <v>640</v>
+        <v>617</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -11805,7 +11630,7 @@
         <v>0</v>
       </c>
       <c r="J187" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.4">
@@ -11813,13 +11638,13 @@
         <v>294</v>
       </c>
       <c r="C188" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="D188" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E188" t="s">
-        <v>642</v>
+        <v>619</v>
       </c>
       <c r="G188">
         <v>0</v>
@@ -11831,7 +11656,7 @@
         <v>0</v>
       </c>
       <c r="J188" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.4">
@@ -11839,13 +11664,13 @@
         <v>294</v>
       </c>
       <c r="C189" t="s">
-        <v>643</v>
+        <v>620</v>
       </c>
       <c r="D189" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E189" t="s">
-        <v>644</v>
+        <v>621</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -11857,7 +11682,7 @@
         <v>0</v>
       </c>
       <c r="J189" t="s">
-        <v>643</v>
+        <v>620</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.4">
@@ -11865,16 +11690,16 @@
         <v>294</v>
       </c>
       <c r="C190" t="s">
-        <v>645</v>
+        <v>622</v>
       </c>
       <c r="D190" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E190" t="s">
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -11883,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="J190" t="s">
-        <v>645</v>
+        <v>622</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.4">
@@ -11891,16 +11716,16 @@
         <v>294</v>
       </c>
       <c r="C191" t="s">
-        <v>647</v>
+        <v>624</v>
       </c>
       <c r="D191" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E191" t="s">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="G191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H191">
         <v>0</v>
@@ -11909,7 +11734,7 @@
         <v>0</v>
       </c>
       <c r="J191" t="s">
-        <v>647</v>
+        <v>624</v>
       </c>
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.4">
@@ -11917,16 +11742,16 @@
         <v>294</v>
       </c>
       <c r="C192" t="s">
-        <v>649</v>
+        <v>626</v>
       </c>
       <c r="D192" t="s">
         <v>296</v>
       </c>
       <c r="E192" t="s">
-        <v>650</v>
+        <v>627</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -11935,21 +11760,21 @@
         <v>0</v>
       </c>
       <c r="J192" t="s">
-        <v>649</v>
+        <v>626</v>
       </c>
     </row>
     <row r="193" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B193" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C193" t="s">
-        <v>651</v>
+        <v>628</v>
       </c>
       <c r="D193" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E193" t="s">
-        <v>652</v>
+        <v>629</v>
       </c>
       <c r="G193">
         <v>0</v>
@@ -11961,82 +11786,73 @@
         <v>0</v>
       </c>
       <c r="J193" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
     </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B194" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C194" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="D194" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="E194" t="s">
-        <v>654</v>
-      </c>
-      <c r="F194" t="s">
-        <v>318</v>
+        <v>632</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194">
         <v>0</v>
       </c>
       <c r="I194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B195" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C195" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="D195" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="E195" t="s">
-        <v>656</v>
-      </c>
-      <c r="F195" t="s">
-        <v>318</v>
+        <v>634</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195">
         <v>0</v>
       </c>
       <c r="I195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B196" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C196" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
       <c r="D196" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E196" t="s">
-        <v>658</v>
-      </c>
-      <c r="F196" t="s">
-        <v>318</v>
+        <v>636</v>
       </c>
       <c r="G196">
         <v>0</v>
@@ -12045,27 +11861,24 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B197" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C197" t="s">
-        <v>659</v>
+        <v>637</v>
       </c>
       <c r="D197" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E197" t="s">
-        <v>660</v>
-      </c>
-      <c r="F197" t="s">
-        <v>318</v>
+        <v>638</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -12074,27 +11887,24 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197" t="s">
-        <v>659</v>
+        <v>637</v>
       </c>
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B198" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C198" t="s">
-        <v>661</v>
+        <v>639</v>
       </c>
       <c r="D198" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E198" t="s">
-        <v>662</v>
-      </c>
-      <c r="F198" t="s">
-        <v>318</v>
+        <v>640</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -12103,27 +11913,24 @@
         <v>0</v>
       </c>
       <c r="I198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" t="s">
-        <v>661</v>
+        <v>639</v>
       </c>
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B199" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C199" t="s">
-        <v>663</v>
+        <v>641</v>
       </c>
       <c r="D199" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E199" t="s">
-        <v>664</v>
-      </c>
-      <c r="F199" t="s">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -12132,27 +11939,24 @@
         <v>0</v>
       </c>
       <c r="I199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J199" t="s">
-        <v>663</v>
+        <v>641</v>
       </c>
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B200" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C200" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
       <c r="D200" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E200" t="s">
-        <v>666</v>
-      </c>
-      <c r="F200" t="s">
-        <v>318</v>
+        <v>644</v>
       </c>
       <c r="G200">
         <v>0</v>
@@ -12161,27 +11965,24 @@
         <v>0</v>
       </c>
       <c r="I200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J200" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B201" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C201" t="s">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="D201" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E201" t="s">
-        <v>668</v>
-      </c>
-      <c r="F201" t="s">
-        <v>318</v>
+        <v>646</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -12190,27 +11991,24 @@
         <v>0</v>
       </c>
       <c r="I201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J201" t="s">
-        <v>667</v>
+        <v>645</v>
       </c>
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B202" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C202" t="s">
-        <v>669</v>
+        <v>647</v>
       </c>
       <c r="D202" t="s">
         <v>296</v>
       </c>
       <c r="E202" t="s">
-        <v>670</v>
-      </c>
-      <c r="F202" t="s">
-        <v>318</v>
+        <v>648</v>
       </c>
       <c r="G202">
         <v>0</v>
@@ -12219,27 +12017,24 @@
         <v>0</v>
       </c>
       <c r="I202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J202" t="s">
-        <v>669</v>
+        <v>647</v>
       </c>
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B203" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C203" t="s">
-        <v>671</v>
+        <v>649</v>
       </c>
       <c r="D203" t="s">
         <v>296</v>
       </c>
       <c r="E203" t="s">
-        <v>672</v>
-      </c>
-      <c r="F203" t="s">
-        <v>318</v>
+        <v>650</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -12248,27 +12043,24 @@
         <v>0</v>
       </c>
       <c r="I203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203" t="s">
-        <v>671</v>
+        <v>649</v>
       </c>
     </row>
     <row r="204" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B204" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C204" t="s">
-        <v>351</v>
+        <v>651</v>
       </c>
       <c r="D204" t="s">
         <v>296</v>
       </c>
       <c r="E204" t="s">
-        <v>352</v>
-      </c>
-      <c r="F204" t="s">
-        <v>318</v>
+        <v>652</v>
       </c>
       <c r="G204">
         <v>0</v>
@@ -12277,10 +12069,10 @@
         <v>0</v>
       </c>
       <c r="I204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J204" t="s">
-        <v>351</v>
+        <v>651</v>
       </c>
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.4">
@@ -12288,13 +12080,13 @@
         <v>315</v>
       </c>
       <c r="C205" t="s">
-        <v>673</v>
+        <v>653</v>
       </c>
       <c r="D205" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E205" t="s">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="F205" t="s">
         <v>318</v>
@@ -12309,7 +12101,7 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>673</v>
+        <v>653</v>
       </c>
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.4">
@@ -12317,13 +12109,13 @@
         <v>315</v>
       </c>
       <c r="C206" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="D206" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E206" t="s">
-        <v>676</v>
+        <v>656</v>
       </c>
       <c r="F206" t="s">
         <v>318</v>
@@ -12338,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.4">
@@ -12346,13 +12138,13 @@
         <v>315</v>
       </c>
       <c r="C207" t="s">
-        <v>677</v>
+        <v>657</v>
       </c>
       <c r="D207" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E207" t="s">
-        <v>678</v>
+        <v>658</v>
       </c>
       <c r="F207" t="s">
         <v>318</v>
@@ -12367,7 +12159,7 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>677</v>
+        <v>657</v>
       </c>
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.4">
@@ -12375,13 +12167,13 @@
         <v>315</v>
       </c>
       <c r="C208" t="s">
-        <v>353</v>
+        <v>659</v>
       </c>
       <c r="D208" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E208" t="s">
-        <v>354</v>
+        <v>660</v>
       </c>
       <c r="F208" t="s">
         <v>318</v>
@@ -12396,7 +12188,7 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>353</v>
+        <v>659</v>
       </c>
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.4">
@@ -12404,13 +12196,13 @@
         <v>315</v>
       </c>
       <c r="C209" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="D209" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E209" t="s">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="F209" t="s">
         <v>318</v>
@@ -12425,7 +12217,7 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
     </row>
     <row r="210" spans="2:10" x14ac:dyDescent="0.4">
@@ -12433,13 +12225,13 @@
         <v>315</v>
       </c>
       <c r="C210" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="D210" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E210" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="F210" t="s">
         <v>318</v>
@@ -12454,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
     </row>
     <row r="211" spans="2:10" x14ac:dyDescent="0.4">
@@ -12462,13 +12254,13 @@
         <v>315</v>
       </c>
       <c r="C211" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
       <c r="D211" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E211" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="F211" t="s">
         <v>318</v>
@@ -12483,7 +12275,7 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.4">
@@ -12491,13 +12283,13 @@
         <v>315</v>
       </c>
       <c r="C212" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="D212" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E212" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="F212" t="s">
         <v>318</v>
@@ -12512,7 +12304,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.4">
@@ -12520,13 +12312,13 @@
         <v>315</v>
       </c>
       <c r="C213" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="D213" t="s">
         <v>296</v>
       </c>
       <c r="E213" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="F213" t="s">
         <v>318</v>
@@ -12541,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.4">
@@ -12549,13 +12341,13 @@
         <v>315</v>
       </c>
       <c r="C214" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="D214" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E214" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="F214" t="s">
         <v>318</v>
@@ -12567,10 +12359,10 @@
         <v>0</v>
       </c>
       <c r="I214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.4">
@@ -12578,13 +12370,13 @@
         <v>315</v>
       </c>
       <c r="C215" t="s">
-        <v>692</v>
+        <v>351</v>
       </c>
       <c r="D215" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E215" t="s">
-        <v>693</v>
+        <v>352</v>
       </c>
       <c r="F215" t="s">
         <v>318</v>
@@ -12596,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="I215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>692</v>
+        <v>351</v>
       </c>
     </row>
     <row r="216" spans="2:10" x14ac:dyDescent="0.4">
@@ -12607,13 +12399,13 @@
         <v>315</v>
       </c>
       <c r="C216" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="D216" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E216" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="F216" t="s">
         <v>318</v>
@@ -12625,10 +12417,10 @@
         <v>0</v>
       </c>
       <c r="I216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>696</v>
+        <v>673</v>
       </c>
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.4">
@@ -12636,13 +12428,13 @@
         <v>315</v>
       </c>
       <c r="C217" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="D217" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E217" t="s">
-        <v>698</v>
+        <v>676</v>
       </c>
       <c r="F217" t="s">
         <v>318</v>
@@ -12654,10 +12446,10 @@
         <v>0</v>
       </c>
       <c r="I217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.4">
@@ -12665,13 +12457,13 @@
         <v>315</v>
       </c>
       <c r="C218" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="D218" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E218" t="s">
-        <v>700</v>
+        <v>678</v>
       </c>
       <c r="F218" t="s">
         <v>318</v>
@@ -12683,10 +12475,10 @@
         <v>0</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.4">
@@ -12694,13 +12486,13 @@
         <v>315</v>
       </c>
       <c r="C219" t="s">
-        <v>701</v>
+        <v>353</v>
       </c>
       <c r="D219" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E219" t="s">
-        <v>702</v>
+        <v>354</v>
       </c>
       <c r="F219" t="s">
         <v>318</v>
@@ -12712,10 +12504,10 @@
         <v>0</v>
       </c>
       <c r="I219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>701</v>
+        <v>353</v>
       </c>
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.4">
@@ -12723,13 +12515,13 @@
         <v>315</v>
       </c>
       <c r="C220" t="s">
-        <v>703</v>
+        <v>679</v>
       </c>
       <c r="D220" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E220" t="s">
-        <v>704</v>
+        <v>680</v>
       </c>
       <c r="F220" t="s">
         <v>318</v>
@@ -12741,10 +12533,10 @@
         <v>0</v>
       </c>
       <c r="I220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>703</v>
+        <v>679</v>
       </c>
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.4">
@@ -12752,13 +12544,13 @@
         <v>315</v>
       </c>
       <c r="C221" t="s">
-        <v>705</v>
+        <v>681</v>
       </c>
       <c r="D221" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E221" t="s">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="F221" t="s">
         <v>318</v>
@@ -12770,10 +12562,10 @@
         <v>0</v>
       </c>
       <c r="I221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>705</v>
+        <v>681</v>
       </c>
     </row>
     <row r="222" spans="2:10" x14ac:dyDescent="0.4">
@@ -12781,13 +12573,16 @@
         <v>315</v>
       </c>
       <c r="C222" t="s">
-        <v>707</v>
+        <v>683</v>
       </c>
       <c r="D222" t="s">
         <v>296</v>
       </c>
       <c r="E222" t="s">
-        <v>708</v>
+        <v>684</v>
+      </c>
+      <c r="F222" t="s">
+        <v>318</v>
       </c>
       <c r="G222">
         <v>0</v>
@@ -12796,24 +12591,27 @@
         <v>0</v>
       </c>
       <c r="I222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>707</v>
+        <v>683</v>
       </c>
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B223" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C223" t="s">
-        <v>709</v>
+        <v>685</v>
       </c>
       <c r="D223" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E223" t="s">
-        <v>710</v>
+        <v>686</v>
+      </c>
+      <c r="F223" t="s">
+        <v>318</v>
       </c>
       <c r="G223">
         <v>0</v>
@@ -12822,7 +12620,10 @@
         <v>0</v>
       </c>
       <c r="I223">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J223" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.4">
@@ -12830,13 +12631,16 @@
         <v>315</v>
       </c>
       <c r="C224" t="s">
-        <v>711</v>
+        <v>687</v>
       </c>
       <c r="D224" t="s">
         <v>296</v>
       </c>
       <c r="E224" t="s">
-        <v>712</v>
+        <v>688</v>
+      </c>
+      <c r="F224" t="s">
+        <v>318</v>
       </c>
       <c r="G224">
         <v>0</v>
@@ -12845,10 +12649,10 @@
         <v>0</v>
       </c>
       <c r="I224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>711</v>
+        <v>687</v>
       </c>
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.4">
@@ -12856,16 +12660,19 @@
         <v>315</v>
       </c>
       <c r="C225" t="s">
-        <v>713</v>
+        <v>689</v>
       </c>
       <c r="D225" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E225" t="s">
-        <v>714</v>
+        <v>691</v>
+      </c>
+      <c r="F225" t="s">
+        <v>318</v>
       </c>
       <c r="G225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -12874,7 +12681,7 @@
         <v>0</v>
       </c>
       <c r="J225" t="s">
-        <v>713</v>
+        <v>689</v>
       </c>
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.4">
@@ -12882,13 +12689,16 @@
         <v>315</v>
       </c>
       <c r="C226" t="s">
-        <v>715</v>
+        <v>692</v>
       </c>
       <c r="D226" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E226" t="s">
-        <v>716</v>
+        <v>693</v>
+      </c>
+      <c r="F226" t="s">
+        <v>318</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -12900,7 +12710,7 @@
         <v>0</v>
       </c>
       <c r="J226" t="s">
-        <v>715</v>
+        <v>692</v>
       </c>
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.4">
@@ -12908,13 +12718,16 @@
         <v>315</v>
       </c>
       <c r="C227" t="s">
-        <v>717</v>
+        <v>694</v>
       </c>
       <c r="D227" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E227" t="s">
-        <v>718</v>
+        <v>695</v>
+      </c>
+      <c r="F227" t="s">
+        <v>318</v>
       </c>
       <c r="G227">
         <v>0</v>
@@ -12926,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="J227" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.4">
@@ -12934,16 +12747,19 @@
         <v>315</v>
       </c>
       <c r="C228" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="D228" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E228" t="s">
-        <v>720</v>
+        <v>698</v>
+      </c>
+      <c r="F228" t="s">
+        <v>318</v>
       </c>
       <c r="G228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -12952,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="J228" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.4">
@@ -12960,13 +12776,16 @@
         <v>315</v>
       </c>
       <c r="C229" t="s">
-        <v>721</v>
+        <v>699</v>
       </c>
       <c r="D229" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E229" t="s">
-        <v>722</v>
+        <v>700</v>
+      </c>
+      <c r="F229" t="s">
+        <v>318</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -12978,7 +12797,7 @@
         <v>0</v>
       </c>
       <c r="J229" t="s">
-        <v>721</v>
+        <v>699</v>
       </c>
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.4">
@@ -12986,13 +12805,16 @@
         <v>315</v>
       </c>
       <c r="C230" t="s">
-        <v>723</v>
+        <v>701</v>
       </c>
       <c r="D230" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E230" t="s">
-        <v>724</v>
+        <v>702</v>
+      </c>
+      <c r="F230" t="s">
+        <v>318</v>
       </c>
       <c r="G230">
         <v>0</v>
@@ -13004,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="J230" t="s">
-        <v>723</v>
+        <v>701</v>
       </c>
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.4">
@@ -13012,16 +12834,19 @@
         <v>315</v>
       </c>
       <c r="C231" t="s">
-        <v>725</v>
+        <v>703</v>
       </c>
       <c r="D231" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E231" t="s">
-        <v>726</v>
+        <v>704</v>
+      </c>
+      <c r="F231" t="s">
+        <v>318</v>
       </c>
       <c r="G231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -13030,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="J231" t="s">
-        <v>725</v>
+        <v>703</v>
       </c>
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.4">
@@ -13038,13 +12863,16 @@
         <v>315</v>
       </c>
       <c r="C232" t="s">
-        <v>727</v>
+        <v>705</v>
       </c>
       <c r="D232" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E232" t="s">
-        <v>728</v>
+        <v>706</v>
+      </c>
+      <c r="F232" t="s">
+        <v>318</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -13056,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="J232" t="s">
-        <v>727</v>
+        <v>705</v>
       </c>
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.4">
@@ -13064,13 +12892,13 @@
         <v>315</v>
       </c>
       <c r="C233" t="s">
-        <v>729</v>
+        <v>707</v>
       </c>
       <c r="D233" t="s">
         <v>296</v>
       </c>
       <c r="E233" t="s">
-        <v>730</v>
+        <v>708</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -13082,33 +12910,30 @@
         <v>0</v>
       </c>
       <c r="J233" t="s">
-        <v>729</v>
+        <v>707</v>
       </c>
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B234" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C234" t="s">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="D234" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E234" t="s">
-        <v>732</v>
+        <v>710</v>
       </c>
       <c r="G234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234">
         <v>0</v>
       </c>
       <c r="I234">
         <v>0</v>
-      </c>
-      <c r="J234" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.4">
@@ -13116,13 +12941,13 @@
         <v>315</v>
       </c>
       <c r="C235" t="s">
-        <v>733</v>
+        <v>711</v>
       </c>
       <c r="D235" t="s">
         <v>296</v>
       </c>
       <c r="E235" t="s">
-        <v>734</v>
+        <v>712</v>
       </c>
       <c r="G235">
         <v>0</v>
@@ -13134,7 +12959,7 @@
         <v>0</v>
       </c>
       <c r="J235" t="s">
-        <v>733</v>
+        <v>711</v>
       </c>
     </row>
     <row r="236" spans="2:10" x14ac:dyDescent="0.4">
@@ -13142,16 +12967,16 @@
         <v>315</v>
       </c>
       <c r="C236" t="s">
-        <v>735</v>
+        <v>713</v>
       </c>
       <c r="D236" t="s">
         <v>296</v>
       </c>
       <c r="E236" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -13160,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="J236" t="s">
-        <v>735</v>
+        <v>713</v>
       </c>
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.4">
@@ -13168,13 +12993,13 @@
         <v>315</v>
       </c>
       <c r="C237" t="s">
-        <v>737</v>
+        <v>715</v>
       </c>
       <c r="D237" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E237" t="s">
-        <v>738</v>
+        <v>716</v>
       </c>
       <c r="G237">
         <v>0</v>
@@ -13186,7 +13011,7 @@
         <v>0</v>
       </c>
       <c r="J237" t="s">
-        <v>737</v>
+        <v>715</v>
       </c>
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.4">
@@ -13194,13 +13019,13 @@
         <v>315</v>
       </c>
       <c r="C238" t="s">
-        <v>355</v>
+        <v>717</v>
       </c>
       <c r="D238" t="s">
         <v>296</v>
       </c>
       <c r="E238" t="s">
-        <v>356</v>
+        <v>718</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -13212,7 +13037,7 @@
         <v>0</v>
       </c>
       <c r="J238" t="s">
-        <v>355</v>
+        <v>717</v>
       </c>
     </row>
     <row r="239" spans="2:10" x14ac:dyDescent="0.4">
@@ -13220,16 +13045,16 @@
         <v>315</v>
       </c>
       <c r="C239" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
       <c r="D239" t="s">
-        <v>740</v>
+        <v>296</v>
       </c>
       <c r="E239" t="s">
-        <v>741</v>
+        <v>720</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -13238,7 +13063,7 @@
         <v>0</v>
       </c>
       <c r="J239" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.4">
@@ -13246,13 +13071,13 @@
         <v>315</v>
       </c>
       <c r="C240" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
       <c r="D240" t="s">
         <v>296</v>
       </c>
       <c r="E240" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="G240">
         <v>0</v>
@@ -13264,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="J240" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
     </row>
     <row r="241" spans="2:10" x14ac:dyDescent="0.4">
@@ -13272,13 +13097,13 @@
         <v>315</v>
       </c>
       <c r="C241" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
       <c r="D241" t="s">
         <v>296</v>
       </c>
       <c r="E241" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="G241">
         <v>0</v>
@@ -13290,7 +13115,7 @@
         <v>0</v>
       </c>
       <c r="J241" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
     </row>
     <row r="242" spans="2:10" x14ac:dyDescent="0.4">
@@ -13298,13 +13123,13 @@
         <v>315</v>
       </c>
       <c r="C242" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
       <c r="D242" t="s">
         <v>296</v>
       </c>
       <c r="E242" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="G242">
         <v>1</v>
@@ -13316,7 +13141,7 @@
         <v>0</v>
       </c>
       <c r="J242" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.4">
@@ -13324,16 +13149,16 @@
         <v>315</v>
       </c>
       <c r="C243" t="s">
-        <v>369</v>
+        <v>727</v>
       </c>
       <c r="D243" t="s">
         <v>296</v>
       </c>
       <c r="E243" t="s">
-        <v>370</v>
+        <v>728</v>
       </c>
       <c r="G243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -13342,7 +13167,7 @@
         <v>0</v>
       </c>
       <c r="J243" t="s">
-        <v>371</v>
+        <v>727</v>
       </c>
     </row>
     <row r="244" spans="2:10" x14ac:dyDescent="0.4">
@@ -13350,16 +13175,16 @@
         <v>315</v>
       </c>
       <c r="C244" t="s">
-        <v>372</v>
+        <v>729</v>
       </c>
       <c r="D244" t="s">
         <v>296</v>
       </c>
       <c r="E244" t="s">
-        <v>373</v>
+        <v>730</v>
       </c>
       <c r="G244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -13368,24 +13193,24 @@
         <v>0</v>
       </c>
       <c r="J244" t="s">
-        <v>374</v>
+        <v>729</v>
       </c>
     </row>
     <row r="245" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B245" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C245" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="D245" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E245" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -13394,21 +13219,21 @@
         <v>0</v>
       </c>
       <c r="J245" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
     </row>
     <row r="246" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B246" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C246" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="D246" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E246" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -13420,21 +13245,21 @@
         <v>0</v>
       </c>
       <c r="J246" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
     </row>
     <row r="247" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B247" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C247" t="s">
-        <v>752</v>
+        <v>735</v>
       </c>
       <c r="D247" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E247" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="G247">
         <v>0</v>
@@ -13446,21 +13271,21 @@
         <v>0</v>
       </c>
       <c r="J247" t="s">
-        <v>752</v>
+        <v>735</v>
       </c>
     </row>
     <row r="248" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B248" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C248" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="D248" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E248" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
       <c r="G248">
         <v>0</v>
@@ -13472,21 +13297,21 @@
         <v>0</v>
       </c>
       <c r="J248" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
     </row>
     <row r="249" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B249" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C249" t="s">
-        <v>756</v>
+        <v>355</v>
       </c>
       <c r="D249" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E249" t="s">
-        <v>757</v>
+        <v>356</v>
       </c>
       <c r="G249">
         <v>0</v>
@@ -13498,21 +13323,21 @@
         <v>0</v>
       </c>
       <c r="J249" t="s">
-        <v>756</v>
+        <v>355</v>
       </c>
     </row>
     <row r="250" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B250" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C250" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="D250" t="s">
-        <v>303</v>
+        <v>740</v>
       </c>
       <c r="E250" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -13524,7 +13349,7 @@
         <v>0</v>
       </c>
       <c r="J250" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
     </row>
     <row r="251" spans="2:10" x14ac:dyDescent="0.4">
@@ -13532,24 +13357,310 @@
         <v>315</v>
       </c>
       <c r="C251" t="s">
+        <v>742</v>
+      </c>
+      <c r="D251" t="s">
+        <v>296</v>
+      </c>
+      <c r="E251" t="s">
+        <v>743</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="252" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B252" t="s">
+        <v>315</v>
+      </c>
+      <c r="C252" t="s">
+        <v>744</v>
+      </c>
+      <c r="D252" t="s">
+        <v>296</v>
+      </c>
+      <c r="E252" t="s">
+        <v>745</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="253" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B253" t="s">
+        <v>315</v>
+      </c>
+      <c r="C253" t="s">
+        <v>746</v>
+      </c>
+      <c r="D253" t="s">
+        <v>296</v>
+      </c>
+      <c r="E253" t="s">
+        <v>747</v>
+      </c>
+      <c r="G253">
+        <v>1</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="254" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B254" t="s">
+        <v>315</v>
+      </c>
+      <c r="C254" t="s">
+        <v>369</v>
+      </c>
+      <c r="D254" t="s">
+        <v>296</v>
+      </c>
+      <c r="E254" t="s">
+        <v>370</v>
+      </c>
+      <c r="G254">
+        <v>1</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="255" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B255" t="s">
+        <v>315</v>
+      </c>
+      <c r="C255" t="s">
+        <v>372</v>
+      </c>
+      <c r="D255" t="s">
+        <v>296</v>
+      </c>
+      <c r="E255" t="s">
+        <v>373</v>
+      </c>
+      <c r="G255">
+        <v>1</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="256" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B256" t="s">
+        <v>294</v>
+      </c>
+      <c r="C256" t="s">
+        <v>748</v>
+      </c>
+      <c r="D256" t="s">
+        <v>303</v>
+      </c>
+      <c r="E256" t="s">
+        <v>749</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="257" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B257" t="s">
+        <v>294</v>
+      </c>
+      <c r="C257" t="s">
+        <v>750</v>
+      </c>
+      <c r="D257" t="s">
+        <v>303</v>
+      </c>
+      <c r="E257" t="s">
+        <v>751</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="258" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B258" t="s">
+        <v>294</v>
+      </c>
+      <c r="C258" t="s">
+        <v>752</v>
+      </c>
+      <c r="D258" t="s">
+        <v>303</v>
+      </c>
+      <c r="E258" t="s">
+        <v>753</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="259" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B259" t="s">
+        <v>294</v>
+      </c>
+      <c r="C259" t="s">
+        <v>754</v>
+      </c>
+      <c r="D259" t="s">
+        <v>303</v>
+      </c>
+      <c r="E259" t="s">
+        <v>755</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="260" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B260" t="s">
+        <v>294</v>
+      </c>
+      <c r="C260" t="s">
+        <v>756</v>
+      </c>
+      <c r="D260" t="s">
+        <v>303</v>
+      </c>
+      <c r="E260" t="s">
+        <v>757</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="261" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B261" t="s">
+        <v>294</v>
+      </c>
+      <c r="C261" t="s">
+        <v>758</v>
+      </c>
+      <c r="D261" t="s">
+        <v>303</v>
+      </c>
+      <c r="E261" t="s">
+        <v>759</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="262" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B262" t="s">
+        <v>315</v>
+      </c>
+      <c r="C262" t="s">
         <v>760</v>
       </c>
-      <c r="D251" t="s">
+      <c r="D262" t="s">
         <v>320</v>
       </c>
-      <c r="E251" t="s">
+      <c r="E262" t="s">
         <v>761</v>
       </c>
-      <c r="G251">
-        <v>1</v>
-      </c>
-      <c r="H251">
-        <v>0</v>
-      </c>
-      <c r="I251">
-        <v>0</v>
-      </c>
-      <c r="J251" t="s">
+      <c r="G262">
+        <v>1</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262" t="s">
         <v>760</v>
       </c>
     </row>
@@ -13560,10 +13671,10 @@
     </sortState>
   </autoFilter>
   <mergeCells count="4">
-    <mergeCell ref="M54:M59"/>
+    <mergeCell ref="M64:M69"/>
     <mergeCell ref="M2:M18"/>
     <mergeCell ref="M37:M42"/>
-    <mergeCell ref="M43:M53"/>
+    <mergeCell ref="M53:M63"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\e_pcmaster_elecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F66E2A1-AE05-4AF9-82EA-E825E8913B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7E3332-1310-4E8F-9900-7DC89E5FD084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2220" windowWidth="23415" windowHeight="11295" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="-25290" yWindow="2415" windowWidth="23415" windowHeight="11295" activeTab="3" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="1012">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -2967,18 +2967,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>M00215 신호가 들어오면 에러메시지 창을 띄우고 거기 화면에 PC에서 모듈 리셋 신호 버튼 필요(모듈 에러 크리어)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PLC 와의 효률적 통신을 위해서 필요하면 조작이나 상태 확인 관계는 200ms 주기로 통신도 가능해셔요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오류 신호가 들어오면 오류내용을 오류목록에 기록하고 알람창에 오류 내용 띄움, M215는 M115 에러 크리어 신호와 연계 함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>_010_W_TR3_temp_high_set</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3144,6 +3136,123 @@
   </si>
   <si>
     <t>배기휀 써멀 동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M00221</t>
+  </si>
+  <si>
+    <t>M00222</t>
+  </si>
+  <si>
+    <t>M00223</t>
+  </si>
+  <si>
+    <t>M00224</t>
+  </si>
+  <si>
+    <t>aircon01_operation</t>
+  </si>
+  <si>
+    <t>aircon02_operation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에어컨01 가동 (환기팬 연동 정지)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에어컨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>환기팬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M00225</t>
+  </si>
+  <si>
+    <t>PLC_to_PC_heart_bit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3151,7 +3260,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3209,6 +3318,25 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3238,7 +3366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3277,6 +3405,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6827,7 +6964,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q251"/>
+  <dimension ref="A1:Q257"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
@@ -6912,8 +7049,8 @@
       <c r="L2" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="M2" s="12" t="s">
-        <v>957</v>
+      <c r="M2" s="13" t="s">
+        <v>956</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>342</v>
@@ -6962,7 +7099,7 @@
       <c r="L3" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="M3" s="12"/>
+      <c r="M3" s="13"/>
       <c r="O3" s="6" t="s">
         <v>293</v>
       </c>
@@ -6995,7 +7132,7 @@
       <c r="L4" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="M4" s="12"/>
+      <c r="M4" s="13"/>
       <c r="O4" s="6" t="s">
         <v>920</v>
       </c>
@@ -7028,7 +7165,7 @@
       <c r="L5" s="6" t="s">
         <v>898</v>
       </c>
-      <c r="M5" s="12"/>
+      <c r="M5" s="13"/>
       <c r="O5" s="6" t="s">
         <v>921</v>
       </c>
@@ -7065,7 +7202,7 @@
       <c r="L6" s="10" t="s">
         <v>899</v>
       </c>
-      <c r="M6" s="12"/>
+      <c r="M6" s="13"/>
       <c r="O6" s="10" t="s">
         <v>922</v>
       </c>
@@ -7105,12 +7242,12 @@
         <v>440</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="M7" s="12"/>
+      <c r="M7" s="13"/>
       <c r="O7" s="8" t="s">
         <v>450</v>
       </c>
@@ -7118,7 +7255,7 @@
         <v>919</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -7129,7 +7266,7 @@
         <v>294</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D8" t="s">
         <v>303</v>
@@ -7150,12 +7287,12 @@
         <v>446</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="M8" s="12"/>
+      <c r="M8" s="13"/>
       <c r="O8" s="8" t="s">
         <v>557</v>
       </c>
@@ -7163,7 +7300,7 @@
         <v>919</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -7196,9 +7333,9 @@
         <v>919</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>966</v>
-      </c>
-      <c r="M9" s="12"/>
+        <v>964</v>
+      </c>
+      <c r="M9" s="13"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -7229,12 +7366,12 @@
         <v>454</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="M10" s="12"/>
+      <c r="M10" s="13"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -7270,7 +7407,7 @@
       <c r="L11" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M11" s="12"/>
+      <c r="M11" s="13"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -7301,12 +7438,12 @@
         <v>466</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="M12" s="12"/>
+      <c r="M12" s="13"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -7337,12 +7474,12 @@
         <v>547</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="M13" s="12"/>
+      <c r="M13" s="13"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -7352,7 +7489,7 @@
         <v>294</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D14" t="s">
         <v>303</v>
@@ -7373,12 +7510,12 @@
         <v>553</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="M14" s="12"/>
+      <c r="M14" s="13"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
@@ -7410,9 +7547,9 @@
         <v>919</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>967</v>
-      </c>
-      <c r="M15" s="12"/>
+        <v>965</v>
+      </c>
+      <c r="M15" s="13"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -7443,12 +7580,12 @@
         <v>561</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="M16" s="12"/>
+      <c r="M16" s="13"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -7487,7 +7624,7 @@
       <c r="L17" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="M17" s="12"/>
+      <c r="M17" s="13"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -7518,14 +7655,14 @@
         <v>573</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="M18" s="12"/>
-    </row>
-    <row r="19" spans="1:13" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>887</v>
       </c>
@@ -7554,13 +7691,10 @@
         <v>834</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>910</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -8104,16 +8238,13 @@
         <v>0</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>911</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>943</v>
-      </c>
-      <c r="M37" s="12" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -8142,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>911</v>
@@ -8150,7 +8281,6 @@
       <c r="L38" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -8178,7 +8308,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>911</v>
@@ -8186,7 +8316,6 @@
       <c r="L39" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="M39" s="12"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -8222,7 +8351,6 @@
       <c r="L40" s="6" t="s">
         <v>946</v>
       </c>
-      <c r="M40" s="12"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -8258,7 +8386,6 @@
       <c r="L41" s="6" t="s">
         <v>947</v>
       </c>
-      <c r="M41" s="12"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -8294,360 +8421,229 @@
       <c r="L42" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="M42" s="12"/>
-    </row>
-    <row r="43" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>868</v>
-      </c>
-      <c r="B43" t="s">
-        <v>315</v>
-      </c>
-      <c r="C43" t="s">
-        <v>357</v>
-      </c>
-      <c r="D43" t="s">
-        <v>296</v>
-      </c>
-      <c r="E43" t="s">
-        <v>358</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>888</v>
-      </c>
-      <c r="L43" s="6"/>
-      <c r="M43" s="12" t="s">
-        <v>894</v>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J43" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>911</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>1008</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>869</v>
-      </c>
-      <c r="B44" t="s">
-        <v>315</v>
-      </c>
-      <c r="C44" t="s">
-        <v>359</v>
-      </c>
-      <c r="D44" t="s">
-        <v>296</v>
-      </c>
-      <c r="E44" t="s">
-        <v>360</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>889</v>
-      </c>
-      <c r="L44" s="6"/>
-      <c r="M44" s="12"/>
+      <c r="J44" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>911</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M44" s="15" t="s">
+        <v>1009</v>
+      </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>870</v>
-      </c>
-      <c r="B45" t="s">
-        <v>315</v>
-      </c>
-      <c r="C45" t="s">
-        <v>361</v>
-      </c>
-      <c r="D45" t="s">
-        <v>296</v>
-      </c>
-      <c r="E45" t="s">
-        <v>362</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>361</v>
-      </c>
+      <c r="J45" s="6"/>
       <c r="K45" s="6" t="s">
-        <v>890</v>
-      </c>
-      <c r="L45" s="6"/>
+        <v>911</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>1004</v>
+      </c>
       <c r="M45" s="12"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>871</v>
-      </c>
-      <c r="B46" t="s">
-        <v>315</v>
-      </c>
-      <c r="C46" t="s">
-        <v>363</v>
-      </c>
-      <c r="D46" t="s">
-        <v>296</v>
-      </c>
-      <c r="E46" t="s">
-        <v>364</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>363</v>
-      </c>
+      <c r="J46" s="6"/>
       <c r="K46" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="L46" s="6"/>
+        <v>911</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>1005</v>
+      </c>
       <c r="M46" s="12"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>872</v>
-      </c>
-      <c r="B47" t="s">
-        <v>315</v>
-      </c>
-      <c r="C47" t="s">
-        <v>365</v>
-      </c>
-      <c r="D47" t="s">
-        <v>296</v>
-      </c>
-      <c r="E47" t="s">
-        <v>366</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
       <c r="J47" s="6" t="s">
-        <v>959</v>
+        <v>1011</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>892</v>
-      </c>
-      <c r="L47" s="6"/>
+        <v>911</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>1010</v>
+      </c>
       <c r="M47" s="12"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>873</v>
-      </c>
-      <c r="B48" t="s">
-        <v>315</v>
-      </c>
-      <c r="C48" t="s">
-        <v>367</v>
-      </c>
-      <c r="D48" t="s">
-        <v>296</v>
-      </c>
-      <c r="E48" t="s">
-        <v>368</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>960</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>893</v>
-      </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
       <c r="L48" s="6"/>
       <c r="M48" s="12"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B49" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="D49" s="4" t="s">
+    <row r="49" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>868</v>
+      </c>
+      <c r="B49" t="s">
+        <v>315</v>
+      </c>
+      <c r="C49" t="s">
+        <v>357</v>
+      </c>
+      <c r="D49" t="s">
         <v>296</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4">
-        <v>1</v>
-      </c>
-      <c r="H49" s="4">
-        <v>0</v>
-      </c>
-      <c r="I49" s="4">
-        <v>0</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>968</v>
+      <c r="E49" t="s">
+        <v>358</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>888</v>
       </c>
       <c r="L49" s="6"/>
-      <c r="M49" s="12"/>
+      <c r="M49" s="13" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B50" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="A50" t="s">
+        <v>869</v>
+      </c>
+      <c r="B50" t="s">
+        <v>315</v>
+      </c>
+      <c r="C50" t="s">
+        <v>359</v>
+      </c>
+      <c r="D50" t="s">
         <v>296</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>969</v>
-      </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4">
-        <v>1</v>
-      </c>
-      <c r="H50" s="4">
-        <v>0</v>
-      </c>
-      <c r="I50" s="4">
-        <v>0</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>969</v>
+      <c r="E50" t="s">
+        <v>360</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>889</v>
       </c>
       <c r="L50" s="6"/>
-      <c r="M50" s="12"/>
+      <c r="M50" s="13"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B51" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="A51" t="s">
+        <v>870</v>
+      </c>
+      <c r="B51" t="s">
+        <v>315</v>
+      </c>
+      <c r="C51" t="s">
+        <v>361</v>
+      </c>
+      <c r="D51" t="s">
         <v>296</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4">
-        <v>1</v>
-      </c>
-      <c r="H51" s="4">
-        <v>0</v>
-      </c>
-      <c r="I51" s="4">
-        <v>0</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>970</v>
+      <c r="E51" t="s">
+        <v>362</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>890</v>
       </c>
       <c r="L51" s="6"/>
-      <c r="M51" s="12"/>
+      <c r="M51" s="13"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B52" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="A52" t="s">
+        <v>871</v>
+      </c>
+      <c r="B52" t="s">
+        <v>315</v>
+      </c>
+      <c r="C52" t="s">
+        <v>363</v>
+      </c>
+      <c r="D52" t="s">
         <v>296</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>971</v>
-      </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4">
-        <v>1</v>
-      </c>
-      <c r="H52" s="4">
-        <v>0</v>
-      </c>
-      <c r="I52" s="4">
-        <v>0</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>731</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>971</v>
+      <c r="E52" t="s">
+        <v>364</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>891</v>
       </c>
       <c r="L52" s="6"/>
-      <c r="M52" s="12"/>
-    </row>
-    <row r="53" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M52" s="13"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B53" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C53" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D53" t="s">
         <v>296</v>
       </c>
       <c r="E53" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -8656,32 +8652,32 @@
         <v>0</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="L53" s="8"/>
-      <c r="M53" s="12"/>
+        <v>957</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="L53" s="6"/>
+      <c r="M53" s="13"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B54" t="s">
-        <v>771</v>
+        <v>315</v>
       </c>
       <c r="C54" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D54" t="s">
         <v>296</v>
       </c>
       <c r="E54" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -8690,174 +8686,160 @@
         <v>0</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>973</v>
-      </c>
-      <c r="L54" s="8"/>
-      <c r="M54" s="12" t="s">
-        <v>953</v>
-      </c>
+        <v>958</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="L54" s="6"/>
+      <c r="M54" s="13"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>879</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="B55" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="C55" t="s">
-        <v>375</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E55" t="s">
-        <v>376</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>949</v>
+      <c r="E55" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>713</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>974</v>
-      </c>
-      <c r="L55" s="8"/>
-      <c r="M55" s="12"/>
+        <v>966</v>
+      </c>
+      <c r="L55" s="6"/>
+      <c r="M55" s="13"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>881</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="B56" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="C56" t="s">
-        <v>378</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E56" t="s">
-        <v>379</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>950</v>
+      <c r="E56" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4">
+        <v>0</v>
+      </c>
+      <c r="I56" s="4">
+        <v>0</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>719</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>975</v>
-      </c>
-      <c r="L56" s="8"/>
-      <c r="M56" s="12"/>
+        <v>967</v>
+      </c>
+      <c r="L56" s="6"/>
+      <c r="M56" s="13"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>883</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="B57" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="C57" t="s">
-        <v>381</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C57" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E57" t="s">
-        <v>382</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>951</v>
+      <c r="E57" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>725</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="M57" s="12"/>
+        <v>968</v>
+      </c>
+      <c r="L57" s="6"/>
+      <c r="M57" s="13"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>884</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="B58" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="C58" t="s">
-        <v>384</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E58" t="s">
-        <v>385</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>952</v>
+      <c r="E58" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4">
+        <v>0</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>731</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>977</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>980</v>
-      </c>
-      <c r="M58" s="12"/>
-    </row>
-    <row r="59" spans="1:13" ht="82.15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>969</v>
+      </c>
+      <c r="L58" s="6"/>
+      <c r="M58" s="13"/>
+    </row>
+    <row r="59" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="B59" t="s">
         <v>771</v>
       </c>
       <c r="C59" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="D59" t="s">
         <v>296</v>
       </c>
       <c r="E59" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -8866,224 +8848,281 @@
         <v>0</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>955</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>978</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>981</v>
-      </c>
-      <c r="M59" s="12"/>
+        <v>371</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>970</v>
+      </c>
+      <c r="L59" s="8"/>
+      <c r="M59" s="13"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>877</v>
+      </c>
+      <c r="B60" t="s">
+        <v>771</v>
+      </c>
+      <c r="C60" t="s">
+        <v>372</v>
+      </c>
+      <c r="D60" t="s">
+        <v>296</v>
+      </c>
+      <c r="E60" t="s">
+        <v>373</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="L60" s="8"/>
+      <c r="M60" s="13" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>879</v>
+      </c>
+      <c r="B61" t="s">
+        <v>771</v>
+      </c>
+      <c r="C61" t="s">
+        <v>375</v>
+      </c>
+      <c r="D61" t="s">
+        <v>296</v>
+      </c>
+      <c r="E61" t="s">
+        <v>376</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="L61" s="8"/>
+      <c r="M61" s="13"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>881</v>
+      </c>
+      <c r="B62" t="s">
+        <v>771</v>
+      </c>
+      <c r="C62" t="s">
+        <v>378</v>
+      </c>
+      <c r="D62" t="s">
+        <v>296</v>
+      </c>
+      <c r="E62" t="s">
+        <v>379</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="L62" s="8"/>
+      <c r="M62" s="13"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>883</v>
+      </c>
+      <c r="B63" t="s">
+        <v>771</v>
+      </c>
+      <c r="C63" t="s">
+        <v>381</v>
+      </c>
+      <c r="D63" t="s">
+        <v>296</v>
+      </c>
+      <c r="E63" t="s">
+        <v>382</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="M63" s="13"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>884</v>
+      </c>
+      <c r="B64" t="s">
+        <v>771</v>
+      </c>
+      <c r="C64" t="s">
+        <v>384</v>
+      </c>
+      <c r="D64" t="s">
+        <v>296</v>
+      </c>
+      <c r="E64" t="s">
+        <v>385</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="M64" s="13"/>
+    </row>
+    <row r="65" spans="1:13" ht="82.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>885</v>
+      </c>
+      <c r="B65" t="s">
+        <v>771</v>
+      </c>
+      <c r="C65" t="s">
+        <v>387</v>
+      </c>
+      <c r="D65" t="s">
+        <v>296</v>
+      </c>
+      <c r="E65" t="s">
+        <v>388</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="M65" s="13"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
         <v>315</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C79" t="s">
         <v>405</v>
       </c>
-      <c r="D73" t="s">
-        <v>303</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="D79" t="s">
+        <v>303</v>
+      </c>
+      <c r="E79" t="s">
         <v>406</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>1</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
-        <v>294</v>
-      </c>
-      <c r="C74" t="s">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>294</v>
+      </c>
+      <c r="C80" t="s">
         <v>408</v>
       </c>
-      <c r="D74" t="s">
-        <v>303</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="D80" t="s">
+        <v>303</v>
+      </c>
+      <c r="E80" t="s">
         <v>409</v>
       </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
         <v>408</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B75" t="s">
-        <v>294</v>
-      </c>
-      <c r="C75" t="s">
-        <v>410</v>
-      </c>
-      <c r="D75" t="s">
-        <v>303</v>
-      </c>
-      <c r="E75" t="s">
-        <v>411</v>
-      </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
-        <v>294</v>
-      </c>
-      <c r="C76" t="s">
-        <v>412</v>
-      </c>
-      <c r="D76" t="s">
-        <v>303</v>
-      </c>
-      <c r="E76" t="s">
-        <v>413</v>
-      </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
-        <v>294</v>
-      </c>
-      <c r="C77" t="s">
-        <v>414</v>
-      </c>
-      <c r="D77" t="s">
-        <v>303</v>
-      </c>
-      <c r="E77" t="s">
-        <v>415</v>
-      </c>
-      <c r="G77">
-        <v>1</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
-        <v>294</v>
-      </c>
-      <c r="C78" t="s">
-        <v>416</v>
-      </c>
-      <c r="D78" t="s">
-        <v>303</v>
-      </c>
-      <c r="E78" t="s">
-        <v>417</v>
-      </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
-        <v>294</v>
-      </c>
-      <c r="C79" t="s">
-        <v>418</v>
-      </c>
-      <c r="D79" t="s">
-        <v>303</v>
-      </c>
-      <c r="E79" t="s">
-        <v>419</v>
-      </c>
-      <c r="G79">
-        <v>1</v>
-      </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>315</v>
-      </c>
-      <c r="C80" t="s">
-        <v>420</v>
-      </c>
-      <c r="D80" t="s">
-        <v>303</v>
-      </c>
-      <c r="E80" t="s">
-        <v>421</v>
-      </c>
-      <c r="G80">
-        <v>0</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
@@ -9091,16 +9130,16 @@
         <v>294</v>
       </c>
       <c r="C81" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D81" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E81" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -9109,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
@@ -9117,16 +9156,16 @@
         <v>294</v>
       </c>
       <c r="C82" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="D82" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E82" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -9135,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
@@ -9143,16 +9182,16 @@
         <v>294</v>
       </c>
       <c r="C83" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="D83" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E83" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -9161,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
@@ -9169,16 +9208,16 @@
         <v>294</v>
       </c>
       <c r="C84" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="D84" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E84" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -9187,7 +9226,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
@@ -9195,16 +9234,16 @@
         <v>294</v>
       </c>
       <c r="C85" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="D85" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E85" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -9213,21 +9252,21 @@
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C86" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="D86" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E86" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -9237,23 +9276,20 @@
       </c>
       <c r="I86">
         <v>0</v>
-      </c>
-      <c r="J86" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C87" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="D87" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E87" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -9265,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
@@ -9273,13 +9309,13 @@
         <v>294</v>
       </c>
       <c r="C88" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="D88" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E88" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -9291,7 +9327,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
@@ -9299,16 +9335,16 @@
         <v>294</v>
       </c>
       <c r="C89" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="D89" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E89" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -9317,7 +9353,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
@@ -9325,19 +9361,16 @@
         <v>294</v>
       </c>
       <c r="C90" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="D90" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E90" t="s">
-        <v>443</v>
-      </c>
-      <c r="F90" t="s">
-        <v>318</v>
+        <v>430</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -9346,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
@@ -9354,13 +9387,13 @@
         <v>294</v>
       </c>
       <c r="C91" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="D91" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E91" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -9372,7 +9405,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
@@ -9380,16 +9413,16 @@
         <v>294</v>
       </c>
       <c r="C92" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="D92" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E92" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -9398,27 +9431,24 @@
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C93" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="D93" t="s">
         <v>303</v>
       </c>
       <c r="E93" t="s">
-        <v>449</v>
-      </c>
-      <c r="F93" t="s">
-        <v>318</v>
+        <v>436</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -9427,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
@@ -9435,16 +9465,16 @@
         <v>294</v>
       </c>
       <c r="C94" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="D94" t="s">
         <v>303</v>
       </c>
       <c r="E94" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -9453,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
@@ -9461,16 +9491,16 @@
         <v>294</v>
       </c>
       <c r="C95" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="D95" t="s">
         <v>303</v>
       </c>
       <c r="E95" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -9479,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
@@ -9487,13 +9517,16 @@
         <v>294</v>
       </c>
       <c r="C96" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="D96" t="s">
         <v>303</v>
       </c>
       <c r="E96" t="s">
-        <v>455</v>
+        <v>443</v>
+      </c>
+      <c r="F96" t="s">
+        <v>318</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -9505,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
@@ -9513,19 +9546,16 @@
         <v>294</v>
       </c>
       <c r="C97" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="D97" t="s">
         <v>303</v>
       </c>
       <c r="E97" t="s">
-        <v>457</v>
-      </c>
-      <c r="F97" t="s">
-        <v>318</v>
+        <v>445</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -9534,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
@@ -9542,13 +9572,13 @@
         <v>294</v>
       </c>
       <c r="C98" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="D98" t="s">
         <v>303</v>
       </c>
       <c r="E98" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -9560,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
@@ -9568,13 +9598,16 @@
         <v>294</v>
       </c>
       <c r="C99" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="D99" t="s">
         <v>303</v>
       </c>
       <c r="E99" t="s">
-        <v>461</v>
+        <v>449</v>
+      </c>
+      <c r="F99" t="s">
+        <v>318</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -9586,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
@@ -9594,16 +9627,16 @@
         <v>294</v>
       </c>
       <c r="C100" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="D100" t="s">
         <v>303</v>
       </c>
       <c r="E100" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -9612,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
@@ -9620,16 +9653,16 @@
         <v>294</v>
       </c>
       <c r="C101" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="D101" t="s">
         <v>303</v>
       </c>
       <c r="E101" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -9638,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
@@ -9646,13 +9679,13 @@
         <v>294</v>
       </c>
       <c r="C102" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="D102" t="s">
         <v>303</v>
       </c>
       <c r="E102" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -9664,21 +9697,24 @@
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C103" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="D103" t="s">
         <v>303</v>
       </c>
       <c r="E103" t="s">
-        <v>469</v>
+        <v>457</v>
+      </c>
+      <c r="F103" t="s">
+        <v>318</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -9688,20 +9724,23 @@
       </c>
       <c r="I103">
         <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C104" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D104" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E104" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -9711,20 +9750,23 @@
       </c>
       <c r="I104">
         <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C105" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D105" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="E105" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -9734,6 +9776,9 @@
       </c>
       <c r="I105">
         <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
@@ -9741,13 +9786,13 @@
         <v>294</v>
       </c>
       <c r="C106" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="D106" t="s">
         <v>303</v>
       </c>
       <c r="E106" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -9759,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
@@ -9767,16 +9812,16 @@
         <v>294</v>
       </c>
       <c r="C107" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="D107" t="s">
         <v>303</v>
       </c>
       <c r="E107" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -9785,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.3">
@@ -9793,16 +9838,16 @@
         <v>294</v>
       </c>
       <c r="C108" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="D108" t="s">
         <v>303</v>
       </c>
       <c r="E108" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -9811,85 +9856,76 @@
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C109" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="D109" t="s">
         <v>303</v>
       </c>
       <c r="E109" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109">
         <v>0</v>
       </c>
       <c r="I109">
         <v>0</v>
-      </c>
-      <c r="J109" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C110" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="D110" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E110" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110">
         <v>0</v>
       </c>
       <c r="I110">
         <v>0</v>
-      </c>
-      <c r="J110" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C111" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="D111" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E111" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111">
         <v>0</v>
       </c>
       <c r="I111">
         <v>0</v>
-      </c>
-      <c r="J111" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.3">
@@ -9897,13 +9933,13 @@
         <v>294</v>
       </c>
       <c r="C112" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D112" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E112" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -9915,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
@@ -9923,13 +9959,13 @@
         <v>294</v>
       </c>
       <c r="C113" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D113" t="s">
         <v>303</v>
       </c>
       <c r="E113" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -9941,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="J113" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.3">
@@ -9949,13 +9985,13 @@
         <v>294</v>
       </c>
       <c r="C114" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="D114" t="s">
         <v>303</v>
       </c>
       <c r="E114" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -9967,7 +10003,7 @@
         <v>0</v>
       </c>
       <c r="J114" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.3">
@@ -9975,16 +10011,16 @@
         <v>294</v>
       </c>
       <c r="C115" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="D115" t="s">
         <v>303</v>
       </c>
       <c r="E115" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -9993,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="J115" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.3">
@@ -10001,13 +10037,13 @@
         <v>294</v>
       </c>
       <c r="C116" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="D116" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E116" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -10019,7 +10055,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.3">
@@ -10027,13 +10063,13 @@
         <v>294</v>
       </c>
       <c r="C117" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="D117" t="s">
         <v>296</v>
       </c>
       <c r="E117" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -10045,7 +10081,7 @@
         <v>0</v>
       </c>
       <c r="J117" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.3">
@@ -10053,13 +10089,13 @@
         <v>294</v>
       </c>
       <c r="C118" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D118" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E118" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -10071,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="J118" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
@@ -10079,13 +10115,13 @@
         <v>294</v>
       </c>
       <c r="C119" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="D119" t="s">
         <v>303</v>
       </c>
       <c r="E119" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -10097,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.3">
@@ -10105,16 +10141,16 @@
         <v>294</v>
       </c>
       <c r="C120" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="D120" t="s">
         <v>303</v>
       </c>
       <c r="E120" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="G120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -10123,7 +10159,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.3">
@@ -10131,13 +10167,13 @@
         <v>294</v>
       </c>
       <c r="C121" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="D121" t="s">
         <v>303</v>
       </c>
       <c r="E121" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -10147,6 +10183,9 @@
       </c>
       <c r="I121">
         <v>0</v>
+      </c>
+      <c r="J121" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
@@ -10154,22 +10193,25 @@
         <v>294</v>
       </c>
       <c r="C122" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="D122" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E122" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="G122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
       <c r="I122">
         <v>0</v>
+      </c>
+      <c r="J122" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
@@ -10177,13 +10219,13 @@
         <v>294</v>
       </c>
       <c r="C123" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D123" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E123" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -10195,7 +10237,7 @@
         <v>0</v>
       </c>
       <c r="J123" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
@@ -10203,13 +10245,13 @@
         <v>294</v>
       </c>
       <c r="C124" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="D124" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E124" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -10221,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
@@ -10229,13 +10271,13 @@
         <v>294</v>
       </c>
       <c r="C125" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D125" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E125" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -10247,7 +10289,7 @@
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
@@ -10255,16 +10297,16 @@
         <v>294</v>
       </c>
       <c r="C126" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="D126" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E126" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -10273,7 +10315,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.3">
@@ -10281,25 +10323,22 @@
         <v>294</v>
       </c>
       <c r="C127" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D127" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E127" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127">
         <v>0</v>
       </c>
       <c r="I127">
         <v>0</v>
-      </c>
-      <c r="J127" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
@@ -10307,25 +10346,22 @@
         <v>294</v>
       </c>
       <c r="C128" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="D128" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E128" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128">
         <v>0</v>
-      </c>
-      <c r="J128" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
@@ -10333,13 +10369,13 @@
         <v>294</v>
       </c>
       <c r="C129" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="D129" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E129" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -10351,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.3">
@@ -10359,13 +10395,13 @@
         <v>294</v>
       </c>
       <c r="C130" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="D130" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E130" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -10377,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.3">
@@ -10385,13 +10421,13 @@
         <v>294</v>
       </c>
       <c r="C131" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="D131" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E131" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -10403,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.3">
@@ -10411,13 +10447,13 @@
         <v>294</v>
       </c>
       <c r="C132" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="D132" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E132" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -10429,7 +10465,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.3">
@@ -10437,16 +10473,16 @@
         <v>294</v>
       </c>
       <c r="C133" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D133" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E133" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -10455,7 +10491,7 @@
         <v>0</v>
       </c>
       <c r="J133" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.3">
@@ -10463,13 +10499,13 @@
         <v>294</v>
       </c>
       <c r="C134" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="D134" t="s">
         <v>296</v>
       </c>
       <c r="E134" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -10481,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.3">
@@ -10489,13 +10525,13 @@
         <v>294</v>
       </c>
       <c r="C135" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="D135" t="s">
         <v>296</v>
       </c>
       <c r="E135" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -10507,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
@@ -10515,13 +10551,13 @@
         <v>294</v>
       </c>
       <c r="C136" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="D136" t="s">
         <v>303</v>
       </c>
       <c r="E136" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -10533,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.3">
@@ -10541,13 +10577,13 @@
         <v>294</v>
       </c>
       <c r="C137" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="D137" t="s">
         <v>303</v>
       </c>
       <c r="E137" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -10559,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="J137" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.3">
@@ -10567,16 +10603,16 @@
         <v>294</v>
       </c>
       <c r="C138" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="D138" t="s">
         <v>303</v>
       </c>
       <c r="E138" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -10585,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="J138" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.3">
@@ -10593,13 +10629,13 @@
         <v>294</v>
       </c>
       <c r="C139" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="D139" t="s">
         <v>303</v>
       </c>
       <c r="E139" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -10611,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.3">
@@ -10619,16 +10655,16 @@
         <v>294</v>
       </c>
       <c r="C140" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="D140" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E140" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -10637,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="J140" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.3">
@@ -10645,13 +10681,13 @@
         <v>294</v>
       </c>
       <c r="C141" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="D141" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E141" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -10663,7 +10699,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.3">
@@ -10671,16 +10707,16 @@
         <v>294</v>
       </c>
       <c r="C142" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="D142" t="s">
         <v>303</v>
       </c>
       <c r="E142" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="G142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -10689,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="J142" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.3">
@@ -10697,19 +10733,16 @@
         <v>294</v>
       </c>
       <c r="C143" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D143" t="s">
         <v>303</v>
       </c>
       <c r="E143" t="s">
-        <v>550</v>
-      </c>
-      <c r="F143" t="s">
-        <v>318</v>
+        <v>538</v>
       </c>
       <c r="G143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -10718,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="J143" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
@@ -10726,16 +10759,16 @@
         <v>294</v>
       </c>
       <c r="C144" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="D144" t="s">
         <v>303</v>
       </c>
       <c r="E144" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -10744,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="J144" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.3">
@@ -10752,13 +10785,13 @@
         <v>294</v>
       </c>
       <c r="C145" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="D145" t="s">
         <v>303</v>
       </c>
       <c r="E145" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -10770,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="J145" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.3">
@@ -10778,16 +10811,13 @@
         <v>294</v>
       </c>
       <c r="C146" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="D146" t="s">
         <v>303</v>
       </c>
       <c r="E146" t="s">
-        <v>556</v>
-      </c>
-      <c r="F146" t="s">
-        <v>318</v>
+        <v>544</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -10799,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="J146" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
@@ -10807,16 +10837,16 @@
         <v>294</v>
       </c>
       <c r="C147" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="D147" t="s">
         <v>303</v>
       </c>
       <c r="E147" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -10825,7 +10855,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.3">
@@ -10833,16 +10863,16 @@
         <v>294</v>
       </c>
       <c r="C148" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D148" t="s">
         <v>303</v>
       </c>
       <c r="E148" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -10851,7 +10881,7 @@
         <v>0</v>
       </c>
       <c r="J148" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.3">
@@ -10859,13 +10889,16 @@
         <v>294</v>
       </c>
       <c r="C149" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="D149" t="s">
         <v>303</v>
       </c>
       <c r="E149" t="s">
-        <v>562</v>
+        <v>550</v>
+      </c>
+      <c r="F149" t="s">
+        <v>318</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -10877,7 +10910,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
@@ -10885,19 +10918,16 @@
         <v>294</v>
       </c>
       <c r="C150" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="D150" t="s">
         <v>303</v>
       </c>
       <c r="E150" t="s">
-        <v>564</v>
-      </c>
-      <c r="F150" t="s">
-        <v>318</v>
+        <v>552</v>
       </c>
       <c r="G150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -10906,7 +10936,7 @@
         <v>0</v>
       </c>
       <c r="J150" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
@@ -10914,16 +10944,13 @@
         <v>294</v>
       </c>
       <c r="C151" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D151" t="s">
         <v>303</v>
       </c>
       <c r="E151" t="s">
-        <v>566</v>
-      </c>
-      <c r="F151" t="s">
-        <v>318</v>
+        <v>554</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -10935,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.3">
@@ -10943,13 +10970,16 @@
         <v>294</v>
       </c>
       <c r="C152" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="D152" t="s">
         <v>303</v>
       </c>
       <c r="E152" t="s">
-        <v>568</v>
+        <v>556</v>
+      </c>
+      <c r="F152" t="s">
+        <v>318</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -10961,7 +10991,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
     </row>
     <row r="153" spans="2:10" x14ac:dyDescent="0.3">
@@ -10969,16 +10999,16 @@
         <v>294</v>
       </c>
       <c r="C153" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="D153" t="s">
         <v>303</v>
       </c>
       <c r="E153" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -10987,7 +11017,7 @@
         <v>0</v>
       </c>
       <c r="J153" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.3">
@@ -10995,16 +11025,16 @@
         <v>294</v>
       </c>
       <c r="C154" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="D154" t="s">
         <v>303</v>
       </c>
       <c r="E154" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="G154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -11013,7 +11043,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.3">
@@ -11021,13 +11051,13 @@
         <v>294</v>
       </c>
       <c r="C155" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D155" t="s">
         <v>303</v>
       </c>
       <c r="E155" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -11039,24 +11069,27 @@
         <v>0</v>
       </c>
       <c r="J155" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C156" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="D156" t="s">
         <v>303</v>
       </c>
       <c r="E156" t="s">
-        <v>576</v>
+        <v>564</v>
+      </c>
+      <c r="F156" t="s">
+        <v>318</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -11065,24 +11098,27 @@
         <v>0</v>
       </c>
       <c r="J156" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C157" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D157" t="s">
         <v>303</v>
       </c>
       <c r="E157" t="s">
-        <v>578</v>
+        <v>566</v>
+      </c>
+      <c r="F157" t="s">
+        <v>318</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -11091,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="J157" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
@@ -11099,16 +11135,16 @@
         <v>294</v>
       </c>
       <c r="C158" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="D158" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E158" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -11117,7 +11153,7 @@
         <v>0</v>
       </c>
       <c r="J158" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.3">
@@ -11125,13 +11161,13 @@
         <v>294</v>
       </c>
       <c r="C159" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="D159" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E159" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -11143,7 +11179,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.3">
@@ -11151,16 +11187,16 @@
         <v>294</v>
       </c>
       <c r="C160" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E160" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -11169,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="J160" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.3">
@@ -11177,16 +11213,16 @@
         <v>294</v>
       </c>
       <c r="C161" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="D161" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E161" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -11195,21 +11231,21 @@
         <v>0</v>
       </c>
       <c r="J161" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C162" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="D162" t="s">
-        <v>509</v>
+        <v>303</v>
       </c>
       <c r="E162" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="G162">
         <v>0</v>
@@ -11221,21 +11257,21 @@
         <v>0</v>
       </c>
       <c r="J162" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C163" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="D163" t="s">
-        <v>423</v>
+        <v>303</v>
       </c>
       <c r="E163" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -11247,7 +11283,7 @@
         <v>0</v>
       </c>
       <c r="J163" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.3">
@@ -11255,13 +11291,13 @@
         <v>294</v>
       </c>
       <c r="C164" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="D164" t="s">
-        <v>509</v>
+        <v>423</v>
       </c>
       <c r="E164" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -11273,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="J164" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
@@ -11281,13 +11317,13 @@
         <v>294</v>
       </c>
       <c r="C165" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="D165" t="s">
         <v>509</v>
       </c>
       <c r="E165" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -11299,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="J165" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.3">
@@ -11307,13 +11343,13 @@
         <v>294</v>
       </c>
       <c r="C166" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="D166" t="s">
         <v>423</v>
       </c>
       <c r="E166" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -11325,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="J166" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.3">
@@ -11333,13 +11369,13 @@
         <v>294</v>
       </c>
       <c r="C167" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="D167" t="s">
         <v>509</v>
       </c>
       <c r="E167" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -11351,7 +11387,7 @@
         <v>0</v>
       </c>
       <c r="J167" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.3">
@@ -11359,13 +11395,13 @@
         <v>294</v>
       </c>
       <c r="C168" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="D168" t="s">
         <v>509</v>
       </c>
       <c r="E168" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -11377,7 +11413,7 @@
         <v>0</v>
       </c>
       <c r="J168" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.3">
@@ -11385,13 +11421,13 @@
         <v>294</v>
       </c>
       <c r="C169" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="D169" t="s">
-        <v>509</v>
+        <v>423</v>
       </c>
       <c r="E169" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -11403,7 +11439,7 @@
         <v>0</v>
       </c>
       <c r="J169" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.3">
@@ -11411,16 +11447,16 @@
         <v>294</v>
       </c>
       <c r="C170" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="D170" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E170" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -11429,7 +11465,7 @@
         <v>0</v>
       </c>
       <c r="J170" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.3">
@@ -11437,16 +11473,16 @@
         <v>294</v>
       </c>
       <c r="C171" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="D171" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E171" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="G171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -11455,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="J171" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.3">
@@ -11463,16 +11499,16 @@
         <v>294</v>
       </c>
       <c r="C172" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="D172" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="E172" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -11481,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="J172" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
@@ -11489,16 +11525,16 @@
         <v>294</v>
       </c>
       <c r="C173" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="D173" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E173" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -11507,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="J173" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.3">
@@ -11515,16 +11551,16 @@
         <v>294</v>
       </c>
       <c r="C174" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="D174" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E174" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="G174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -11533,7 +11569,7 @@
         <v>0</v>
       </c>
       <c r="J174" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.3">
@@ -11541,16 +11577,16 @@
         <v>294</v>
       </c>
       <c r="C175" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="D175" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="E175" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="G175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -11559,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="J175" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
@@ -11567,13 +11603,13 @@
         <v>294</v>
       </c>
       <c r="C176" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="D176" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E176" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -11585,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="J176" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
@@ -11593,16 +11629,16 @@
         <v>294</v>
       </c>
       <c r="C177" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="D177" t="s">
         <v>303</v>
       </c>
       <c r="E177" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="G177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -11611,7 +11647,7 @@
         <v>0</v>
       </c>
       <c r="J177" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
@@ -11619,16 +11655,16 @@
         <v>294</v>
       </c>
       <c r="C178" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="D178" t="s">
         <v>303</v>
       </c>
       <c r="E178" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -11637,7 +11673,7 @@
         <v>0</v>
       </c>
       <c r="J178" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.3">
@@ -11645,13 +11681,13 @@
         <v>294</v>
       </c>
       <c r="C179" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="D179" t="s">
         <v>303</v>
       </c>
       <c r="E179" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -11663,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="J179" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.3">
@@ -11671,13 +11707,13 @@
         <v>294</v>
       </c>
       <c r="C180" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="D180" t="s">
         <v>303</v>
       </c>
       <c r="E180" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -11689,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="J180" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.3">
@@ -11697,13 +11733,13 @@
         <v>294</v>
       </c>
       <c r="C181" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="D181" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E181" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -11715,24 +11751,24 @@
         <v>0</v>
       </c>
       <c r="J181" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C182" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="D182" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E182" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -11741,7 +11777,7 @@
         <v>0</v>
       </c>
       <c r="J182" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.3">
@@ -11749,16 +11785,16 @@
         <v>294</v>
       </c>
       <c r="C183" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="D183" t="s">
         <v>303</v>
       </c>
       <c r="E183" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="G183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -11767,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="J183" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.3">
@@ -11775,16 +11811,16 @@
         <v>294</v>
       </c>
       <c r="C184" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="D184" t="s">
         <v>303</v>
       </c>
       <c r="E184" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="G184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -11793,7 +11829,7 @@
         <v>0</v>
       </c>
       <c r="J184" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.3">
@@ -11801,16 +11837,16 @@
         <v>294</v>
       </c>
       <c r="C185" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="D185" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E185" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -11819,7 +11855,7 @@
         <v>0</v>
       </c>
       <c r="J185" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
@@ -11827,16 +11863,16 @@
         <v>294</v>
       </c>
       <c r="C186" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="D186" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E186" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -11845,7 +11881,7 @@
         <v>0</v>
       </c>
       <c r="J186" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.3">
@@ -11853,16 +11889,16 @@
         <v>294</v>
       </c>
       <c r="C187" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="D187" t="s">
         <v>296</v>
       </c>
       <c r="E187" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -11871,21 +11907,21 @@
         <v>0</v>
       </c>
       <c r="J187" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C188" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="D188" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E188" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="G188">
         <v>0</v>
@@ -11897,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="J188" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.3">
@@ -11905,16 +11941,16 @@
         <v>294</v>
       </c>
       <c r="C189" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="D189" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E189" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -11923,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="J189" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.3">
@@ -11931,16 +11967,16 @@
         <v>294</v>
       </c>
       <c r="C190" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D190" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E190" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -11949,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="J190" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.3">
@@ -11957,13 +11993,13 @@
         <v>294</v>
       </c>
       <c r="C191" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="D191" t="s">
         <v>296</v>
       </c>
       <c r="E191" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -11975,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="J191" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.3">
@@ -11983,13 +12019,13 @@
         <v>294</v>
       </c>
       <c r="C192" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="D192" t="s">
         <v>296</v>
       </c>
       <c r="E192" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -12001,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="J192" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
     </row>
     <row r="193" spans="2:10" x14ac:dyDescent="0.3">
@@ -12009,13 +12045,13 @@
         <v>294</v>
       </c>
       <c r="C193" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="D193" t="s">
         <v>296</v>
       </c>
       <c r="E193" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="G193">
         <v>0</v>
@@ -12027,24 +12063,21 @@
         <v>0</v>
       </c>
       <c r="J193" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
     </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C194" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="D194" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E194" t="s">
-        <v>654</v>
-      </c>
-      <c r="F194" t="s">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="G194">
         <v>0</v>
@@ -12053,27 +12086,24 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C195" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="D195" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E195" t="s">
-        <v>656</v>
-      </c>
-      <c r="F195" t="s">
-        <v>318</v>
+        <v>644</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -12082,27 +12112,24 @@
         <v>0</v>
       </c>
       <c r="I195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C196" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="D196" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E196" t="s">
-        <v>658</v>
-      </c>
-      <c r="F196" t="s">
-        <v>318</v>
+        <v>646</v>
       </c>
       <c r="G196">
         <v>0</v>
@@ -12111,27 +12138,24 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C197" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="D197" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E197" t="s">
-        <v>660</v>
-      </c>
-      <c r="F197" t="s">
-        <v>318</v>
+        <v>648</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -12140,27 +12164,24 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C198" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="D198" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E198" t="s">
-        <v>662</v>
-      </c>
-      <c r="F198" t="s">
-        <v>318</v>
+        <v>650</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -12169,27 +12190,24 @@
         <v>0</v>
       </c>
       <c r="I198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C199" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="D199" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E199" t="s">
-        <v>664</v>
-      </c>
-      <c r="F199" t="s">
-        <v>318</v>
+        <v>652</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -12198,10 +12216,10 @@
         <v>0</v>
       </c>
       <c r="I199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J199" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.3">
@@ -12209,13 +12227,13 @@
         <v>315</v>
       </c>
       <c r="C200" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="D200" t="s">
         <v>320</v>
       </c>
       <c r="E200" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="F200" t="s">
         <v>318</v>
@@ -12230,7 +12248,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.3">
@@ -12238,13 +12256,13 @@
         <v>315</v>
       </c>
       <c r="C201" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="D201" t="s">
         <v>320</v>
       </c>
       <c r="E201" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="F201" t="s">
         <v>318</v>
@@ -12259,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.3">
@@ -12267,13 +12285,13 @@
         <v>315</v>
       </c>
       <c r="C202" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="D202" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E202" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="F202" t="s">
         <v>318</v>
@@ -12288,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.3">
@@ -12296,13 +12314,13 @@
         <v>315</v>
       </c>
       <c r="C203" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="D203" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E203" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="F203" t="s">
         <v>318</v>
@@ -12317,7 +12335,7 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
     </row>
     <row r="204" spans="2:10" x14ac:dyDescent="0.3">
@@ -12325,13 +12343,13 @@
         <v>315</v>
       </c>
       <c r="C204" t="s">
-        <v>351</v>
+        <v>661</v>
       </c>
       <c r="D204" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E204" t="s">
-        <v>352</v>
+        <v>662</v>
       </c>
       <c r="F204" t="s">
         <v>318</v>
@@ -12346,7 +12364,7 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>351</v>
+        <v>661</v>
       </c>
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.3">
@@ -12354,13 +12372,13 @@
         <v>315</v>
       </c>
       <c r="C205" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="D205" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E205" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F205" t="s">
         <v>318</v>
@@ -12375,7 +12393,7 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.3">
@@ -12383,13 +12401,13 @@
         <v>315</v>
       </c>
       <c r="C206" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="D206" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E206" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F206" t="s">
         <v>318</v>
@@ -12404,7 +12422,7 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.3">
@@ -12412,13 +12430,13 @@
         <v>315</v>
       </c>
       <c r="C207" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="D207" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E207" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F207" t="s">
         <v>318</v>
@@ -12433,7 +12451,7 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.3">
@@ -12441,13 +12459,13 @@
         <v>315</v>
       </c>
       <c r="C208" t="s">
-        <v>353</v>
+        <v>669</v>
       </c>
       <c r="D208" t="s">
         <v>296</v>
       </c>
       <c r="E208" t="s">
-        <v>354</v>
+        <v>670</v>
       </c>
       <c r="F208" t="s">
         <v>318</v>
@@ -12462,7 +12480,7 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>353</v>
+        <v>669</v>
       </c>
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.3">
@@ -12470,13 +12488,13 @@
         <v>315</v>
       </c>
       <c r="C209" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="D209" t="s">
         <v>296</v>
       </c>
       <c r="E209" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="F209" t="s">
         <v>318</v>
@@ -12491,7 +12509,7 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
     </row>
     <row r="210" spans="2:10" x14ac:dyDescent="0.3">
@@ -12499,13 +12517,13 @@
         <v>315</v>
       </c>
       <c r="C210" t="s">
-        <v>681</v>
+        <v>351</v>
       </c>
       <c r="D210" t="s">
         <v>296</v>
       </c>
       <c r="E210" t="s">
-        <v>682</v>
+        <v>352</v>
       </c>
       <c r="F210" t="s">
         <v>318</v>
@@ -12520,7 +12538,7 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>681</v>
+        <v>351</v>
       </c>
     </row>
     <row r="211" spans="2:10" x14ac:dyDescent="0.3">
@@ -12528,13 +12546,13 @@
         <v>315</v>
       </c>
       <c r="C211" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="D211" t="s">
         <v>296</v>
       </c>
       <c r="E211" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="F211" t="s">
         <v>318</v>
@@ -12549,7 +12567,7 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.3">
@@ -12557,13 +12575,13 @@
         <v>315</v>
       </c>
       <c r="C212" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="D212" t="s">
         <v>296</v>
       </c>
       <c r="E212" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F212" t="s">
         <v>318</v>
@@ -12578,7 +12596,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.3">
@@ -12586,13 +12604,13 @@
         <v>315</v>
       </c>
       <c r="C213" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="D213" t="s">
         <v>296</v>
       </c>
       <c r="E213" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="F213" t="s">
         <v>318</v>
@@ -12607,7 +12625,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.3">
@@ -12615,13 +12633,13 @@
         <v>315</v>
       </c>
       <c r="C214" t="s">
-        <v>689</v>
+        <v>353</v>
       </c>
       <c r="D214" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E214" t="s">
-        <v>691</v>
+        <v>354</v>
       </c>
       <c r="F214" t="s">
         <v>318</v>
@@ -12633,10 +12651,10 @@
         <v>0</v>
       </c>
       <c r="I214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>689</v>
+        <v>353</v>
       </c>
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.3">
@@ -12644,13 +12662,13 @@
         <v>315</v>
       </c>
       <c r="C215" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="D215" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E215" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="F215" t="s">
         <v>318</v>
@@ -12662,10 +12680,10 @@
         <v>0</v>
       </c>
       <c r="I215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
     </row>
     <row r="216" spans="2:10" x14ac:dyDescent="0.3">
@@ -12673,13 +12691,13 @@
         <v>315</v>
       </c>
       <c r="C216" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="D216" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E216" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="F216" t="s">
         <v>318</v>
@@ -12691,10 +12709,10 @@
         <v>0</v>
       </c>
       <c r="I216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.3">
@@ -12702,13 +12720,13 @@
         <v>315</v>
       </c>
       <c r="C217" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="D217" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E217" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="F217" t="s">
         <v>318</v>
@@ -12720,10 +12738,10 @@
         <v>0</v>
       </c>
       <c r="I217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.3">
@@ -12731,13 +12749,13 @@
         <v>315</v>
       </c>
       <c r="C218" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D218" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E218" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="F218" t="s">
         <v>318</v>
@@ -12749,10 +12767,10 @@
         <v>0</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.3">
@@ -12760,13 +12778,13 @@
         <v>315</v>
       </c>
       <c r="C219" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="D219" t="s">
-        <v>690</v>
+        <v>296</v>
       </c>
       <c r="E219" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="F219" t="s">
         <v>318</v>
@@ -12778,10 +12796,10 @@
         <v>0</v>
       </c>
       <c r="I219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.3">
@@ -12789,13 +12807,13 @@
         <v>315</v>
       </c>
       <c r="C220" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="D220" t="s">
         <v>690</v>
       </c>
       <c r="E220" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="F220" t="s">
         <v>318</v>
@@ -12810,7 +12828,7 @@
         <v>0</v>
       </c>
       <c r="J220" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.3">
@@ -12818,13 +12836,13 @@
         <v>315</v>
       </c>
       <c r="C221" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D221" t="s">
         <v>690</v>
       </c>
       <c r="E221" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="F221" t="s">
         <v>318</v>
@@ -12839,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="J221" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
     </row>
     <row r="222" spans="2:10" x14ac:dyDescent="0.3">
@@ -12847,13 +12865,16 @@
         <v>315</v>
       </c>
       <c r="C222" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="D222" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E222" t="s">
-        <v>708</v>
+        <v>695</v>
+      </c>
+      <c r="F222" t="s">
+        <v>318</v>
       </c>
       <c r="G222">
         <v>0</v>
@@ -12865,21 +12886,24 @@
         <v>0</v>
       </c>
       <c r="J222" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C223" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="D223" t="s">
-        <v>303</v>
+        <v>690</v>
       </c>
       <c r="E223" t="s">
-        <v>710</v>
+        <v>698</v>
+      </c>
+      <c r="F223" t="s">
+        <v>318</v>
       </c>
       <c r="G223">
         <v>0</v>
@@ -12889,6 +12913,9 @@
       </c>
       <c r="I223">
         <v>0</v>
+      </c>
+      <c r="J223" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.3">
@@ -12896,13 +12923,16 @@
         <v>315</v>
       </c>
       <c r="C224" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="D224" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E224" t="s">
-        <v>712</v>
+        <v>700</v>
+      </c>
+      <c r="F224" t="s">
+        <v>318</v>
       </c>
       <c r="G224">
         <v>0</v>
@@ -12914,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="J224" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.3">
@@ -12922,16 +12952,19 @@
         <v>315</v>
       </c>
       <c r="C225" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="D225" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E225" t="s">
-        <v>714</v>
+        <v>702</v>
+      </c>
+      <c r="F225" t="s">
+        <v>318</v>
       </c>
       <c r="G225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -12940,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="J225" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.3">
@@ -12948,13 +12981,16 @@
         <v>315</v>
       </c>
       <c r="C226" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="D226" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E226" t="s">
-        <v>716</v>
+        <v>704</v>
+      </c>
+      <c r="F226" t="s">
+        <v>318</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -12966,7 +13002,7 @@
         <v>0</v>
       </c>
       <c r="J226" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.3">
@@ -12974,13 +13010,16 @@
         <v>315</v>
       </c>
       <c r="C227" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="D227" t="s">
-        <v>296</v>
+        <v>690</v>
       </c>
       <c r="E227" t="s">
-        <v>718</v>
+        <v>706</v>
+      </c>
+      <c r="F227" t="s">
+        <v>318</v>
       </c>
       <c r="G227">
         <v>0</v>
@@ -12992,7 +13031,7 @@
         <v>0</v>
       </c>
       <c r="J227" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.3">
@@ -13000,16 +13039,16 @@
         <v>315</v>
       </c>
       <c r="C228" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="D228" t="s">
         <v>296</v>
       </c>
       <c r="E228" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="G228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -13018,21 +13057,21 @@
         <v>0</v>
       </c>
       <c r="J228" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C229" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="D229" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E229" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -13042,9 +13081,6 @@
       </c>
       <c r="I229">
         <v>0</v>
-      </c>
-      <c r="J229" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.3">
@@ -13052,13 +13088,13 @@
         <v>315</v>
       </c>
       <c r="C230" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="D230" t="s">
         <v>296</v>
       </c>
       <c r="E230" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="G230">
         <v>0</v>
@@ -13070,7 +13106,7 @@
         <v>0</v>
       </c>
       <c r="J230" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.3">
@@ -13078,13 +13114,13 @@
         <v>315</v>
       </c>
       <c r="C231" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="D231" t="s">
         <v>296</v>
       </c>
       <c r="E231" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -13096,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="J231" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.3">
@@ -13104,13 +13140,13 @@
         <v>315</v>
       </c>
       <c r="C232" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="D232" t="s">
         <v>296</v>
       </c>
       <c r="E232" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -13122,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="J232" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.3">
@@ -13130,13 +13166,13 @@
         <v>315</v>
       </c>
       <c r="C233" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="D233" t="s">
         <v>296</v>
       </c>
       <c r="E233" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -13148,7 +13184,7 @@
         <v>0</v>
       </c>
       <c r="J233" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.3">
@@ -13156,13 +13192,13 @@
         <v>315</v>
       </c>
       <c r="C234" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="D234" t="s">
         <v>296</v>
       </c>
       <c r="E234" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="G234">
         <v>1</v>
@@ -13174,7 +13210,7 @@
         <v>0</v>
       </c>
       <c r="J234" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.3">
@@ -13182,13 +13218,13 @@
         <v>315</v>
       </c>
       <c r="C235" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="D235" t="s">
         <v>296</v>
       </c>
       <c r="E235" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="G235">
         <v>0</v>
@@ -13200,7 +13236,7 @@
         <v>0</v>
       </c>
       <c r="J235" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
     </row>
     <row r="236" spans="2:10" x14ac:dyDescent="0.3">
@@ -13208,13 +13244,13 @@
         <v>315</v>
       </c>
       <c r="C236" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="D236" t="s">
         <v>296</v>
       </c>
       <c r="E236" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="G236">
         <v>0</v>
@@ -13226,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="J236" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.3">
@@ -13234,16 +13270,16 @@
         <v>315</v>
       </c>
       <c r="C237" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="D237" t="s">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="E237" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -13252,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="J237" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.3">
@@ -13260,13 +13296,13 @@
         <v>315</v>
       </c>
       <c r="C238" t="s">
-        <v>355</v>
+        <v>727</v>
       </c>
       <c r="D238" t="s">
         <v>296</v>
       </c>
       <c r="E238" t="s">
-        <v>356</v>
+        <v>728</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -13278,7 +13314,7 @@
         <v>0</v>
       </c>
       <c r="J238" t="s">
-        <v>355</v>
+        <v>727</v>
       </c>
     </row>
     <row r="239" spans="2:10" x14ac:dyDescent="0.3">
@@ -13286,13 +13322,13 @@
         <v>315</v>
       </c>
       <c r="C239" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="D239" t="s">
-        <v>740</v>
+        <v>296</v>
       </c>
       <c r="E239" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -13304,7 +13340,7 @@
         <v>0</v>
       </c>
       <c r="J239" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.3">
@@ -13312,16 +13348,16 @@
         <v>315</v>
       </c>
       <c r="C240" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="D240" t="s">
         <v>296</v>
       </c>
       <c r="E240" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -13330,7 +13366,7 @@
         <v>0</v>
       </c>
       <c r="J240" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
     <row r="241" spans="2:10" x14ac:dyDescent="0.3">
@@ -13338,13 +13374,13 @@
         <v>315</v>
       </c>
       <c r="C241" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="D241" t="s">
         <v>296</v>
       </c>
       <c r="E241" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="G241">
         <v>0</v>
@@ -13356,7 +13392,7 @@
         <v>0</v>
       </c>
       <c r="J241" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
     </row>
     <row r="242" spans="2:10" x14ac:dyDescent="0.3">
@@ -13364,16 +13400,16 @@
         <v>315</v>
       </c>
       <c r="C242" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="D242" t="s">
         <v>296</v>
       </c>
       <c r="E242" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="G242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H242">
         <v>0</v>
@@ -13382,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="J242" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.3">
@@ -13390,16 +13426,16 @@
         <v>315</v>
       </c>
       <c r="C243" t="s">
-        <v>369</v>
+        <v>737</v>
       </c>
       <c r="D243" t="s">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="E243" t="s">
-        <v>370</v>
+        <v>738</v>
       </c>
       <c r="G243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -13408,7 +13444,7 @@
         <v>0</v>
       </c>
       <c r="J243" t="s">
-        <v>371</v>
+        <v>737</v>
       </c>
     </row>
     <row r="244" spans="2:10" x14ac:dyDescent="0.3">
@@ -13416,16 +13452,16 @@
         <v>315</v>
       </c>
       <c r="C244" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="D244" t="s">
         <v>296</v>
       </c>
       <c r="E244" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="G244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -13434,21 +13470,21 @@
         <v>0</v>
       </c>
       <c r="J244" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
     </row>
     <row r="245" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B245" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C245" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="D245" t="s">
-        <v>303</v>
+        <v>740</v>
       </c>
       <c r="E245" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="G245">
         <v>0</v>
@@ -13460,21 +13496,21 @@
         <v>0</v>
       </c>
       <c r="J245" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
     </row>
     <row r="246" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B246" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C246" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="D246" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E246" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -13486,21 +13522,21 @@
         <v>0</v>
       </c>
       <c r="J246" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
     </row>
     <row r="247" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B247" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C247" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="D247" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E247" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="G247">
         <v>0</v>
@@ -13512,24 +13548,24 @@
         <v>0</v>
       </c>
       <c r="J247" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
     </row>
     <row r="248" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B248" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C248" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="D248" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E248" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -13538,24 +13574,24 @@
         <v>0</v>
       </c>
       <c r="J248" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
     </row>
     <row r="249" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B249" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C249" t="s">
-        <v>756</v>
+        <v>369</v>
       </c>
       <c r="D249" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E249" t="s">
-        <v>757</v>
+        <v>370</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -13564,24 +13600,24 @@
         <v>0</v>
       </c>
       <c r="J249" t="s">
-        <v>756</v>
+        <v>371</v>
       </c>
     </row>
     <row r="250" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B250" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C250" t="s">
-        <v>758</v>
+        <v>372</v>
       </c>
       <c r="D250" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E250" t="s">
-        <v>759</v>
+        <v>373</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -13590,32 +13626,188 @@
         <v>0</v>
       </c>
       <c r="J250" t="s">
-        <v>758</v>
+        <v>374</v>
       </c>
     </row>
     <row r="251" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B251" t="s">
+        <v>294</v>
+      </c>
+      <c r="C251" t="s">
+        <v>748</v>
+      </c>
+      <c r="D251" t="s">
+        <v>303</v>
+      </c>
+      <c r="E251" t="s">
+        <v>749</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="252" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B252" t="s">
+        <v>294</v>
+      </c>
+      <c r="C252" t="s">
+        <v>750</v>
+      </c>
+      <c r="D252" t="s">
+        <v>303</v>
+      </c>
+      <c r="E252" t="s">
+        <v>751</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="253" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B253" t="s">
+        <v>294</v>
+      </c>
+      <c r="C253" t="s">
+        <v>752</v>
+      </c>
+      <c r="D253" t="s">
+        <v>303</v>
+      </c>
+      <c r="E253" t="s">
+        <v>753</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="254" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B254" t="s">
+        <v>294</v>
+      </c>
+      <c r="C254" t="s">
+        <v>754</v>
+      </c>
+      <c r="D254" t="s">
+        <v>303</v>
+      </c>
+      <c r="E254" t="s">
+        <v>755</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="255" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B255" t="s">
+        <v>294</v>
+      </c>
+      <c r="C255" t="s">
+        <v>756</v>
+      </c>
+      <c r="D255" t="s">
+        <v>303</v>
+      </c>
+      <c r="E255" t="s">
+        <v>757</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="256" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B256" t="s">
+        <v>294</v>
+      </c>
+      <c r="C256" t="s">
+        <v>758</v>
+      </c>
+      <c r="D256" t="s">
+        <v>303</v>
+      </c>
+      <c r="E256" t="s">
+        <v>759</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="257" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B257" t="s">
         <v>315</v>
       </c>
-      <c r="C251" t="s">
+      <c r="C257" t="s">
         <v>760</v>
       </c>
-      <c r="D251" t="s">
+      <c r="D257" t="s">
         <v>320</v>
       </c>
-      <c r="E251" t="s">
+      <c r="E257" t="s">
         <v>761</v>
       </c>
-      <c r="G251">
-        <v>1</v>
-      </c>
-      <c r="H251">
-        <v>0</v>
-      </c>
-      <c r="I251">
-        <v>0</v>
-      </c>
-      <c r="J251" t="s">
+      <c r="G257">
+        <v>1</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257" t="s">
         <v>760</v>
       </c>
     </row>
@@ -13625,11 +13817,10 @@
       <sortCondition ref="K1"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="4">
-    <mergeCell ref="M54:M59"/>
+  <mergeCells count="3">
+    <mergeCell ref="M60:M65"/>
     <mergeCell ref="M2:M18"/>
-    <mergeCell ref="M37:M42"/>
-    <mergeCell ref="M43:M53"/>
+    <mergeCell ref="M49:M59"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -14838,7 +15029,7 @@
         <v>928</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -14864,7 +15055,7 @@
         <v>929</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -14890,7 +15081,7 @@
         <v>930</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -14913,7 +15104,7 @@
         <v>931</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -14939,7 +15130,7 @@
         <v>932</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -14965,7 +15156,7 @@
         <v>933</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -14991,7 +15182,7 @@
         <v>934</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -15017,7 +15208,7 @@
         <v>935</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -15043,7 +15234,7 @@
         <v>936</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -15066,7 +15257,7 @@
         <v>937</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -15092,7 +15283,7 @@
         <v>938</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -15118,7 +15309,7 @@
         <v>939</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -15141,7 +15332,7 @@
         <v>940</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -15164,7 +15355,7 @@
         <v>941</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -15187,7 +15378,7 @@
         <v>942</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -15204,7 +15395,7 @@
         <v>303</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>911</v>
@@ -15213,7 +15404,7 @@
         <v>943</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -15230,7 +15421,7 @@
         <v>303</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>911</v>
@@ -15239,7 +15430,7 @@
         <v>944</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -15256,7 +15447,7 @@
         <v>303</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>911</v>
@@ -15265,7 +15456,7 @@
         <v>945</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -15291,7 +15482,7 @@
         <v>946</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -15317,7 +15508,7 @@
         <v>947</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -15343,7 +15534,7 @@
         <v>948</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
   </sheetData>
